--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -10,7 +10,8 @@
     <sheet name="תורמים" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="קובץ_התאמה_חודשיים" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="מזדמנים" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="לבדיקה_קוויטל" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="שמות_לתפילה" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לבדיקה_קוויטל" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +91,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -30382,6 +30386,7293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G245"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>מזהה_שם</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>מזהה_תורם</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>שם_התורם</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>שמות</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>בקשה</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>דרגת_תפילה</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>תוויות_קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ש-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>אברהם פיין</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>אברהם דוד בן אטה בריינא וזוגתו שושנה בת רות, יונה פרץ בן שושנה , אטה בריינה בת רות לברכה והצלחה בכל הענינים אמן</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ש-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>אהרן יהושע רויז</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>אהרן יהושע בן שרה חוה וזוג' פייגא ליבא בת רייזל פערל , ב' שבתי דוד בן פייגא ליבא לרפואה שלמה במהרה , ב' אברהם בן פייגא ליבא , ב' סימא בת פייגא ליבא , ב' יהודה אריה בן פייגא ליבא לוי יצחק בן שרה חוה וזוג' טעמא מירל בת מינדל דבורה ,ב' שבתי דניאל בן טעמא מירל , ב' ישעיה אליעזר בן טעמא מירל , ב' בן ציון בן טעמא מירל , להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ש-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>אלחנן אברמוביץ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>אלחנן יצחק בן חיה לאה לבריאות ורפואה שלמה - זוגתו רות תמר רבקה בת מרים לאה, לנחת מהילדים שמחה וכל טוב -  חיים יונתן בן רות תמר לזיווג הגון בקרוב. עקיבא מאיר בן רות תמר לזיווג הגון בקרוב. קמואל אפרים בן רות תמר לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ש-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>אלחנן לרר</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>משה אלחנן בן זהבה שרה  וזוגתו אסתר בת יפה 
+רחל בת אסתר 
+שרגא יצחק בן אסתר
+שלום דב בער בן אסתר 
+מלכה בת אסתר 
+להצלחה בכל הענינים ברוחניות ובגשמיות  בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ש-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>אליהו ביטש</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>אליהו בן אסתר לברכה והצלחה ועשירות גדולה, וזוגתו לאה בת דבורה , בנם עזרא בן לאה, בתם אסתר בת לאה, בנם דוד בן לאה, בתם דבורה בת לאה לברכה והצלחה בכל הענינים , בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ש-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>אלירן דהאן</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>אלירן בן בלה, לאה בת יפה, חנה בלה בת לאה, אלחנן בן לאה, זכריה בן לאה, הודיה בת לאה</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ש-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>אסתר קארפ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>אסתר חיה בת שרה פערל חוה לזיווג הגון בקרוב ממש ולפרנסה ברווח והצלחה בכל הענינים, דוד מנחם בן שרה פערל חוה לזיווג הגון בקרוב ממש, נחמה רחל חנה בת שרה פערל חוה לזיווג הגון בקרוב ,אליעזר אהרן בן שרה פערל חוה לפרנסה , לוי שרגא פייבל בן אביגיל לפרנסה ברווח, שרה פערל חוה בת טובה איטא לפרנסה ברווח, יצחק אהרן בן שיינדל צביה לפרנסה ברווח ושפע אמן .מנחם מנדל בן נעכא לרפואה שלמה, מאיה רחל מלכה בת מרים לזיווג הגון בקרוב ממש, משה גרשון בן טובה איטא לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ש-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>אפרים מיטמן</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>אפרים יהושע בן מאשע לברכה והצלחה בכל הענינים, מזל בת רבקה לברכה והצלחה ונחת וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ש-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>אריה לייב קאופמן</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>אהובה מאטל בת בלימא מלכה
+לבריאות איתנה ורפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ש-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>בן ציון אליהו ווינפעלד</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>בן ציון אליהו בן מרגליא צביה, יהודית בת אסתר יוטל,  שפרה בת יהודית לזיווג הגון בקרוב, סאשה רחל בת יהודית, ניחא רבקה בת יהודית, ישראל אברהם בן יהודית לברכה והצחה וכל טוב</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ש-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>בנימין שטטפלד</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>בנימין אליעזר בן ברכה  וזוג' אלישבע דינה בת צפורה אורנה, אריאלה בת אלישבע דינה, עקיבא בן אלישבע דינה,  אהובה בת אלישבע דינה, הילל בן אלישבע דינה,  שלוה רות בת אלישבע דינה - לברכה והצלחה בכל הענינים בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ש-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>בצלאל גוטמן</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>בצלאל שמחה בן פרומט רחל וזוג' חנה שירה בת טובה , ב' תהילה פייגא , ב' שלום ,  להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ש-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>בצלאל זושא מרמרשטיין</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>בלצאל זושא בן שושנה רחל וכל משפחתו לברכה והצלחה בכל הענינים עשירות ושפע וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ש-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>גדליה פנסטר</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>גדליהו ישראל בן ריינה חכמה בינה ודעת ועזות דקדושה והתבוננות בתורה, ולהתקרב להשם ושלום בית וזוגתו אלישבע בת נאווה,שלום בית, לברכה והצלחה בכל הענינים, גדיאל בן אלישבע, שפע בת אלישבע , אמת בן אלישבע , ריינה מלכה בת טובה באשע , להצלחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ש-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>דב וויזער</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>מיכאל דב בן מייטי וזוג' חיה בלימה בת יהודית רבקה, עדינה בת חיה בלימה, שלמה יצחק בן שושנה, נחמה מלכה בת עדינה, דליה נעה בת עדינה. 
+נפתלי ראובן בן שרה ברכה, וזוג' מרים בת חיה בלימה, אריאל שמשון בן מרים.
+יהודה אלימלך בן חיה בלימה
+אהובה אסתר בת חיה בלימה
+רפאל משה בן חיה בלימה</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ש-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>דוד יחיאל מיכל מאסקאוויטש</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>דוד יחיאל מיכל בן אדל לברכה והצלחה וסייעתא דשמיא פרנסה בשפע ורווח , וזוגתו חיה לאה בת חנה עטל, בתם פערל בת חיה לאה , בנם אהרן נחמן בן חיה לאה , לנחת בריאות ושמחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ש-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>דוד מאצעס</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>דוד בן רחל וזוג' רחל בת שושנה , ב' בן יוסף בן רחל , ב' שרה לאה בת רחל לברכה והצלחה בכל הענינים אמן , משה בן ריזא לרפואה שלמה במהרה אמן שמחה בת רחל לזיווג הגון בקרוב ממש ממש אמן</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ש-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>דוד סוטון</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>דוד בן פריידא לברכה והצלחה בכל הענינים, פרנסה ברווח, צדקה דעת לימוד התורה שלום בית ובריאות, וזוג' נחמה בת חנה לברכה והצלחה בכל הענינים, ב' פריידא בת נחמה, ב' אליהו בן נחמה לנחת בריאות והצלחה . פסח בן פינחס, חיה בת פריידא, אדמונד בן פריידא, משה בן חיה להצלחה בכל הענינים, פריידא בת חיה לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ש-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>דוד פק</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>לזכות - דוד יהושע בן קיילא לברכה והצלחה וסייעתא דשמיא וזיווג הגון בקרוב , קיילא בת מלכה חנה לברכה והצלחה ובריאות וכל טוב , איתן ראובן חי בן קיילא - לרפואה שלמה במהרה בריאות איתנה  וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ש-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>דוד פק</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>דוד יהושע בן קיילא לזיווג הגון בקרוב והצלחה בכל הענינים שפע פרנסה וכל טוב  , קיילא בת מלכה חנה , איתן ראובן חי בן קיילא - לברכה והצלחה ובריאות ופרנסה בשפע וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ש-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>דניאל יעקובסון</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>דניאל אבי בן שרה מלכה 
+בריינדל בת גיטל
+יצחק דוב בן תמר יוטה
+לאה נעכא בת בריינדל
+ציפורה שרה מלכה בת לאה נעכא
+זכריה בנימין בן לאה נעכא 
+רפאל אריה בן חיה
+אלנה בת בריינדל 
+שרה מלכה בת אלנה
+יטא חוה בת אלנה 
+צבי אלימלך בן נחמה פריידא
+עטה בת בריינדל 
+אהרן שלמה בן עטה
+יוסף ראובן בן עטה
+הלל מרדכי חיים בן בריינדל 
+אריאלה לאה בת נעמי דיצה
+עטרה רחל בת בריינדל 
+דוד ירמיה בן מרים 
+והושע דוד הלוי בן עטה
+גיטל בת לאה</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ש-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>זאב לאם</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>פתחיה זאב בן לאה מינדל הגפ"ן וישוב הדעת וזוג' אסתר פייגא בת נחמה מאטיל, אהרן שמואל בן אסתר פייגא וזוגתו פסיה מרים בת חיה, יהושע אליקום בן אסתר פייגא לזיווג הגון בקרוב ממש, ב' שמעון בן אסתר פייגא, - לברכה והצלחה ובריאות ופרנסה בשפע גדול ונחת וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ש-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>זאב מרמורשטיין</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>זאב בן רצה להצלחה בכל הענינים ובפרט בעסק שלו שיצליח מאוד מאוד עם הרבה סייעתא דשמיא, וזוג' פייגא רבקה בת סעריל , ב' יצחק מאיר לייב , ב' אהרן , לברכה והצלחה וסייעתא דשמיא, ישעיה בן פערל וזוגתו חיה שרה בת פייגא רבקה, ב' יצחק מאיר שמחה בן חיה שרה, דוד בן פייגא רבקה וזוגתו תהילה חיה בת שרה רבקה</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ש-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>חיים הרשקוביץ</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>חיים בן לאה שרה וזוג' מרים בת טובה גיטל , ב' לאה שרה יהודית לרפואה שלמה והתפתחות רגילה ב' משה ב' חנה, ב' סימא אביבה, ב' יהודה פנחס</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ש-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>חיים וויס</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>חיים בן זיסל דבורה לברכה והצלחה בכל הענינים עושר ואושר ופרנסה בשפע  וברווח וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ש-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>חיים לאקס</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>חיים בן שיינדל וזוג' לאה אסתר בת צביה דבורה מלכה רות. דוד בן אסנת, וזוג' רחל נחמה אליענה בת לאה אסתר, קלמן אריה בן רחל נחמה אליענה, אילה שיינדל בת רחל נחמה אליענה, שרה בת רחל נחמה אליענה, אשר בן רחל נחמה אליענה.
+ראובן בן לאה טילה,  וזוג' שרה מנוחה בת לאה אסתר, ליאורה שיינה בת שרה מנוחה, תמר בת שרה מנוחה, קלמן עזרא בן שרה מנוחה.
+קלמן אליהו בן לאה אסתר, וזוג' אסתר בת הינדל חיה, אהובה רות בת אסתר, יצחק אייזיק בן אסתר. בנימין יצחק בן צביה עליזה, וזוג' רבקה חנה בת לאה אסתר. -  לברכה והצלחה בכל הענינים בריאות הגוף והנפש ופרנסה בשפע וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ש-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>טוביה הופמן</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>טוביה מיכאל בן בינה וזוג' אילנה חוה בת ציפורה , בתם שרה לאה בת אילנה חוה, בתם שיינא ברכה בת אילנה חוה, בנם דוד אריה בן אילנה חוה . בתם מרים רייזל בת אילנה חוה, ב' עזרא צבי בן אילנה חיה, ב' מאיר שמחה בן אילנה חיה - להצלחה בכל הענינים, נחת וכל טוב אמן , בערל בן שיינדל , בינה בת לאה לרפואה שלמה בקרוב , איתמר בן ציפורה לרפואה שלמה , ציפורה בת דובה, דובה בת פריידא לרפואה שלמה אמן</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ש-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>יהושע ווינפעלד</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>יהושע בן מרגליא צביה שיהיה לו הצלחה גדולה בעסק ועשירות ובריאותוכל טוב, זוג' רייזל גולדא בת אסתר יכט להצלחה בריאות ונחת מהילדים וכל טוב, יצחק אלעזר בן מרגליט צביה לברכה והצלחה בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ש-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>יהושע פרידמן</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>אנאל שרה בת יהודית רפואה שלמה לחזרה בתשובה ויראת שמים ,יהושע בן אסתר וזוגתו יהודית בת פולה לברכה והצלחה בכל הענינים, רבקה בת יהודית לחזרה בתשובה ויראת שמים, אסתר בת יהודית לחזרה בתשובה ויראת שמים ,אליהו אוריאל נח בן יהודית לרפואה שלמה במהרה ויהיה בריא ושלם ולגדול בן תורה ויראת שמים אמן</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ש-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>יהושע פרנקל</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>יהושע בן רבקה וכל משפחתו לבריאות ושמחה והצלחה ולגדל את ילדיהם לתורה ושלום בית ונחת מכל יוצ"ח ,יהודית ליבא בת לאה לזש"ק ולרפואה שלמה ושלום בית ,להצלחה בכל הענינים וזש"ק, ב' אביגיל חיה שושנה,ב' אברהם שלום זכריה לבריאות ושמחה וכל טוב, ישראל חיים בן הדסה חיה, דוד צבי בן הדסה חיה לבריאות ושמחה ולגדול לתורה ויר"ש ,רבקה בת שיינדל וכל משפחתה לרפו"ש ולבריאות ושמחה והצלחה ונחת מכל יוצ"ח ,לאה בת בינה וכל משפחתה לרפואה שלמה, לבריאות ושמחה והצלחה ונחת מכל יוצ"ח,דוד שלמה בן רבקה וכל משפחתו לבריאות ושמחה והצלחה ונחת מכל יוצ"ח ,בן ציון בן רבקה, דוד שלמה בן רבקה לבריאות ושמחה והצלחה ונחת מכל יוצ"ח, אלטע מרים בת יהודית לרפו"ש ,מרים פערל בת רבקה וכל משפחתה לבריאות ושמחה והצלחה ונחת מכל יוצ"ח</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ש-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>יהושע רוזנפלד</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>יהושע בן סימי לפרנסה בשפע והצלחה גדולה מאוד בעסקיו והצלחה בקניית הדירה החדשה, וזוג' אילנה רבקה בת חיה שרה,ב' חנה לאה קיילה בת אילנה רבקה, ב' עדינה בת אילנה רבקה,ב' יצחק בן אילנה רבקה, ב' יוסף בם אילנה רבקה , לבריאות והצלחה ונחת ופרנסה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ש-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>יואל שטטפלד</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>יואל יהודה בן ברכה  וזוג' שרה עליזה בת נאשה,  יונתן זאב בן שרה עליזה,  נאווה רינה בת שרה עליזה, עזריאל בן שרה עליזה, מאירה רות בת שרה אליזה - לברכה והצלחה ובריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ש-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>יוסף גולדגלאנץ</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>יוסף בנימין בן סימה דעת תורה, יראת שמים, אידישע נחת, בריאות והצלחה. מרים בת לונה בריאות איתנה לכל המשפחה, אידישע נחת, הצלחה לילדים בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ש-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>יוסף קירזנר</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>יוסף אליהו בן מרים וזוג' יעל טובה בת מזל
+ב' עזריאל יהודה בן יעל טובה, יעקב דוד בן יעל טובה, ליאורה רבקה בת יעל טובה 
+להצלחה גדולה בעסק בלי הפסדים והכל יסתדר על הצד היותר טוב בלי עוגמת נפש בכלל ובריאות הצלחה ונחת</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ש-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>יעקב ברקוביץ</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>עזרא בן ביילא, נורית חיה בת מרים גיטל לבריאות נחת ופרנסה בשפע והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ש-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>יעקב גאלד</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>יעקב בן נעכא וזוג' נחמה רחל בת רבקה, מיכל בת נחמה רחל לזיווג הגון בקרוב , מרים בת נחמה רחל, חיה עליזה בת נחמה רחל, יהושע זאב בן נחמה רחל לבריאות וברכה והצלחה בכל הענינים,  חיים שלום בן העניא רבקה וזוג' רבקה בריינדל בת דבורה הענא, יואל פנחס בן רבקה בריינדל, יהודה מאיר בן רבקה בריינדל, אברהם בן רבקה בריינדל, ישראל אשר בן רבקה בריינדל, שרה אסתר מינדל בת רבקה בריינדל, אהרון יהושע בן רבקה בריינדל לבריאות ונחת ולברכה והצלחה בכל הענינים.  נעכא בת גיטל אברהם יצחק בן מרים שמואל שלמה בן רחל דבורה הענא בת שרה בילא העניא רבקה בת רחל משה אפרים בן פיגא רבקה בת חיה אברהם יצחק בן פנינה פערל לרפואה שלמה במהרה</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ש-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>יעקב יוסף קלאק</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>יעקב יוסף בן אסתר דבורה לברכה והצלחה גדולה בעסק ופרנסה בשפע גדול וזוגתו רחל בת חיה לברכה והצלחה וסייעתא דשמיא , בריאות עושר ואושר וכל טוב אמן , שלמה מרדכי בן חיה לרפואה שלמה במהרה</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ש-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>יעקב מוקאי</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>יעקב בן אסתר לזיווג הגון בקרוב ממש. שי בן אסתר לשידוך הגון בקרוב ממש. אורן בן אסתר לפרנסה בשפע ורווח. שרה בת אסתר לזיווג הגון בקרוב ממש. ניסים בן מרים לרפואה שלמה במהרה. אסתר בת שושנה לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ש-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>יעקב קלמן הורוביץ</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>יעקב קלמן בן אסתר גולדא וזוגתו שיינא עדינה בת רחל לאה, יוסף מאיר בן שיינא עדינה, שמעון גרשון בן שיינא עדינה, לאה דאבא בת שיינא עדינה לרפואה שלמה במהרה ובריאות איתנה אמן, גיטל נעכא בת שיינא עדינה, חנה בת שיינא עדינה, משה חיים בן שיינא עדינה, מרים פערל בת שיינא עדינה, טשרנא טובא בת שיינא עדינה, חוה רבקה בת שיינא עדינה. אברהם מרדכי בן חנה וזוגתו אסתר גאלדא בת גיטל נעכא, אפרים אשר בן לאה דאבא וזוגתו רחל לאה בת ציפורה פייגא, ציפורה פייגא בת רחל לאה.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ש-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>יצחק אדלין</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>יצחק בן חנה רבקה לברכה והצלחה וסייעתא דשמיא</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ש-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>יצחק בליסקו</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>שמואל יצחק בן ציפורה לברכה והצלחה בכל הענינים, פרנסה ברווח ושפע והצלחה גדולה בעסק, וזוג' אסתר טעלצא בת נחמה, ב' יעקב ישראל בן אסתר טעלצא, ב' גולדה ברכה בת אסתר טעלצא, ב' אפרים בן אסתר טעלצא לבריאות הצלחה נחת וכל טוב אמן.  ציפורה בת גולדה לרפואה שלמה ובריאות וכל טוב</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ש-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>יצחק ברגר</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>יצחק משה בן שיינדל וזוג' בתיה מלכה בת פרומט רחל לברכה והצלחה פרנסה בשפע וברווח, ושלום בית ושמחה, ב' עליזה חנה בת בתיה מלכה לשידוך הגון בקרוב ממש , ב' שושנה ציפורה, ב' יהושע אריה, לנחת בריאות וכל טוב אמן.  שיינדל בת יודית לברכה והצלחה בכל הענינים  בנימין זאב בן חנה ביילא וזוגתו חביבה מרים בת בתיה מלכה , יוסף מרדכי בן חביבה מרים , מיכל בת חביבה מרים ,  אליהו שרגא בן מרים צינא וזוגתו שרה דינה בת בתיה מלכה , יוסף צבי בן שרה דינה</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ש-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>יצחק טעפפער</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>יצחק יוסף בן שרה לפרנסה בשפע ורווח, וזוגתו רעכל בת זהבה, בנם יחיאל מיכל בן רעכל , בנם זאב וועלוויל בן רעכל, בנם מנחם בן רעכל, בנם רפאל שמואל בן רעכל, לברכה והצלחה בכל הענינים וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ש-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>יצחק לאווי</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>יצחק צבי בן ניחה גיטל חיה שרה בת מרים, יהודה בן חיה שרה, חנה בת חיה שרה לזיוג הגון בקרוב ממש , טוביה בן חיה שרה, דבורה בת חיה שרה, בפרט חנה בת חיה שרה לרפואה שלימה וזיוג הגון בקרוב.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ש-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>יצחק רוזנפלד</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>יצחק בן סימי ומשפחתו , להצלחה בכל הענינים ופרנסה בשפע וברווח אמן. מנחם ישראל בן חי גאלדא להצלחה בישיבה תורה בהתמדה, ויראת שמים טהורה, ונחת להוריו</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ש-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>יצחק שטטפלד</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>יצחק מאיר בן מרים שרה וזוג' ברכה בת צביה דבורה מלכה רות,  מיכל אילה לאה בת ברכה לרפואה שלמה , מרדכי דוד בן ברכה,  לברכה והצלחה ובריאות וכל טוב אמן. חיים ברוך בן לאה לבריאות ולרפו"ש במהרה</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ש-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>ישעיהו אקרמן</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ישעיהו יחיאל בן צירל אסתר וזוג' עליזה פריידל בת שיינדל ביילא, חיה רחל בת עליזה פריידל, אברהם יעקב בן עליזה פריידל, מיכל מרים בת עליזה פריידל, גבריאל לוי בן עליזה פריידל לברכה והצלחה בכל הענינים נחת ובריאות וכל טוב</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ש-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>ישראל אבא רוזנפלד</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>ישאל אבא בן חנה שרה וזוג' טובה גיטל בת אסתר להתברך בזש''ק בקרוב ממש
+שמואל אליהו בן ציפורה לרפו''ש</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ש-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>ישראל ברודי</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ישראל אריה בן רחל שבע ברכה והצלחה בכל הענינים ופרנסה בשפע וברווח עד בלי די וזוג' דינה רבקה בת לאה מלכה, יהודה לייב בן דינה רבקה, שושנה בת דינה רבקה, ישעיה בן דינה רבקה, אליהו שמחה בן דינה רבקה, גרשון עקיבא בן דינה רבקה להצלחה בכל הענינים פרנסה בשפע וברווח ונחת מכל יוצ'' ח</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ש-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>מאיר מיטמן</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>מאיר אליהו בן מזל לרפואה שלמה ולפרנסה והצלחה , שירה לאה בת פריידא להצלחה ושלום בית , דניאל ראובן בן שירה לאה , ב' אריאלה בת שירה לאה, ב' עזרא בן שירה לאה אפרים יהושע בן מאשע לברכה והצלחה בכל הענינים, מזל בת רבקה לברכה והצלחה ונחת, גבריאל שלום בן מזל לברכה והצלחה ופרנסה וכל טוב</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ש-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>מיכאל ואגו</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>מיכאל בן שרה להצלחה בפרנסה , ובריאות וחיים טובים ומאושרים ,
+והצלחה בכל הענינים , וזוגתו רחל בת שרה להצלחה
+בפרנסה , ובריאות וחיים טובים ומאושרים , והצלחה בכל
+הענינים, משה אהרן יהושע בן רחל , לוי שמואל בן רחל ,
+שררה בת רחל, מרדכי שלום בן רחל - שיראו מהם נחת
+ובריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ש-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>מנחם כהן</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>מנחם בן חיה שיינא לבריאות הגוף והנפש ורפואה שלמה במהרה, ויוכל ללכת על שתי רגליו ויוכל ללכת להתפלל בבית הכנסת שלשה פעמים ביום בלי שום בעיות בכלל, והצלחה בכל הענינים אמן.  טליה דבורה בת חנה רייזל לרפואת הנפש ורפואת הגוף , וחזרה בתשובה , וזיווג הגון בקרוב, דעאל אליעזר בן חנה רייזל לבריאות וחזרה בתשובה במהרה, וזיווג הגון בקרוב וכל טוב אמן. אריה בן חיה שיינא חזרה בתשובה שלמה, רפואה שלמה רפואת הנפש ורפואת הגוף, כדי שיהיה חזק בבריאות גוף ונשמה, כדי לקיים את התורה הקדושה.  גל בן סימי שולמית לרפואת הגוף והנפש, שתהליך הגירושין יעבור בקלות ובמהרה בלי בעיות. סימי שולמית בת רבקה שתזכה לרפואת הנפש והגוף בריאות והצלחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ש-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>מרדכי גדולד</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>מרדכי פרץ בן חיה ואסתר יָכֵט בת שיינדל לרפואה שלמה ואריכות ימים ושנים טובות ובריאות איתנה , סיעתה דשמיא מרובה ברוחניות ובגשמיות ובפרט שיצליח מאוד בכל עסקיו כדי שיוכל להחזיק תורה כמה שיותר ויצליח לקרב הרבה נפשות לעבודת השם יתברך  ושיהיה להם כל הישועות שהם צריכים, שכל בניהם יגדלו להיות תלמידי חכמים ועובדי השם אמיתיים, שארגון הקירוב רחוקים שלו יקבל הרבה תרומות גדולות כדי שיוכל להרחיב את הפעילות  מאירה בת אסתר יָכֵט שתזכה לרפואה שלמה ובריאות איתנה  יוסף מנחם בן אסתר יָכֵט שיזכה לרפואת הנפש והגוף  משה שמעון בן אסתר יָכֵט ואביגיל בת סיגלית  שיזכו לזרע של קיימא</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ש-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>מרדכי זוננשיין</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>מרדכי בן מינדל לברכה והצלחה , אסתר חיה בת רחל לזיווג הגון בקרוב ממש , שרה הענא בת חיה רחל לזיווג הגון בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ש-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>מרים טאובנפלד</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>גבריאל ברוך חיים בן חיה צירל פרנסה טובה בשפע, שמחת חיים, בריאות שלמה וברכה  והצלחה בכל הענינים וזוגתו מרים עדינה בת שיינא חיה לרפואה שלמה במהרה ובריאות הגוף והנפש ברכה והצלחה שמחת חיים ונחת מהילדים לגדלם לתורה ומידות טובות ויראת שמים. עזרא יחיאל משה בן מרים עדינה שיוכל לקרוא טוב ומצוין אנגלית ועברית, להתקדם יפה בקריאה והבנת הנקרא, לבריאות שמחת חיים וברכה והצלחה וחברים טובים שישפיעו עליו לטובה בתורה ובמידות טובות. אלחנן יהודה בן מרים עדינה לבריאות שמחת חיים וברכה והצלחה בתורה ומידות טובות, ושיהיה להם חברים טובים. אורלי מיכל בת מרים עדינה לבריאות שמחת חיים וברכה והצלחה ומידות טובות, ושיהיה לה חברות טובות דוד מאיר בן פערל לרפואה שלמה במהרה. רייזל הינדא בת פערל רפואה שלמה במהרה. ישראל שלמה בן טשרנא לזיווג הגוון.  רחל רבקה בת חיה צירל לרפואה שלמה במהרה. עמיאל דוב בן רחל רבקה לרפואה שלמה רפואת הנפש ורפואת הגוף ובריאות איתנה  במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ש-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>משה דויטש</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>אברהם שמואל בן אלטע רבקה לרפואה שלמה ובריאות איתנה אמן. לאה מלכה בת הינדא רחל, משה אלטר אפרים בן לאה מלכה וזוג' גיטל פערל לאה בת סימא לברכה והצלחה בכל הענינים, נחת בריאות ושמחת החיים, פרנסה בשפע ורווח עד בלי די, חיה דינה בת אסתר רבקה לאה, אהרן יהושע בן אסתר רבקה לאה , שושנה הינדא בת אסתר רבקה לאה להצלחה בכל הענינים והגפ"ן אמן . ישראל אריה לייב בן לאה מלכה וזוג' לאה שושנה בת גולדא מרים וכל יוצ"ח. יוסף דוד יהושע בן לאה מלכה וזוג' חנה יוכבד בת יהודית וכל יוצ"ח. אביבה חנה גולדה בת לאה מלכה בתיה בת אביבה חנה גולדה הינדא בת אביבה חנה גולדה</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ש-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>נתן יחזקאל טעפפר</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>נתן יחזקאל בן רחל לאה לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ש-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>סנדר נייווירטה</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>אלכסנדר זיסקינד בן חנה לאה וזוג' שיינדל בת רוזא , ב' שמואל זכריה ,ב' חיה צביה ,ב' יצחק אברהם , ב' שושנה רבקה לרפו"ש ותהיה בריאה וחזקה, ב' תמר אמונה אהרן בן חיניה וזוג' חנה לאה בת חיה איטא</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ש-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>עזרא מקס</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>עזרא מאיר בן חיה חנה לברכה והצלחה פרנסה ברווח ונחת מכל יוצ''ח שמחה ושלום בית ויישוב הדעת וירא''ש, וזוג' יוכבד רחל בת חוה שיינדל, מרים בת יוכבד רחל, משה יצק בן יוכבד רחל, קיילא בת יוכבד רחל, אסתר בת יוכבד רחל, רבקה בת יוכבד רחל</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ש-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>עקיבא סלקוביץ</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>אברהם עקיבא בן נעמי וזוג' לאה בת פרומא חנה, רייזל שושנה בת לאה, אסתר בת לאה, לברכה והצלחה בכל הענינים אמן אברהם בן פרומא חנה לזיווג הגון בקרוב, יוכבד אורה בת נעמי לזיווג הגון בקרוב, שמואל בן נעמי לזיווג הגון בקרוב, מרים רבקה בת נעמי לזיוג הגון בקרוב</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ש-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>פרץ געווערצמאן</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>פרץ בן פיגא לאה וזוגתו פיגא רבקה בת דבורה לתשובה שלום בית בריאות ורפואה שלמה מכל מכאוביה ופרנסה טובה, שיזכו להשיא את בתם בקרוב. ברוך יצחק בן דובי וזוג' פרומיט שיינדל בת דבורה לתשובה שלום בית בריאות ופרנסה טובה. דוד יהודה בן פרומיט שיינדל לבריאות. שרה רייזל בת פייגא רבקה לרפואה שלמה פרנסה טובה תשובה זיווג הגון בקרוב ובניית בית נאמן בישראל</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ש-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>צבי גייקובס</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>צבי יוסף בן אסתר עליזה שמחה שינה מאשה בת ברכה אריה לייב בן עליזה שמחה שינה מאשה, אסתר בת פורטונה כתון לרפואה שלמה ובריאות איתנה, טליה רחל בת עליזה שמחה שינה מאשה</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ש-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>רונן פוקסברוימר</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>רונן ניסן בן יהודית וזוג' חיה שרה איידל בת חנה רייזא ,  גבריאל יצחק בן חיה שרה איידל וזוגתו חיה בת חנה , שלמה דוב בן חיה מעטל וזוגתו רחל אטה בת חיה שרה איידל , ב' אהרן מנחם בן חיה שרה איידל, משה יונה בן חיה שרה איידל, יוסף אליהו בן חיה שרה איידל, לנחת בריאות ושמחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ש-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>רחל סימס</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>שבע רחל בת שולמית שרל הצלחה בכל ,פרנסה נחת ובריאות ושמחה תמיד והגפ"ן, אברהם חיים טוביה בן מרים להצלחה וברכה בכל הענינים ופרנסה ברווח אמן .דבורה בת שבע רחל שתזכה להיות יראת שמים , לב טהור , ותשובה, ושתצליח מאוד ותזכה ללכת בדרך היהדות ושמירת תורה ומצוות , יהונתן חנן בן גילה שה' יערה עליו רוח טהרה ולב טהור וחזרה בתשובה שלמה, בנם יעקב אהרן בן דבורה לנחת דקדושה ממנו, נתנאל שי בן דבורה לבריאות ורפואה שלמה בקרוב אמן .לוי יצחק בן שבע רחל וזוג' הילה יפה בת ציונה, ב' יקותיאל יהודה בן הילה יפה, ב' עזריאל שלמה בן הילה יפה, ב' אביגיל ציונה בת הילה יפה, ב' עטרה פרומט בת הילה יפה,ב' אליענה ברכה בת הילה יפה, לנחת בריאות ברכה והצלחה בכל הענינים ,שולמית שרל בת ברכה גולדא להצלחה ופרנסה ושידוך שמחה והגפ"ן .משה בן זיסל לרפואה שלמה במהרה, יקותיאל יהודה בן חנה רחל לרפואה שלמה במהרה, דינה בת חוה לזיווג הגון בקרוב ממש, מיכאל פנחס בן פרחה לישועה גדולה וזיווג הגון בקרוב , אליענה רחל בת אלכסנדרה יעל לרפואה שלמה במהרה, חיה ברכה ליבא רחמה בת מניה רבקה לרפואה שלמה במהרה,  אברהם מרדכי בן דורית לישועה גדולה</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ש-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>רפאל טרייטעל</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>רפאל בן פערל וזוגתו יעל אילנה בת זלדה, מלכה רבקה בת יעל אילנה, עליזה פערל בת יעל אילנה, שושנה רחל בת יעל אילנה. צבי בן בינה, עדינה ברכה בת יעל אילנה, אריאלה רבקה בת עדינה ברכה, אהרון מרדכי בן עדינה ברכה, דניאל חיים בן עדינה ברכה, נפתלי צבי בן יעל אילנה, עטרה רחל בת דבורה שירה, אלישבע רינה בת עטרה רחל, יחיאל בנימין בן איידי עדינה, יוכבד מיכל בת יעל אילנה</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ש-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>שלמה ביסטריצקי</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>שלמה בן שולמית וזוג' אסתר רחל בת חנה מלכה, וכל משפחתו לברכה והצלחה בכל הענינים , נחת בריאות וכל טוב. מרדכי בן שולמית וכל משפחתו לברכה והצלחה בכל הענינים , נחת בריאות  וכל טוב לברכה. מנחם מענדל בן פייגא שיינדל וזוג' חנה מלכה בת שולמית לברכה והצלחה בכל הענינים ,  נחת בריאות וכל טוב</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ש-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>שלמה פערל</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>שלמה בן צביה, וזוגתו רות בת שיינדל,  יונתן בנימין בן רות . רבקה הענא בת אסתר ,משה בן רות . עטרה אסתר פערל בת רבקה איטה , דוד אהרן בן שרה רחל,  תמר אסתר בת רות, משה בן רות .</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ש-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>שמחה מילר</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ש-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>שמעון עשור</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>שמעון חננאל אליהו בן זלטה וזוג' טובה ניחא בת לאה, אביגיל פערל בת טובא ניחא, דניאל יוסף בן טובה ניחא להצלחה בכל הענינים, פרנסה בשפע וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ש-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>שמשון פינטער</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>שמשון בן טובה מרים וזוג' מרים שיינדל בת שלימה שרה, טובה בת מרים שיינדל, פנחס בן מרים שיינדל, גולדה רחל בת מרים שיינדל, חנה בת מרים שיינדל, מיכאל בן מרים שיינדל לבריאות איתנה ונחת מכל יוצ''ח ויזכה לתמוך בתורה וברכה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ש-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>שניאור מיטמן</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>אהרון דוד בן אלקה שפרינצה מיכלה לפרנסה בשפע והצלחה ובריאות איתנה ומזל לכל המשפחה.
+שניאור אליעזר בן מאשה לפרנסה בשפע הצלחה ובריאות איתנה ומזל לכל המשפחה
+מרים בת חיה זיסל לרפואה שלמה ובריאות איתנה והצלחה ומזל לכל המשפחה
+משה ישראל בן דבורה לפרנסה בשפע הצלחה ובריאות איתנה ומזל לכל המשפחה</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל ישז</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ש-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>אברהם חכמוביץ</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>אברהם בן חניא וזוגתו גולדא בת חיה לאה לברכה והצלחה שמירה ושלום  בית וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ש-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>אברהם מנחם גולדשטיין</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>אברהם בן אילנית שרה 
+תהילה בת סימה שמחה 
+לזרע של קיימא פרנסה ושלום בית</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ש-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>אברהם משה יוסף אירני</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>אברהם משה יוסף בן שיינדל וזוג' אביבה יעל שרון בת עדה שרה לברכה והצלחה בכל הענינים, פרנסה בשפע וכל טוב, עזריאל צבי בן אביבה יעל שרון, אשר נתנאל בן אביבה יעל שרון, פייגא בת מלכה</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ש-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>אברהם קורץ</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>משה אריה אהרון בן חנה יוטא להצלחה בישיבה ויוכל לקרא וללמוד טוב, אלישבע פריידל בת נחמה לזיווג הגון בקרוב ממש, לאה מלכה בת נחמה לזיווג הגון בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ש-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>אדי סחייאק</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>עזרא בן אסתר לפרנסה בשפע והצלחה בכל הענינים, מרים בת מזל לפרנסה בשפע והצלחה בכל הענינים, יחזקאל בן מרים, יעקב בן מרים, אסתר בת מרים, מזל בת מרים , נחת בריאות לפרנסה בשפע והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ש-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>אהובה אופק</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>אהובה ברכה בת גולדה דבורה לישועה והצלחה בכל הענינים וזיווג הגון בקרוב ממש אמן, שלמה בן יהודית ורד לרפואה שלמה ובריאות אמן רבקה שמעונה בת גולדה דבורה לחזרה בתשובה שלמה, כפיר בן יהודית לחזרה בתשובה שלמה, אלה בת רבקה שמעונה, שני בת רבקה שמעונה, בארי אהרן בן רבקה שמעונה- שיזכו לגדול בדרך התורה ויראת שמים טהורה אמן. איתן אבינועם בן אורלי להצלחה ולרוגע ושמחה פנימית, שמואל בן יהודית ורד לבריאות איתנה</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ש-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>אהרן טשרנס</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>שרונה בת רחל מלכה שלום בית בריאות הצלחה בחינוך הילדים וזיווגים הגונים ומנוחת הנפש, אהרון זאבי חיים בן רחל לאה שלום בית בריאות פרנסה ברווח הצלחה בחינוך הילדים וסייעתא דשמיא מנוחת הנפש, ציפורה עדינה בת שרונה לשלום בית בריאות איתנה ופרנסה ברווח ובשפע, חיה שרה בת שרונה שתזכה לחזור לחיי תורה ומצוות ובריאות איתנה וזיווג הגון</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ש-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>אווילין וולסין פיינגולד</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>יואל מאיר בן גלילה יוכבד וזוגתו אווילין מרים בת שרה , יעל אסתר בת אווילין מרים לנחת בריאות וברכה והצלחה בכל הענינים אמן</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ש-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>איגור הולשטין</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>יידל חיים בן רייזל לבריאות איתנה פרנסה ברווח אמונה וזש'' ק בבריאות, אסתר בת נעמי לבריאות איתנה לזש'ק בבריאות אמונה והצלחה בכל הענינים, רייזל בת פנינת לבריאות איתנה אמונה אושר והצלחה בכל הענינים, משה פרץ בן רייזל לבריאות איתנה ופרנסה ברווח ואמונה והצלחה בכל הענינים, ישראל בן מלכה להחלמה שלמה ובריאות איתנה וחיים בריאים וארוכים עם אמונה ואור והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ש-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>איתן זכריאן</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>אסתר בת עליזה לרפואה שלמה במהרה, לעלוי נשמת יוג'ין בן מיכאל ז"ל  ולעלוי נשמת רוזליה בת לייבל ע"ה</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ש-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>אלכסנדר בערגער</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>אלכסנדר בן סימא וזוגתו פערעל בת איטה לברכה והצלחה בכל הענינים, נחת  בריאות וכל טוב.  מאיר יהודה בן לאה וזוגתו מרים גאלדא בת רייזעל פערעל, ב' סימא, ב' אסתר, ב' יעקב צבי, ב' חנה רחל, ב' חיה שרה, ב' אהרן יחיאל זאב בן צביה וזוגתו איידל בת רייזעל פערעל, ב' הינדא עליזה, ב' סימא,  ב' יעקב משה, ב' פנחס אליהו  ישראל דב בן יהודית רבקה וזוגתו גיטל בת רייזעל פערעל , ב' סימא, ב' חנה, ב' יהודה  פנחס</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ש-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>ארי גולדבורד</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>בנימין אריה בן חנה רייזל פרנסה בשפע והצלחה , וזוגתו לאה חנה בת יעל, אלישבע  מלכה בת לאה חנה, אשר דוב בן לאה חנה</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ש-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>אריה לייב סימקין</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>אריה ליב יהודה בן אילנה 
+רבקה אלישבע בת יהודית 
+עטל רוז בת רבקה אלישבע 
+דוד אהרן בן רבקה אלישבע 
+ישעיה ישראל בן רבקה אלישבע 
+דינה רות בת רבקה אלישבע</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ש-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>ארקדי באבקנוב</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>יעל יפה בת אסתר לרפואה שלמה ובריאות איתנה</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ש-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>בנימין אקרמן</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>יחזקאל בנימין בן הענא וזוג' צינא מחלה בת שרה איידל לברכה והצלחה בעסקים על הצד היותר טוב ,ב' עדינה ברכה בת צינא מחלה, ב' יוסף, ב' טובא בת צינא מחלה לזיווג הגון בקרוב ממש ,ב' ישראל דוד ,ב' יהושע פאליק , ב' אברהם אנשיל, ב' מלכה  שלמה יעקב בן העניא להיות בשמחה תמיד</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ש-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>ברוך אמסעל</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>אליהו בן ליבא 
+רעדל בת גיטל 
+ברוך בן רעדל וזוג' הינדל חיה בת רבקה נוחה, בתם ליבא בת הינדל חיה, בנם יצחק אייזיק בן הינדל חיה.
+קלמן אליהו הכהן בן לאה אסתר 
+זוגתו אסתר בת הינדל חיה 
+ב: אהובה רות בת אסתר | יצחק אייזיק הכהן בן אסתר.
+נחמן דוד מאיר בן איידל מלכה 
+זוגתו נחמה דבורה בת הינדל חיה 
+ב: יצחק אייזיק בן נחמה דבורה | שמואל חיים בן נחמה דבורה.
+יצחק רחל בן רחל ציפורה 
+זוגתו פערל בת הינדל חיה 
+ב: אביגיל אסתר.
+שיזכו להרחבת הדעת, ברכה, פרנסה בנקל, הצלחה בכל העניינים.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ש-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>דוד הופמן</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>אברהם דוד בן הנא חיה להצלחה בתורה ויר"ש ופרנסה ברווח, וזוג' עטא חי בת שרה לבריאות טובה ואיתנה ולהתקרב להשי"ת, ב' דניאלה לאה בת עטא חי לשלום בית והצלחה בגידול ילדיה, ב' אהרן משה בן עטא חי לשלום בית והצלחה וצמיחה רוחנית, ב' יהושע יצחק בן עטא חי לזיווג הגון והצלחה בלימוד ורוחניות, ב' אריאל בנימין בן עטא חי - שיצליח בישראל והצלחה גדולה בלימוד וברוחניות.  ישראל יעקב בן הנא חיה לשלום בית ובריאות איתנה והצלחה בכל השתדלותו, מיכאל מרדכי בן הנא חיה לשלום בית ובריאות איתנה והצלחה בכל השתדלותו, העשיל וולף בן שרה מנוחה  שרה רבקה בת תמימה לרפואה שלמה במהרה, מנחם משה בן דבורה וולף דניאל בן שרה, יהודה הערש בן דניאלה לאה, יהודה הערש, שמואל יוסף בן דניאלה לאה, שרה בת חנה, שמעון גרשון בן דניאלה לאה, בעריש שמעון בן שרה, מאיר זאב בן הניה, בלומא מרים בת שרה- לברכה והצלחה ובריאות איתנה וכל טוב אמן.  בלימה מרים בת שרה חנה דבורה בת ביילא, שמחה בת גוטא, נחמן בן רבקה, מרדכי בן טובא רחל, יונטון משה בן הנשה, שושנה בת ביילא, שושנה מינדל בת גולדה, חווה הנה חנה בת פנינה יוכבד, שרה רבקה בת תמימה מיכל, חיה רחל בת תמימה מיכל</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ש-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>דוד סויבלמן</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>דוד נחמן בן אלישבע גזונט פרנסה ותורה, וזוג' רויזא שושנה בת מרגלית ,ב' אביבה בת רויזא שושנה ,ב' יצחק בן רויזא שושנה ,ב' תמר בת רויזא שושנה , ב' מינדל חנה בת רויזא שושנה, ב' לאה בת רויזא שושנה יוסף דניאל אליעזר בן אלישבע לנחת דקדושה מהילדים</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ש-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>זאב טנדלר</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>זאב בנימין בן מאשא לאה לבריאות, נחת מהילדים ופרנסה ברווח, וס״ד בעבודת הקב״ה וגם בכל עשקיו שרה חיה פייגא בת בריינדל הינדא לבריאות, נחת מהילדים ופרנסה ברווח,  זיסא בתיה בת בריינדל הינדא לזיווג הגון בקרוב ממש, שמואל יצחק אריה בן שרה חיה פייגא לבריאות והצלחה בלימודים,  שפרה בת שרה חיה פייגא לבריאות והצלחה בלימודים, תהילה רחל בת שרה חיה פייגא לבריאות והצלחה בלימודים.  אסתר בתיה בת שרה חיה פייגא לבריאות והצלחה בלימודים,   יוסף יהודה בן שרה חיה פייגא לבריאות והצלחה בלימודים,  הלל בן שפרה מאשא לאה בת בילה וכל משפחותיהם לבריאות, נחת מהילדים  ופרנסה ברווח יחיאל מיכל שלום בן מרים בריינדל הינא בת מלכה וכל משפחותיהם לבריאות, נחת מהילדים  ופרנסה ברווח</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ש-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>חיים יעקב קורלנד</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>חיים יעקב בן חיה רייזל, אשר זעליג בן איטא ליראת שמים, נחמה קריינא בת איטא לזיווג הגון בקרוב ממש ,איטא בת רחל להצלחה בכל הענינים ברו"ג אמן ואמן .אליעזר ליפא בן חיה רייזעל לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ש-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>חיים פסח ווינשניידר</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>חיים פסח בן שרה לברכה והצלחה ופרנסה בשפע ורווח אמן, חוה בת חנה לרפואה שלמה במהרה לבריאות איתנה וכל טוב אמן. לוי יוסף בן עליזה מלכה להצלחה בלימודים בישיבה ויגדל בתורה ויראת שמים  טהורה לנחת הוריו</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ש-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>יהושע טעפפר</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>יהושע בן מינדל
+רחל לאה בת שולמית
+הוריהם:
+יהושע בן רחל חיה
+וילדיהם:
+משה שמואל בן רחל לאה
+חנה איטא רחל בת שושנה רויזאל
+שאול בן חנה איטא רחל
+ישראל צבי בן חנה איטא רחל
+מינדעל ברכה בת חנה איטא רחל
+רבקה בת חנה איטא רחל
+יצחק ישעיה בן חנה איטא רחל
+שולמית פעסיא בת חנה איטא רחל
+מנחם שלום בן חנה איטא רחל
+אברהם שמשון בן רחל לאה
+חנה רחל בת אליזה זלדה
+מיכאל יעקב בן חנה רחל
+דניאל אהרן בן חנה רחל
+אביגיל ברכה בת חנה רחל
+רפאל ישעיה בת חנה רחל
+נתן יחזקאל בן רחל לאה
+אלטא חנה טויבא בת דבורה זיסעל
+מרים ברכה בת אלטא חנה טויבא
+מינדעל ליבא בת אלטא חנה טויבא
+שושנה מלכה בת אלטא חנה טויבא
+אלימלך אשר בן רבקה
+אסתר חוה בת רחל לאה
+מינדל ברכה בת אסתר חוה
+אברהם בן אסתר חוה
+ישעיה בן אסתר חוה
+שולמית בת אסתר חוה
+משה יעקב בן אסתר חוה
+רויזה מלכה חיה בת אסתר חוה
+משה יוסף בן שושנה
+הדסה ברכה בת רחל לאה</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ש-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>יהושע מאיר דויטש</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>יהושע מאיר בן רחל להצלחה בבניית הבניין הקדוש והכולל חצות ובכל הענינים ולהתקרב לרבינו הקדוש וזוגתו בלהה בת ציפורה לבריאות ואושר והצלחה וכל טוב אמן, חנה בת בלהה לזיווג הגון בקרוב ממש, יעקב משה בן רחל לאה וזוגתו שפרה בת בלהה להתבקרך בזרעא חיא וקיימא במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ש-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>יהושע משה שילד</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>אלישבע מרים בת אילנה רחל לזש"ק, יהושע משה בן אילנה רחל לזיווג הגון, יעל ברכה בת אילנה רחל לזיווג הגון</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ש-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>יוסף גולדבורד</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>יוסף חיים בן חנה רייזל וזוג' חיה שרה מלכה בת לאה, ב' ברוך, ב' מיכל מרים בת חיה שרה מלכה לרפואה שלמה ובריאות, ב' אביגיל בת חיה שרה מלכה, ב' דבורה בת חיה שרה מלכה, לברכה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ש-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>יוסף דוב קופרוואסר</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>יוסף דוב בן שרה ליבא לרפו"ש, וזוג' רחל רבקה בת חיה לאה לרפואה שלמה במהרה, ב' שלמה בן רחל רבקה, ב' מלכה שרל בת רחל רבקה, ב' דוד בן רחל רבקה , ב' אלטר יעקב בן רחל רבקה, ב' פייגא מרים בת רחל רבקה לברכה והצלחה בכל הענינים, בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ש-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>יוסף דייטש</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>יוסף בן אסתר פנינה בת גיטל גולדה, בניהם- ברוך בן פנינה, משה דב בן פנינה לפרנסה, בריאות, שלום בית, שפע והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ש-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>יוסף לטיניק</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>יוסף פנחס בן מרים יוכבד לבריאות הגוף והנפש, וזוג' נחמה בת יהודית הינדל, לפרנסה בשפע ורווח , בריאות שמחה נחת מהילדים , משה יהושע בן נחמה, אברהם בנימין בן נחמה , יצחק אליהו בן נחמה, לבריאות וכל טוב</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ש-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>יעקב טוביה גולדשטיין</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>יעקב טוביה בן חוה וזוג' דבורה בת שרה אמנו, חיים יהושע בן דבורה ומשפ' , משה דוד בן דבורה ומשפ', אברהם מנחם בן דבורה ומשפ' , הינדא בת דבורה ובעלה משה יונה בן עליזה נחמה ומשפ', נחום מאיר בן דבורה ומשפ', שלמה יוסף בן דבורה, מרים בת דבורה ובעלה יוסף משה בן בת שבע, לנחת בריאות ושמחה, שלום בית, זרעא חיא וקיימא ופרנסה טובה בשפע וברווח גדול והצלחה וכל טוב אמן. במיוחד, שלמה  יוסף בן דבורה לזיווג הגון בקרוב בעזרת השם.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ש-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>יעקב נאבעל</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>יעקב יצחק בן אסתר רייזל וזוג' ציפורה בת חוה ביילא , ב' מלכה בלומא בת ציפורה , ב' חיה רחל בת ציפורה, ב' גיטל בת ציפורה , ב' יוכבד בת ציפורה , ב' שלמה בן ציפורה , ב' שמואל עוזיאל בן ציפורה אושר ועושר אמן , ב' יוסף בן ציפורה , - לברכה והצלחה ובריאות ושמחה נפתלי הירץ בן אסתר גיטל וזוג' אסתר רייזל בת חנה ביילא וכל משפחתם</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ש-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>יעקב פרידמן</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>יעקב יהונתן בן זהבה לברכה והצלחה ופרנסה בשפע</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ש-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>יפה ענגלאנדר</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>יוסף יצחק בן חיה פרימיט וזוגתו יפה רחל בת מלכה פערל , נעמי בת יפה רחל לברכה והצלחה ,מרים חיה בת חניתה לרפואה שלמה ושידוך הגון, טובה גיטל אסתר בת מרים לשידוך הגון</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ש-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>יצחק מוגרבי</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>יצחק בן רחל לברכה והצלחה ברוחניות וחינוך הבנים פרנסה בשפע וברווח להצלחת הבנים, שרה בת אסתר חיה לברכה והצלחה לרוחניות ובריאות איתנה, יהודה בן שרה לברכה והצלחה ברוחניות תורה ובריאות איתנה, בת שבע בת שרה לברכה והצלחה ברוחניות ובריאות איתנה</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ש-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>יצחק מרדכי פאללאק</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>יצחק מרדכי בן רבקה פייגא וזוג' לאה יהודית בת שיינדל לישוב הדעת ושמחה תמיד מתוך בריאות הגוף והנפש ויראו הרבה נחת מכל יוצאי חלציהם, ויזכו לגדלם לתורה ויר"ש ומידות טובות ותמיד יאיר להם המזל בעז"ה , ב' בלומא בת לאה יהודית שיעלה הזיווג יפה יפה, ב' מנחם מאניס בן לאה יהודית לזיווג הגון בקרוב, ב' דוד מאיר בן לאה יהודית לזיווג הגון בקרוב, ב' יעקב בן לאה יהודית שיצליח בלימודים בישיבה וילמד תורה בהתמדה, ויהיה לו חברים טובים וחשקת התורה, ב' חיים בן לאה יהודית שיצליח מאוד בלימודים בחיידר , ב' אברהם יהודה בן לאה יהודית שיצליח בלימודים בחיידר , ב' משה צבי בן לאה יהודית, ב' חיה טויבא בת לאה יהודית, וכל המשפחה - להצלחה ונחת ופרנסה ברווח ולעבוד את ה' בשמחה , והרחבת הדעת אמן.ישראל אלעזר בן חיה טויבא וזוג' שיינדל בת ציפורה לבריאות והצלחה ופרנסה וכל טוב, אלטר שמעון יחזקאל בן רחל חנה לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ש-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>לאה מנדלסון</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>לאה בת חנה להצלחה בכל הענינים פרנסה ברווח ושלום אמן. שיינדל רחל בת לאה לזיווג הגון בקרוב ממש.</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ש-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>ליאורה הירש</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>גיטל עליזה בת ליאורה זהבה לזיווג הגון בקרוב ממש חיש קל מהרה אמן. ליאורה זהבה בת חנה בילא רבקה לבריאות איתנה והצלחה וכל טוב, מיכל בת ליאורה זהבה לזיווג הגון בקרוב ממש חיש קל מהרה אמן, חנה בילא רבקה בת חיה שרה לרפואה שלמה, אליהו בן ליאורה זהבה ליראת שמים ולב טהור וללכת בדרך התורה תמיד</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ש-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>לינדה מאגאזינטש</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>יוסף משה בן לינדה זוהרה שיחזור בתשובה שלמה ויזכה ללמוד תורה והוריו יראו ממנו נחת דקדושה ולבריאות הנפש אמן, יונתן חיים בן לינדה זוהרה פרנסה בשפע ורווח, שיהיה בשלום עם הוריו שיחיו , דוד רפאל בן לינדה זוהרה שיזכה לטהרת הלב ויחזור בתשובה וזוג' שיינא פערל בת עלקא גיטל לרפו"ש במהרה, יוני יוסי בן אליסה לפרנסה בשפע ורווח, רבקה בת לינדה זוהרה להצלחה בכל הענינים אמן ,לינדה זוהרא בת איבן לפרנסה ברווח ושתמצא עבודה טובה מאוד במהרה ולהצלחה בכל הענינים ונחת מהילדים ובריאות ושמחה וכל טוב</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ש-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>מאיר אייזנשטאט</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>מאיר שלום דוב בן חיה לפרנסה בשפע ורווח, וכל הקמים עליו לרעה תופר עצתם, וזוגתו סימא בת חיה רבקה, אליעזר בן סימא, חיים צבי בן סימא, משה יוסף נחמיה בן סימא, בנימין אריה בן סימא, לברכה והצלחה בכל הענינים, בריאות פרנסה ונחת</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ש-0110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>מאיר זילבר</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>מאיר יעקב בן שיינדל וזוג' רחל ליבא בת חנה אסתר,ב' פערל דינה בת רחל ליבא שרה בת רחל ליבא , ב' חיים משה בן רחל ליבא , ב' נעמי פעסיל בת רחל ליבא , ב' גיטל בת רחל ליבא, ב'  שרגא פייבל בן גיטל ומשפחתו, דוד בן חיה פייגא ומשפחתו. שמואל מאיר בן יוכבד באשע להצלחה, רבקה בת יוכבד באשע להצלחה</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ש-0111</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>מיכאל רומי</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>יאן שי בן רוזלין חנה לחזרה בתשובה ופרנסה בשפע וזיווג הגון בקרוב ממש, אליהו בן דבורה להצלחה ושידוך הגון בקרוב ממש, וחזרה בתשובה שלמה, רוזלין חנה בת באלדה לרפואה שלמה ואריכות ימים, מיכאל בן רוזלין חנה להצלחה בלימוד התורה וזוג' חנה בת דבורה להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ש-0112</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>משה דוד פרידלנדר</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>משה דוד בן זלאטע לבריאות איתנה ונחת וחיים ארוכים ופרנסה טובה , סערל שרית בת מלכה לבריאות איתנה וחיים ארוכים ונחת והרחבת הדעת , אליעזר זוסמאן בן סערל שרית וזוג' מרים בת אסתר לשלום בית לברכה והצלחה ושמחת החיים, חיה פעסל לאה בת סערל שרית שהזיווג יעלה יפה יפה  , יוסף בן סערל שרית לבריאות ואהבת תורה ושמחת חיים</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ש-0113</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>משה חיים פישער</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>משה חיים בן רייזל, רבקה בילא בת נחמה, ישי בן רבקה בילא, חי בת רבקה בילא, הענדל שרה בת רבקה בילא, צבי בן רבקה בילא, יעקב דוד בן רבקה בילא, משולם זאב בן רבקה בילא, שרה העניא בת אסתר חנה, יוסף יוחנן בן חי מרים לברכה והצלחה בכל הענינים שפע וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ש-0114</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>נפתלי בוכינגר</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>נפתלי אשר בן מאטל וזוג' שרה בת הינדא וכל משפחתו לברכה והצלחה וכל טוב אמן , רייזל בת שרה לשידוך הגון בקרוב ממש וברכה והצלחה וסייעתא דשמיא , הניא בת שרה להצלחה</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ש-0115</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>נתנאל ציון</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>נתנאל בן מלכה לצאת מכל החובות ושיהיה לו שפע גדול של פרנסה וכל טוב אמן , יוכבד בת ג'קלין שרה לברכה והצלחה וסייעתא דשמיא</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ש-0116</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>עדן בידאני</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>יובל בן בת חן להצלחה בכל מעשי ידיו ושיהיה לו בית משלו שיוכל לקיים מצוות יישוב ארץ ישראל, נועם בן עדן שילך תמיד בדרך הנכונה של לימוד תורה וקיום מצוות ויתפלל 3 פעמים ביום בבית הכנסת, איילת בת עדן שתראה את החברות שלה פורחת ושתעבור את שנות העשרה שלה בשלום למרות העליות והמורדות, עדן בת שרה אמנו לפרנסה ברווח ובשפע והצלחה גדולה בעסק והצלחה בכל הענינים אמן</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ש-0117</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>עזריאלה יפה</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>זלמן בן גיטל וזוגתו עזריאלה בת מרגלית לברכה והצלחה בכל הענינים ,  פרנסה בשפע ונחת ובריאות.  משה בן אריה לייב וזוגתו שרה בת עזריאלה להצלחה בכל הענינים, וילדיהם סימה יהודית בת שרה, חנה אסתר בת שרה , שיינא רחל בת שרה, תהילה בת שרה . יונה בן גדליה, משה וזוגתו אילנה בת עזריאלה לברכה והצלחה, וילדיהם עזרא בן אילנה, דניאלה בת אילנה, נח בן אילנה. אליהו מרדכי בן עזריאלה וזוגתו שירה בת מזל לברכה והצלחה, ליאורה בת שירה , מרגלית בת אסתר לבריאות איתנה ושלום בית ואריכות ימים בשמחה.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ש-0118</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>ריסעל ניימארק</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>זלמן מרדכי מאיר בן שיינדל פייגא וזוג' ריסעל פריידא בת חיה שרה וכל משפחתם וכל יוצאי חלציהם לברכה והצלחה בכל הענינים,שלום בית, בריאות ונחת מכל הילדים ופרנסה ברווח. ירוחם פישעל אריה בן חיה פריידאעליזה וזוג' מרים גולדא בת ריסעל פריידא, חיים ישראל בן מרים גולדא ,ב' אהרן בן מרים גולדא, ב' יהודה בן מרים גולדא, ב' שיינדל פייגא בת מרים גולדא, ב' אהובה בת מרים גולדא, ב' דוד נחמיה בן מרים גולדא, בריאות אריכות ימים ושנים טובות, נחת ופרנסה, ב' שרה עטל בת מרים גאלדא, ב' רחל בת מרים גאלדא,  אברהם אליעזר צבי בן ריסעל פריידא וזוג' נעמי ברכה בת רות מרים , ב' שרה רבקה בת נעמי ברכה, ב' נועה בת נעמי ברכה, ב' צביה בת נעמי ברכה , ב' דוד נחמיה בן נעמי ברכה , לברכה הצלחה בכל הענינים , בריאות ואריכות ימים ושנים טובות, שלום בית ופרנסה אמן</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ש-0119</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>רני מנדל</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>ירחמיאל אברהם רחביה בן דבורה לרפואה שלמה , בריאות הגוף והנפש, פרנסה בשפע ורווח הצלחה בכל הענינים לוי יצחק בן דבורה</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ש-0120</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>שלום אנטין</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>חיים שלום פייבל בן שמחה איקאה וזוגתו רבקה בת מינדל,   שושנה ליבא בת רבקה לברכה והצלחה בכל הענינים ופרנסה בשפע ורווח וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ש-0121</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>שלמה קנופף</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>שלמה בן אסתר וזוגתו מיכל רות בת בארי ציפורה לבריאות נחת,פרנסה טובה ולזכות לעלות לישראל בקרוב ממש. 
+רצון בן הרצל  וזוג' שירה יפעת בת מיכל רות וכל יוצאי חלציהם
+אריאל ברוך בן מיכל רות לזיווג הגון בקרוב ממש 
+יהודה זאב יאיר בן מיכל רות וזוג' יהודית בת אילנה גולדה וכל יוצאי חלציהם 
+ליאת ברכה בת מיכל רות לרפואה שלימה בגוף ונפש.
+נעם שלום בן מיכל רות וזוג' יוכבד בת לאה מלי-ה וכל יוצאי חלציהם  
+בריאות והצלחה בכל אמן .</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ש-0122</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>שמואל זאנטעג</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>שמואל שלמה בן רחל וזוגתו דבורה הענא בת שרה ביילא לברכה והצלחה בכל  הענינים. אלון נתנאל בן אסתר מלכה וזוגתו שושנה איידל בת דבורה הענא, ב' אברהם יעקב לרפואה שלמה, ב' משה, ב' יואל אליהו . יחיאל יהודה בן נחמה וזוגתו יהודית חנה בת דבורה הענא ב' מרים, ב' אברהם, ב' חיים צבי . יואל פנחס בן דבורה הענא שהזיווג יעלה יפה יפה עם הכלה לאה בת עליזה פריידא</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ש-0123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>שמואל יעקובי</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>יששכר דב בן מרישה מרים פריידל לרפואה שלימה במהרה וייצא מהמחלה מהר אמן, יעקב חיים בן שיינדל לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ש-0124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>שמחה ניימארק</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>שמחה שלום משה בן ריסעל פריידא וזוג' זיסל פייגא ברכה בת חיה לאה הצלחה בכל הענינים ופרנסה ברווח, ב' יעקב שלמה בן זיסל פייגא ברכה ,ב' יוסף יצחק בן זיסל פייגא ברכה, ב' שיינדל פעסיל בת זיסל פייגא ברכה, ב' שרה מלכה בת זיסל פייגא ברכה</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ש-0125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>שמשון יוסף פוקס</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>שמשון יוסף בן אסתר רבקה לברכה והצלחה בכל הענינים, שלום בית , פרנסה ברווח, נחת מהילדים וישוב הדעת וכל טוב, וזוגתו ישראלה בת צביה לאה לברכה והצלחה בכל הענינים, בריאות ונחת מהילדים, שלווה וישוב הדעת וכל טוב . בניהם - שמואל יהודה בן ישראלה, בנימין עזרא בן ישראלה , דניאל זאב בן ישראלה . אסתר רבקה בת רייזל – לבריאות טובה ואושר , ולגדול תלמידי חכמים . שיינדל לרפואה שלמה, ברכה והצלחה בכל הענינים, וכל טוב</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ש-0126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>שפרה גוזף</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>ציון בן סעדה לרפואה שלמה במהרה ובריאות איתנה אמן, שפרה בת ברכה לרפואה שלימה רפואת הנפש ורפואת הגוף בריאות ואריכות ימים שנים טובות עד מאה ועשרים שנה ,שלום בית , פרנסה בשפע וכל טוב, אביעד בן דבורה וזוג' שרה אביגיל בת שפרה  לברכה והצלחה וזש"ק וכל טוב, בן ציון שלמה בן שפרה להצלחה וזיווג הגון בקרוב ממש, יהודה יחיאל בן שפרה לזיווג הגון בקרוב ממש, אברהם מנחם בן שפרה לזיווג הגון בקרוב ליראת שמים טהורה, דבורה מרים בת שפרה לזיווג הגון בקרוב ממש, אלישבע ברכה בת שפרה לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_101</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל;קוויטל 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ש-0127</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>אבא קלוק</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>אברהם אבא בן אסתר דבורה וזוג' פריידא גיטל בת ליבא, בנם בנימין אריה, בנם חיים יצחק להצלחה בכל הענינים אמן</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>ש-0128</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>אבי ליפשיץ</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>אברהם מנחם בן חנה וזוג' שרה ביילא בת מלכה ,להצלחה בכל הענינים, בנם שילה נתנאל בן שרה ביילא לגדול בתורה ויראת שמים, שלוה גולדא מיכל בת שרה ביילא לרפואה שלמה. לאה בת שפרה לרפואה שלמה בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ש-0129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>אברהם דוואק</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>אברהם בן סלחה שולמית להצלחה בעסק שלו ולב טהור ולשלם את כל החובות. חיים  ארוכים ובריאות. הצלחה בפרנסה. עזרא בן חנה לרפואה שלמה במהרה ושמחת חיים. שרה בת חסידה לרפואה שלמה, רבי אמנון בן רומיה להצלחה ולהחזיר בתשובה עוד ועוד, תמר רחל בת סלחה שולמית בריאות איתנה והצלחה בכל הענינים, זיווג הגון. שאול בן גילה לרפואה שלמה. נטלי שמחה בת אודרי חנה לרפואה שלמה. יצחק יהודה בן חיה שרה גיטל לשלום בית והצלחה בעבודת ה' ובעסק. אסתר שרה לאה בת רחל בריאות ואושר. . אמילי שרה בת סלחה שולמית זיווג הגון, בריאות</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ש-0130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>אברהם דווייק</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>אהרון יואל בן רות: לברכה והצלחה בעסקים וחיים ארוכים
+שלמה בן סאלחה שולמית סילבנה: לרפואה שלמה והצלחה בקבלתו לאוהל ברוקלין
+יצחק בן לאה גיטל: להצלחה בתשלום כל חובותיו והלוואותיו בחודש סיוון</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>ש-0131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>אברהם וויספיש</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>אברהם אלחנן בן נחמה לברכה והצלחה וסייעתא דשמיא , פרנסה ברווח ועשירות, הצלחה גדולה בעסק ובכל הענינים אמן</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>ש-0132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>אברהם וינשטוק</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>מאיר חנוך בן דרעיזל לאה וזוג' שרה בת רייזל ייטא, שלום בן דרעזיל לאה וזוג' רבקה בת מרים אביבה,שרה חיה בת רבקה פרידא לזיווג הגון, רבקה פריידא בת דרעזיל לאה לרפואה שלמה לישועה גדולה ושלמה , שרה בריינדל בת דרעיזל לאה ויצחק בן לאה שיעלה הזיווג יפה נחת ושלום בת עד 120 בת חיה לזרע של קיימא, אלעזר בן דרעזיל לאה וזוג' רחל , ישראל משה בן דרעזיל לאה וזוג' מרים יענטא בת חיה רבקה , חיה יוטא בת פריידל אסתר שתחזור בתשובה, חנה בת אסתר לרפואה שלמה, חוה בת ליפשא אהובה לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ש-0133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>אברהם פלורנס - קווויטל</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>אברהם צבי בן פריידא רייזא לפרנסה ברווח והצלחה בעסק החדש ויזכה להשתחרר ולצאת מהאסירות בברכת מתיר אסורים, וזוג' בלומא בת חיה פעשא, מיכל בת בלומא, יעקב בן בלומא, שמואל דוד בן בלומא, בנימין בן בלומא, אריה לייב בן בלומא, אהרן בן בלומא, לברכה והצלחה בכל הענינים, בריאות ואריכות ימים וכל טוב אמן, מרים בת בלומה לרפואה שלמה במהרה אמן יוסף יצחק בן שושנה דבורה וזוגתו שרה לאה בת יעל להתברך בזרע של קיימא במהרה, אהרן יואל בן מיראלה, לרפואה שלמה, רפאל יעקב בן ציפורה לרפואה שלמה, עקיבא בן פייגא לפרנסה ברווח, שמעון בן פרחיה לפרנסה ברווח, גרשון מענדל בן אסתר מלכה לברכה והצלחה, משה בן חיה וזוג' רחל בת גיטל - להתברך בזש"ק</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>ש-0134</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>אברהם שרייבר</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>אשר זעליג בן הדסה טויבא להצלחה בישיבה, שימצא עבודה חדשה בזמן, לרפואה שלמה במהרה. הדסה טויבא בת שרה שיינדל לרפואה שלמה במהרה בגב והפריצת דיסק יתרפא לגמרי אמן , בריאות ילדיה. גבריאל משה אברהם בן זלטה לרפואה שלמה ובריאות, הדסה טובה בת שרה שיינדל לבריאות הילדים. אברהם משה בן רחל מיכל להצלחה ובריאות עם כל המשפחה שיחיו, פרנסה טובה, ברכה עבור כל ילדיו וסובביו.</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ש-0135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>אדם לורברט</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>אדם אברהם משה בן אטה נחמה וזוג' שרה צפורה בת דבורה חנה, בתם שירה רבקה בת שרה ציפורה , בנם זהוב יעקב בן שרה ציפורה , בתם אסתר אביבה בת שרה ציפורה, נחום אריה בן שרה ציפורה</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ש-0136</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>אוהד גמליאל</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>רעות בת תקווה לבריאות והריון קל בלי שום בעיות ולידה בניקל וולד בריא ושלם, אוהד בן דורית לברכה והצלחה , איתמר בן רעות לבריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ש-0137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>אוהד שמואלביץ</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>אוהד בן חיה ובריאות והצלחה בכל הענינים ולשמחה בקדושה ובשבת אמן</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ש-0138</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>אורי קאהן</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>אורי ישראל בן שרה מלכה להצלחה ופרנסה ברווח וזיווג הגון בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>ש-0139</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>אייזיק שבות</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>יצחק בן רות להצלחה בכל הענינים ופרנסה ועשירות גדולה וזוגתו לאה בת אילה לברכה והצלחה בכל הענינים, וילדיהם עזרא בת לאה , רות בת לאה, אילה בת לאה , לנחת בריאות ושמחה וכל טוב אמן ברוך בן אילה וזוג' סילה בת לאה להתברך בזרעא חיא וקיימא אמןזאב בן רות לזיווג הגון בקרוב ממש,</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>ש-0140</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>אילנה סימקין</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>חיים קאפל בן צביה מאשע וזוג' נעמי בת אילנה להצלחה ופרנסה ברווח , ב' אסתר בת נעמי , ב' פסח בן נעמי , ב' יצחק בן נעמי , אילנה בת דינה להצלחה בכל הענינים. ישראל ראובן בן אילנה לזיווג הגון בקרוב ממש ועליה בתורה ויר"ש והצלחה</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ש-0141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>אלחנן נפתלי מאשער</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>אלחנן נפתלי בן שיינדל לפרנסה בשפע ורווח ורפוא שלמה ובריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>ש-0142</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>אלי וויינפעלד</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>בן ציון אליהו בן מרגלא צביה יהודית בת אסתר יוטל, שפרה בת יהודית לזיווג הגון בקרוב, סאשה רחל בת יהודית, ניחא רבקה בת יהודית, ישראל אברהם בן יהודית לברכה והצלחה וכל טוב</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>ש-0143</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>אליהו ביים</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>אליהו בן מאשע וזוג' רבקה בריינדל בת מלכה, ב' אסתר בת רבקה בריינדל , ב' שלום מאיר בן רבקה בריינדל, ב' רויזא שושנה בת רבקה בריינדל, ב' חיים שמעון בן רבקה בריינדל, ב' תמר בת רבקה בריינדל - לברכה והצלחה בכל הענינים, פרנסה בשפע ורווח , נחת וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>ש-0144</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>אליעזר גרוסמן</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>אליעזר בן מאניה אמונה ושלום בית נחת מהילדים ופרנסה בשפע וברווח, מרים בת חוה שלום בית בריאות איתנה נחת מהילדים וזיווג,שושנה בת מרים לבריאות איתנה ושמחה וזיווג הגון, דוד מתיתיהו בן מרים אמונה בריאות איתנה שמחה והצלחה. מיעאל בן בנימין וחיה שרה לשמירה והצלחה גדולה בכל הענינים.  מיכאל בן חיה שרה שיחזור בריא ושלם מהמלחמה בעזה</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>ש-0145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>אליעזר שמואל ווינגרדן</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>אליעזר שמואל בן חוה ברכה לפרנסה בשפע ורווח, וזוג' לאה בת שושנה, גיטא בת לאה, אהרן מנחם בן לאה , חנה מרים בת לאה, בתיה בת לאה, זהבה גולדה בת לאה, אריה לייב בן לאה, אשר בן לאה, בנימין צבי בן לאה, אסתר בת לאה לברכה והצלחה בריאות וכל טוב אמן. שאול ישראל בן פערל מלכה לבריאות</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>ש-0146</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr"/>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>אמי פרלוב</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>ירחמיאל הלל בן בתיה וזוג' אדל בת מרים לברכה והצלחה בכל הענינים ופרנסה ברווח ובשפע ונחת ובריאות וכל טוב , ב' מנחם צבי בן אדל לרפואה שלמה במהרה , ב' ראובן אריה בן אדל וזוגתו שושנה בת רחל, ב' מרדכי בן שושנה, אברהם יהודה בן אדל - לברכה והצלחה בכל הענינים אמן.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>ש-0147</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>אסתר באום</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>משה אליעזר יוסף בן פרימט לרפואה שלמה 
+ישראל מיכאל בן אסתר מלכה לזיווג הגון בקרוב</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>ש-0148</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr"/>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>אסתר בוים</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>ישראל מיכאל בן אסתר מלכה לזיווג הגון בקרוב ממש, אסתר מלכה בת בת ציון לפרנסה ברווח ושלום בית, משה אליעזר יוסף בן פרימט בריאות בגוף ובנפש, מרדכי בן אסתר מלכה לבריאות הנפש ושלום בית, חיים בן בת ציון לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>ש-0149</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>אסתר וויין</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>לעילוי נשמת רייזל בת דב</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>ש-0150</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>אריה ערן שמואל</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>אסתר אריאלה בת רבקה לזיווג הגון בקרוב ממש, יואל שרון בן רבקה וזוג' פנינה יפה בת שולמית חנה להתברך בזרעא חיא וקיימא בקרוב ממש. אריה ערן בן רבקה וזוג' שרה מירב רחל בת עדנה , יעקב איתן בן שרה מירב רחל לנחת ובריאות, בנם גבריאל יוסף בן שרה מירב רחל לנחת ובריאות, אביגיל רבקה בת שרה מירב רחל לנחת ובריאות, עדינה לאה בת שרה מירב רחל - לנחת בריאות ברכה והצלחה בכל הענינים ופרנסה בשפע ויזכו לקנות דירה טובה בירושלים, מיכאל בן ישועה לאריכות ימים ושנים טובות</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>ש-0151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>אריק דזמשידוף</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>אריק דז'משידוף  אהרון בן לאה רבקה הצלחה בלימוד התורה, חברים טובים, חיים בריאים ומאושרים ,רפואה שלמה מהחרדות וילך תמיד בדרך התורה לעבודת השם, שלמה ישראל בן לאה רבקה הצלחה בלימוד התורה, חברים טובים חיים בריאים ומאושרים רפואה שלמה מהחרדות וילך תמיד בדרך הראויה לעבודת השם, אביגיל מרים בת לאה רבקה להצלחה בהכל, מידות טובות זיווג הגון עם צדיק ותזכה ללכת בדרך הראויה לעבודת השם, יוסף יהודה בן לאה רבקה שיזכה ללמוד תורה ויהיה לו חברים טובים, בריאות איתנה וחיים מאושרים, משה בן שושנה לבריאות איתנה ורפואה שלמה, אברהם בן שושנה לזיווג הגון בקרוב.   לאה רבקה בת שושנה יצחק בן מרים לחיים בריאים ושלום בית תורה ומצוות ורפואה ופרנסה טובה ושיזכו לראות את ילדיהם גדלים התורה ויראת שמים. שרה בת מרים להתברך בזש"ק במהרה, יחזקאל לוי בן אילנה להתברך בזש"ק במהרה.</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ש-0152</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>ביילא הערש</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>שולמית בת חיה שרה לזיווג הגון בקרוב, מיכל בת חיה שרה לזיווג הגון בקרוב, אביגיל בת חיה שרה לזיווג הגון בקרוב לאה בת חיה שרה לזיווג הגון בקרוב</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ש-0153</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>בערי גולדגראב</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>בנימין שלמה בן רחל לאה לברכה והצלחה אמן אהבה רבקה בת יהודית עלישה לרפואה שלמה רחל לאה בת יטא לרפואה שלמה במהרה אמן אבא ישראל צבי בן יהודית עלישה לברכה והצלחה אמן אשר אליעזר בן חנה רבקה לרפואה שלמה במהרה</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ש-0154</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>בערי שכטר</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>יששכר בעריש בן יהודית וזוג' פייגא בת אסתר מירל לפרנסה ברווח ובשפע ושלום בית ורפואה שלמה, מנחם מענדל בן פיגא, שמואל צבי בן פיגא, אברהם בן פיגא, זימלא נעמי בת פיגא, אהרון בן פיגא, מאיר דוד בן פיגא, רבקה טויבא בת פיגא, לחברים טובים והצלחה בלימודים ובריאות איתנה והצלחה בכל הענינים. בן ציון בן פרומיט לרפואה שלמה במהרה, יהודית בת יוכבד וכל משפחתם, משה יעקב בן זימלא נעמי זוג' אסתר מירל בת לאה וכל משפחתם, פרומיט בת גיטל פער וכל משפחתם, יהודה בן יהודית וזוג' יוכבד בת עטל וכל משפחתם, חיים בן הינדה ברכה וזוג' לאה בת פייגה וכל משפחתם, פייגא בת אסתר מירל לרפואה שלמה במהרה. יעקב יצחק בן יוכבד לרפואה שלמה, אהרון בן מרים וזוג' אסתר בת חנה שבע לשלום בית, שלום דוב בן אסתר להצלחה בכל הענינים, ינטא רחל בת בת ציון לרפואה שלמה, בנימין יהודה בן דבורה מלכה וזוג' עדינה לאה בת אביבה מינה לבריאות איתנה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ש-0155</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>ברוך ליכטער</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>ברוך בן שרה דינה להצלחה ופרנסה בשפע גדול והצלחה גדולה מאוד בעסק שלו, וזוג' רחל בת עטל, ב' חנה ברכה, ב' אברהם נחמן, ב' חיה פייגא, ב' בן ציון, ב' אסתר חוה, ב' נתן צבי לברכה והצלחה ונחת ובריאות ושמחה תמיד ולהיות ברסלבר חסידים אמן.  נחמן בן שרה דינה להצלחה ופרנסה ברווח ובשפע גדול</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ש-0156</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>בריינדל חנה שוורץ</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>בריינדל חנה בת רייזא לבריאות והצלחה בכל הענינים ,יוסף אהרון בן שרה לרפואה שלמה שיתרפא מהמחלה,ופרנסה בשפע , יעקב בן בריינדל חנה לפרנסה בשפע, אברהם ישראל בן בריינדל חנה לרפואת הגוף והנפש ופרנסה בשפע ושיהיה לו הכח הפיזי והמנטלי שהוא זקוק לו בשביל התביעה והצלחה בכל הענינים הצלחה במציאת עבודה,שמואל אפרים בן בריינדל חנה לרפואה שלמה ופרנסה ברווח, משה בן עטל לבריאות ופרנסה בשפע והצלחה בכל הענינים. טשארנא רבקה בת בריינדל חנה לבריאות והצלחה. אסתר בת אליענה לרפואה שלמה והצלחה במציאת עבודה. שלי בת שרון להריון קל והעובר יהיה בריא ושלם</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ש-0157</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>ברק נחמן בר חיים</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>נחמן בן אסתר זאלדע לברכה והצלחה בכל הענינים עליזה בת מרים לבריאות ופרנסה שירה בת עליזה לבריאות ושידוך עם בן תורה אמיתי אריה בן עליזה הצלחה בלימוד התורה ובשאר עסקיו</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ש-0158</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>בת שבע נאווה רוזנטל</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>בת שבע נאווה בן רחל לבריאות ורפואה שלמה והצלחה וכל טוב אמן, מרדכי בן בת שבע נאווה לברכה ובריאות איתנה ופרנסה טובה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>ש-0159</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>גואל בלאחאני</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>גואל בן איומה להצלחה ופרנסה בשפע ושלום בית וכל טוב</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>ש-0160</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>דוד גאדין</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>אלטע פריידא עטיא בת מרים לבריאות ורפואה שלמה, שרה יענטא בת דבורה פערל לזיווג הגון בקרוב ממש, מרים בת דבורה פערל לזיווג הגון בקרוב ממש, ברוך בן דבורה פערל לברכה והצלחה וישוב הדעת, חנה ברכה בת דבורה פערל לשמחת חיים, יעקב דוד בן אלטע פריידא עטיא וזוג' דבורה פערל בת טובא לאה לברכה והצלחה, לנחת מכל יוצאי חלציהם</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ש-0161</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>דוד כהן</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>דוד הכהן בן נעמה. שרה בת חנה לפרנסה ברווח , שרה בת נעמה לפרנסה ברווח, משה בן שרה,נעמה בת שרה , אסתר בת שרה להצלחה ובריאות ופרנסה טובה, יעקב בן שרה, יוסף ודוד בני כוכבה</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>ש-0162</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>דוד מצגר</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>דוד עוזיאל בן אסתר להצלחה בכל הענינים ופרנסה, אדלה מנוחה בת הניא לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ש-0163</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>דוד נחמן סאויס</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>מיכאל בן מלכה,סעדה חדוה בת חנה בריאות ונחת מהצאצאים .שירה בת אסתר רפו"ש מכל מכאוביה שתחזור לאיתנה הראשון ולתפקד כאם בבית יהודי. דוד נחמן בן סעדה חדוה לכל הישועות וליישב את דעתו מידי יום עם בורא עולם שעה כציווי רבינו הק'.מיכאל אליאל, עמנואל,ורחל בתאל בני שירה שיגדלו לתורה חופה ומעש"ט בדרך רבינו הק'.</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ש-0164</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr"/>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>דוד קרלבך</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>דוד בן בונא מרים לרפואה שלמה במהרה ובריאות איתנה , עטרה חדוה בת רחל לרפואה שלמה במהרה אריכות ימים ושנים טובות אמן</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ש-0165</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>דוד שטיינברג</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>אליהו דוד בן שרה רבקה שלום בית וחינוך הילדים טוב, ופרנסה בשפע וברווח, וזוג' חיה בת פייגא שלום בית וחינוך הילדים ופרנסה בשפע, אסתר רחל בת חיה, יששכר דב בן חיה, מאיר בן חיה, חיים צבי בן לאה לברכה והצלחה בכל הענינים ברוחניות וגשמיות. יונתן לוי בן אביגיל וזוג' אסתר רחל בת חיה לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ש-0166</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>הערשל אוזיק</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>רפאל זאב בן אסתר וזוגתו הדר אהובה בת אירית אלגרה לרפואה שלמה  ובריאות איתנה  צבי בן גנעשה לרפואה שלמה בכליות ובכל הגוף  אסתר בת חנה לרפואה שלמה אמן, אריאל נתן בן אסתר וזוג' ריבה איילה בת עליזה שיתחזקו בתורה ומצוות ויראת שמים טהורה והצלחה בחינוך הילדים, בנם אסף נחשון בן ריבה איילה, בתם טליה חנה בת ריבה איילה, בנם יואב גדעון בן ריבה איילה, לבריאות והצלחה אמן. גנעשה בת אסתר מלכה לבריאות ואריכות ימים לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ש-0167</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>הרשל פרידמן</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>צבי חיים בן ציפורה וזוג' שיינדל ברכה בת חנה , ב' אהרן , ב' לוי יצחק , ב' יואל ב' חיה , ב' מרים מליא , ב' יחזקאל שרגא בן שיינדל , ב' חינקא רחל, ב' משה , ב' ישעיה , ב' אברהם , ב' סימא , להצלחה בישיבה בלימוד התורה ויראת שמים ולב טהור, ב' פערל</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ש-0168</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>זאב סאפטלאס</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>זאב בן שיינא מלכה וזוג' טובה ברכה בת שרה איידל ,ב' שמחה דוד , בתם אסתר צינה בתם בת שבע, בנם אהרן, בנם ישראל מאיר, בנם אברהם יעקב, בנם משה ... יוסף ברוך בן אפרת שיחזור בתשובה שלמה ולב טהור באמת, חדוה בת אפרת, זהבה מרים בת אפרת, אהובה חנה בת אפרת שיינא מלכה בת מרים ,דוד יהודה בן שרה לאה לרפו"ש במהרה .חיים בן הענא לרפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ש-0169</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>זאב שטרן</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>זאב צבי בן שרה רבקה וזוגתו בלימה בת שרה, מיכל רחל בת בלימה, נעמי לאה בת בלימה, אליהו בן בלימה, ציפורה בריינא בת בלימה, יעקב יצחק בן בלימה לבריאות והצלחה בעסק ובכל הענינים ונחת מהילדים</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ש-0170</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>זאבי פרטיג</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>ראובן בן רות דבורה וכל משפחתו: זווג הגון
+לאה בת בלימה שרה וכל משפחתו: בריאות איתנה, נחת, פרנסה טובה, ברכה והצלחה
+ר' יוסף מאיר בן יוטא עלקא וכל משפחתו: בריאות איתנה, נחת, פרנסה טובה, ברכה והצלחה
+ר' שלמה יהודה לייב בן חיה וכל משפחתו: בריאות איתנה, נחת, פרנסה טובה, ברכה והצלחה
+גיטל יהודית בת אביבה ציפורה וכל משפחתו: רפואה שלמה בקרוב</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ש-0171</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>זאוויל אדלקוף</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>זאוויל בן שרה וזוגתו דלה בת מאטי לברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ש-0172</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr"/>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>זכריה פלדמן</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>זכריה בן שרה,הבנת וזכרון התורה בנגלה ובנסתר, חכמה, בינה דעת, בנים זכרים צדיקים בנות צדקניות, פרנסה טובה והצלחה ועשירות, בריאות, יראת שמים ודבקות בהשם. בתיה חנה בת מלכה רוזא מנוחת הנפש ישוב הדעת שמחת החיים עשירות מופלגת בריאותוכוח וחיים ארוכים. שמחה אליהו בן שרה הרבה הצלחה בכל מעשה ידיו פרנסה טובה בריאות זיווג הגון ויפה. יראת שמיים. שיינא גולדא בת שרה שלום בית ישוב הדעת בריאות בנפש ובגוף. ביטחון בשם הרבה הצלחה פרנסה טובה בשפע. רפואת הנפש ורפואת הגוף.</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>ש-0173</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>חיה אולגה קירשבוים - שירצקי</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>אביאל אברהם בן רבקה לברכה והצלחה בכל מעשי ידיו , זוגתו חיה יהודית בת שרה, אמיתי גדעון בן חיה יהודית לבריאות טובה, יאיר בצלאל בן חיה יהודית לגדול בתורה ויראת שמים- לכל המשפחה שמירה, נחת ושמחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>ש-0174</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>חיים הוכמן</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>מיכאל חיים בן הניא לרפואה שלמה במהרה בריאות איתנה נחת ושמחה וכל טוב שמעון בן מנוחה וזוג' חוה בת אסתר ביילא, לפרנסה ברווח, הניא בת חוה, יהודית שבע לאה בת חוה, יואל אהרן בן רחל בת שרה, רבקה בת שרה - שמואל בן מנוחה מנוחה בת רחל לרפואה שלמה במהרה  בריאות הגוף ומנוחת הנפש ופרנסה ברווח,</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ש-0175</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>יהודה ליברמן</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>יהודה בן חנה פייגא לברכה והצלחה בכל הענינים ופרנסה בשפע ורווח, נחת בריאות וכל טוב אמן , וזוג' שרה אסתר בת חנה לבריאות והצלחה בכל הענינים ונחת וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>ש-0176</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>יהודה צוקר</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>יהודה בן יפה וזוג' הודיה מרים בת יהודית להצלחה בריאות איתנה ונחת מכל יוצאי חלציהם. הילדים נחמן בן הודיה מרים, פיגא בת הודיה מרים, נפתלי הרץ בן הודיה מרים, שרה בת הודיה מרים, רבקה בת הודיה מרים, רחל בת הודיה מרים להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>ש-0177</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>יהודה רוזובסקי</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>יהודה בן אסתר וזוג' חנה בתשבע בת ברכה, שושנה רחל בת בתשבע, תהילה בת חנה בתשבע, אליהו בן חנה בתשבע, מיכאל בן חנה בתשבע, תמר בת חנה בתשבע, רות בת חנה בתשבע. לברכה והצלחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>ש-0178</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>יהודית קונקל</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>יהודית רוחמה בת חוה להצלחה בגידול ילדיה ולרפואה שלמה , דבורה שרה בת יהודית רוחמה לרפואה שלמה בקרוב ורחמי שמים , נחמן שמשון בן יהודית רוחמה להצלחה בכל הענינים, יהודית בת שרה אמנו לזיווג הגון בקרוב ממש ולהצלחה בכל הענינים אמן, פרנצ'ה בת שרה אמנו לישועת הנפש ועליה קלה לארץ ישראל</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>ש-0179</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>יהושע וויינפעלד</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>יהושע בן מרגליא צביה שיהיה לו הצלחה גדולה בעסק ועשירות, ובריאות וכל טוב, וזוגתו רייזל גולדא בת אסתר יכט להצלחה בריאות נחת מהילדים וכל טוב, יצחק אלעזר בן מרגליא צביה לברכה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>ש-0180</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>יהושע מאיר דויטש</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>יהושע מאיר בן רחל להצלחה בבניית הבניין הקדוש וכולל חצות ובכל הענינים ולהתקרב לרבינו הקדוש וזוגתו בלהה בת ציפורה לבריאות ואושר והצלחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>ש-0181</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>יואל לוינסון</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>אלישבע בת ברוניא - זיווג הגון
+דבורה חדוה בת יונה - זיווג הגון
+ענת בת אסתר - זיווג הגון
+מרים אביבה בת שרה - זיווג הגון
+עדי בן תמרה טובה - ברכה והצלחה
+רות דבורה בת יהודית - ברכה והצלחה
+יעל בת רות דבורה - ברכה והצלחה
+אורלי בת רות דבורה - ברכה והצלחה
+גאיה בת רות דבורה - ברכה והצלחה</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל אב פו</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>ש-0182</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>יוני קורבמן</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>אהרן יוסף בן נעמי נעכה הינדה - בראות, הצלחה, ודבקות בה׳
+שמחה בת נעמי נעכה הינדה - שתחזור ותדבק בהקב״ה ובתורתו
+בנימין בן נעמי נעכה הינדה - בריאות, הצלחה, שמחה, ודבקות בה׳ ושקידה ביראת שמים
+אליעזר ישראל בן מלכה ריזל - בריאות, הצלחה, ושתחזור לדרך התורה</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>ש-0183</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>יוסף אגמי</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>שמעון דוד יוסף בן שרה וזוגתו אסתר הדסה בת שרה חנה וכל יוצאי חלציהם לברכה והצלחה בכל הענינים, שכל צאציהם יהיו חסידי ברסלב אמיתיים, וינצלו מפגעי הטכנולוגיה אמן שרה רות בת אסתר הדסה לזיווג הגון בקרוב</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>ש-0184</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>יוסף אורדנטליך</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>יוסף בן ברכה וזוג' אהובה בת חיה איטה קרול להתברך בזרעא חיא וקיימא אמן, ושיזכה שיהיה לו הרבה ממון בשפע וברווח לחלק לצדקה, ובריאות איתנה אמן. ברכה בת חנה מארא לרפואת הנפש ורפואת הגוף ונחת מכל יוצ'' ח ובריאות איתנה שלא יהיו לה מיחושים וכאבים ושתהיה שמחה ומאושרת אמן. משה בן ברכה לרפו"ש, רפאל בן ברכה לרפו''ש.
+נעמי אסתר בת רחל לאה לרפואה שלמה ובריאות איתנה אמן</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>ש-0185</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>יוסף גאנז</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>יוסף מרדכי בן יהודית שיינדל נחמה בת אלישבע, דניאל יהודה בן נחמה, ישעיה בן נחמה, שמואל בן אסתר, שרה רחל בת נחמה, אשליבע חיה בת שרה רחל, משה אליעזר בן שרה רחל, בנימין בייניש בן שרה רחל, בנימין חיים בן נחמה, רחל בת פייגא חנה, אלישבע ברכה בת רחל, אליהו דוד בן חיה, יהודית שניידל בת שרה רחל</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ש-0186</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>יוסף גוטפרב</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>יוסף בן אסתר רבקה וזוג' מינדל בת שרה לרפואה שלמה ובריאות איתנה ופרנסה בשפע וברווח ושיהיה בית של ברסלב מלא בשמחה ואמונה ושלום בית וסייעתא דשמיא והצלחה ברו'' ג, נחמן דוד בן מינדל להצלחה בלימודים ובחברה ושיהיה לו אהבת התורה והשי'' ת, נחמה רייזל בת מינדל לבריאות איתנה והתפתחות טובה ובריאה ושתצליח בלימודים ובחברה, אלטע דבורה בת מינדל להתפתחות טובה ובריאה ושתצליח בתקשורת נכונה וביטחון עצמי, נתן שמעון בן מינדל שיצליח בלימודים ויהיה לו אהבת התורה והשי'' ת, פייגא ליבא בת מינדל שתליח לדבר בקרוב ממש ושתצליח בכל ותהיה שמחה ואהבת השי'' ת אמן, אלימלך בן מינדל שיצליח בלימודים ויהיה לו אהבת התורה והשי'' ת</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>ש-0187</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>יוסף ירט</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>יוסף שמואל בן טובה לפרנסה ברווח. רבקה בת טשארנא פריידל לפרנסה ברווח,  שולמית עטרה בת רחל נחמה, מנוחה בת רחל נחמה, יהושע נתן הלוי בן שפרה מינא רחל, הדסה בת מנוחה, מאיר בן רחל נחמה\ נחמה רחל בת שרה, פרומיט בת רבקה. אריה ניסן בן ציפורה, עדינה בת פרומיט. אהובה רחל בריינדל בת פרומיט, דבורה בת רבקה, יוסף מאיר אורי הלוי בן ליבא גיטעל, חיים יצחק יהודה הלוי בן דבורה. רחל דינה בת רבקה, צירעל בת רבקה</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>ש-0188</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>יוסף מרדכי מנדלסון</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>יוסף מרדכי בן לאה וזוג' הדסה רבקה בת זלטה בריאות איתנה, ברוך בן הדסה רבקה, דניאל משה בן הדסה רבקה , יהודה דוב בן הדסה רבקה, אלישע שמואל בן הדסה רבקה - לברכה והצלחה בכל הענינים ונחת ופרנסה בשפע וכט"ס .שיינדל רחל בת לאה לזיווג הגון בקרוב ממש ממש .אריה מלכיאל בן הענטשא דינה וזוגתו רחל אסתר בת הדסה רבקה, רישעל בת רחל אסתר לברכה והצלחה וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>ש-0189</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>יחזקאל גולדברגר</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>יחזקאל שרגא בן שרה רבקה לברכה והצלחה בכל העסקים ובכל הענינים ברו"ג, בריאות ומנוחת הגוף והנפש, וזוג' בלימא יטל בת רחל פראדל לרפואה שלמה בגב לבריאות והצלחה בכל הענינים והצלחה גדולה בעסק התיווך, ב' אהרןבן בלימא יטל להצלחה בישיבה ובלימוד התורה ולמצוא ישיבה מתאימה בשבילו, ב' חיים צבי, ב' עמרם, ב' יהונתן לרפואה שלמה, ב' נתנאל, ב' יהודית לבריאות איתנה - לברכה והצלחה בכל הענינים ברוחניות וגשמיות</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>ש-0190</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>יחזקאל סייד</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>יחזקאל אליעזר בן לאה .משה פנחס בן טובה לב טהור ולחזור לאידישקייט במהרה, חזרה בתשובה שלמה וזוג' שיינא יהודית בת זיסל, רפואה שלמה במהרה ושיתרפא ממחלת הקרוהן שיש לו אמן .נתנאל יוסף בן ליאורה לרפואה שלמה בקרוב</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ש-0191</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>יחיאל עקשטיין</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>יחיאל צבי בן פיגא ציפורה מלכה לפרנסה ברווח ובנקל והצלחה רבה בבית העסק</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ש-0192</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>יידי וורצברגר</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>צבי יהודה אלימלך בן בלימא וזוג' שיינדל בת הינדל , ב' חיה פראדיל , ב' יחזקאל שרגא , ב' ציפורה , ב' רבקה, ב' אסתר , ב' שמואל, ב' משה , ב' הלל, ב' אילה בלומא להצלחה בכל הענינים ופרנסה וכל טוב.  חוה בת הינדל לרפואה שלמה במהרה</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ש-0193</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>יעקב בן שמואל</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>יעקב בן אסתר לברכה והצלחה בכל הענינים, סיעתא דשמיא והצלחה בלימוד הלכות איסור והיתר ובלמוד התורה, שלום, קדושה וטהרה. הצלחה בניסיונות. שלום בית .ישעיה דוד בן רחל, לברכה והצלחה בכל הענינים, ופרנסה ברווח, ניסים בן חיה לרפואה שלמה, נחמה ליבא גיננדעל בת רחל לברכה והצלחה ,רחל בת איטה רייזא לברכה והצלחה,</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>ש-0194</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>יעקב גולדבורד</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>יעקב בן בתיה וזוג' חנה רייזל בת בדנה לברכה והצלחה ובריאות וכל טוב בדנה בת זלדה לבריאות ורפואה שלמה אמן</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ש-0195</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>יעקב גרין</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>יעקב דוד רפאל בן חנה מינדל וזוג' רינת רחל בת נחמה, ב' שרה דינה בת רינת רחל, ב' יוסף דב בן רינת רחל, ב' אלישבע צביה בת רינת רחל, ב' ציפורה פייגא בת רינת רחל, ב' בנימין מאיר בן רינת רחל, ב' משה בן רינת רחל, ב' דבורה רבקה בת רינת רחל לבריאות איתנה ופרנסה בשפע וברווח והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>ש-0196</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr"/>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>יעקב דוב פרכטר</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>יעקב דוב בן פיגא לאה לפרנסה ברווח ובשפע, וזוג' רחל ליבא בתיה בת יהודית אסתר פערל, לפרנסה בשפע ורווח , ב' אילנה ,ב' משה יוסף, ב' יעל, ב' דינה אלישבע ,ב' אברהם אליעזר לזכותו לזכות כל כלל ישראל אמן, שמחה יששכר צבי בן ציפורה וזוג' חיה שרה גולדה בת רחל ליבא בתיה, ב' קיילא חנה בת חיה שרה גולדה שמואל יצחק בן גולדה רחל לרפואה שלמה במהרה, וזוגתו יהודית אסתר פערל בת ציפורה פייגא לרפואה שלמה במהרה אמן. דוד אריה בן מיכל גיטל לחזרה בתשובה. חיינע בת שבע בת חיה שרה גולדא לרפואה שלמה במהרה אמן, שמעון חיים בן חיינע בת שבע לזיווג הגון בקרוב ממש, רבקה דליה בת רחל לזיווג הגון בקרוב, שחר בן יהודית פרומא לזיווג הגון בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ש-0197</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>יעקב מרדכי קלאוס</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>יעקב מרדכי בן אסתר וזוג' שרה פריידא בת עטל וכל המשפחה שיחיו לבריאות הגוף והנפש, הצלחה בכל הענינים, יעקב מרדכי בן אסתר ושמואל שלום בן אסתר להצלחה בכל הדברים שעוסקים ביחד</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>ש-0198</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr"/>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>יעקב קריאף</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>רינה מרים בת חיה ושלום ושלווה פנימית ללא כעס, יהושע הלל בן חיה שיפסיק לגמגם והצלחה בכל הענינים, אהובה רחל בת חיה לשמחה ובריאות איתנה</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>ש-0199</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr"/>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>יעקב שלמה צוקרמן</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>שירה בת חגי לשמחה ואמונה, עלמה מרים בת שירה ,נתן אליהו בן שירה שיגדלו לתורה ולרוגע נפשי, נחמן פלא בן שירה שיגדלו לתורה ולרוגע נפשי, שהילדים יגדלו בקדושה לאהבת השם והצדיקים והרבה שמחה והרבה אמונה, יעקב שלמה בן לאה לפרנסה בשפע וברווח וברכה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>ש-0200</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr"/>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>יצחק גולדשטיין</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>ישראל יצחק בן אסתר חיה להצלחה בכל הענינים, פרנסה ברווח, וזוג' מאטיל חנה בת רבקה נוחה, ב' אלכסנדר, ב' פערל, ב' משה חיים, ב' שבתי ברוך  שאול יחזקאל בן חנה וזוגתו,  ליבא רייזל בת מאטיל חנה, ב' שבתי ברוך , אסתר  חיה בת דבורה</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>ש-0201</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr"/>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>יצחק פוקס</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>יצחק אהרן בן רחל שיינדל וזוג' דבורה אסתר בת שרה לברכה והצלחה בכל הענינים, פרנסה בשפע גדול וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>ש-0202</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr"/>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>יצחק צוויק</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>יצחק בן ציון בן לאה צביה וזוג' אסתר בת רבקה רחל , ב' חיים , ב' שלמה גבריאל , ב' יהודה יידל , ב' חיה שרה ,ב' נתנאל ב' צבי יאיר, רבקה רחל בת שרה ביילא לרפואה שלמה בקרוב. שושנה רות בת לאה צביה לזיווג הגון ורפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ש-0203</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>ישראל פלאוט</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>ישראל מאיר בן פריידל לבריאות הגוף והנפש ורפואה שלמה, פרנסה בשפע גדול וברווח עד בלי די, הצלחה בגידול הילדים ושיראה מהם נחת דקדושה ויהיה לבניו זיווג הגון במהרה, וזוג' רבקה ביילא בת פייגא טויבא לרפואה שלמה ולהצלחה ושלום בית, ונחת מהילדים ופרנסה טובה, זבולון ירמיהו בן רבקה ביילא לזיווג הגון בקרוב, יראת שמים ולב טהור, בנימין בן רבקה ביילא ליראת שמים ולב טהור לה', אהובה בת פריידל לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ש-0204</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr"/>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>ישראל רוזנפלד</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>ישראל אבא בן חנה שרה וזוג' טובה גיטל בת אסתר להתברך בזש"ק בקרוב ממש.שמואל אליהו בן ציפורה לרפו"ש</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>ש-0205</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>כסנדרה למפקוב</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>כסנדרה בת פולו בידריאם להצלחה בכל הענינים, בריאות הגוף והנפש, זרע של  קיימא, פרנסה טובה. טיילור אשורט בן אליסה גאיל לפרנסה טובה, זרע של קיימא ורפואה שלמה.</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>ש-0206</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr"/>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>לאה אברמוביץ</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>אליעזר דניאל בן חיה לאה וכל משפחתו. דב מרכי בן חיה לאה וכל משפחתו</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ש-0207</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr"/>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>לאה לארטש</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>חיים שלמה זלמן בן בלומא לרפואה שלמה במהרה ולפרנסה טובה, בריאות, והצלחה בכל הענינים, לאה בת חיה רחל לפרנסה והצלחה בכל הענינים, ברכה בלומה בת לאה לזיווג הגון</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ש-0208</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr"/>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>לוי זייגלבוים</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>לוי בן נעכא וזוג' דינה ביילא בת יהודית , ב' שיינדל בת דינה ביילא , ב' מאיר בן דינה ביילא , ב' אפרים דוב בן דינה ביילא , ב' הינדא לאה חיה בת דינה ביילא ,ב' גבריאל זושא - להצלחה בכל הענינים ונחת ופרנסה ובריאות וכט"ס</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>ש-0209</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>מאיר אזאגורי</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>אברהם בן רחל לפרנסה בשפע יעקב בן רחל לזיווג הגון, רחל בת ליזי  לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>ש-0210</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>מאיר שלום הרשקוביץ</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>מאיר שלום בן בלומא שרה לבריאות והצלחה ופרנסה בשפע, וזוג' שירה בריינא בת שרה איידל , ב' ברוך יהודה , ב' שמואל , ב' רייזל , ב' קיילא , ב' שמחה משה , לברכה והצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>ש-0211</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>מארק הלברשטם</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>משה אליקים בריעה בן חיה רייזל וזוג' חוה צביה בת פעשא פייגא להצלחה ופרנסה ושלום בית, ב' חיה רייזל , ב' אליעזר ירוחם חיים לנחת דקדושה ובריאות וחיים טובים</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>ש-0212</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>מיכאל זינגר</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>מלכה נה יהודית בת פרכה נעימה לרפו"ש בקרוב</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ש-0213</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr"/>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>מינדי הלפרין</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>ריצרד מריל 
+בן פאצט 
+לרפואה שלמה ובריאות איתנה</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ש-0214</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr"/>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>מלאני לייטמאן</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>אסתר מלכה בת תמר לזיווג הגון ופרנסה בשפע ורפואה שלמה
+תמר בת שרה לזיווג הגון ופרנסה בשפע ורפואה שלמה
+אינגה אסתר בת גיטל לזיווג הגון ופרנסה בשפע ורפואה שלמה</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>ש-0215</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr"/>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>מנחם מנטל</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>מנחם בן רבקה לפרנסה ברווח , וזוג' רבקה בת צירל , ב' יהודה אריה בן רבקה לברכה והצלחה, מיכאל בן רבקה לברכה והצלחה, דניאל בן רבקה, יעקב בן רבקה לזרע של קיימא , ב' דוד בן רבקה להצלחה בתורה ויראת שמים , להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>ש-0216</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr"/>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>מרדכי גלבר</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>מרדכי צבי בן פרימט שרה לרפואה שלמה ולברכה והצלחה. דבורה בת ציפורה ברכה לזיווג הגון, שלמה ישראל בן פעסא בתיה לחזרה בתשובה שלמה, רבקה חנה בת פעסא בתיה זיווג הגון</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>ש-0217</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr"/>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>מרדכי הכהן</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>מרדכי הכהן בן מאשה פייגא
+הצלחה, זיווג הגון, בריאות שלמה, וזרע של קיימא, שיזכה ללימוד תורה</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>ש-0218</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr"/>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>מרדכי ליפשיץ</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>מרדכי שלמה בן אסתר 
+מרים בת חנה לאה 
+תמר שרה בת מרים
+מנחם מנדל בן מרים 
+מלכה נחמה בת מרים
+יעל ברכה בת מרים לנחת בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>ש-0219</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr"/>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>משה בינעט</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>אברהם משה בן אסתר יענטא להצלחה בכל הענינים, ובכל המשפטים, ולא יאונה לו כל רע, פרנסה בשפע ורווח ונחת מכל יוצ"ח וכל טוב</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>ש-0220</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr"/>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>משה הורן</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>משה דוד חיים בן חוה וזוגתו גולדה נעמי בת אסתר לברכה והצלחה בכל העניינים ופרנסה ברווח ועשירות והצלחה בעסק 
+נחמה בת גולדה נעמי , מלכה בת גולדה נעמי , בנימין בלע בן גולדה נעמי , עזריאל שמעון בן גולדה נעמי 
+לנחת בריאות וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>ש-0221</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr"/>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>משה מנדל טאוב</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>משה מנדל בן רויזא לפרנסה טובה ויצליח מאוד בכל עסקיו ובכל הענינים , וזוג' שרה לאה בת אסתר רבקה לבריאות ורפואה שלמה אמן</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>ש-0222</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr"/>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>משה עייאש</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>משה בן גבריאל גבריאל בן אסתר לרפואה שלמה ,שרה רחל דונה בת דבורה לרפואה שלמה מהמחלה בקרוב ממש אמן חנה בת מזל לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>ש-0223</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr"/>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>נחום פישמן</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>נחום דוב בן רבקה בת שבע, פרנסה ברווח ובנקל, אושר ועושר נשיאת חן הצלחה בכל ענינים שמירה מחשבות טובות אמונה ,ובטחון, להיות תמיד עסוק הרחבת הדעת שמחת תמיד, גזונט פרנסה נחת , סביבה טובה הדרכה, חברים ,רחמים וחסדים, שלום בית סייעתא דשמיא, פייגא בת חיה עטל שמחה,הריון קל וכשורה ולידה בזמן בקלות ובריאות, נחת,שמירה הצלחה שלום בית סיעתא דשמיא, יצחק בן פייגא, שיגדל לתורה ולחופה ולמעשים טובים נשיאות חן בריאות והצלחה וברכה, טובה אסתר בת פייגא זאל זיין א פיין ערליך יודש מיידעל, בריאות ברכה והצלחה,שרה בת פיגא, אברהם בן פיגא לרפואה שלמה במהרה ,מאיר יהודה בן הענדל לרפואה שלמה רפואת הנפש ורפואת הגוף, הענא פרומא בת שרה לרפו"ש</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>ש-0224</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>נתן ירבלום</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>נתן בן בתיה וזוג' רחל בת חיה קלרה לברכה והצלחה ובריאות וכל טוב, נחמן ישראל בן ברוריה וזוג' אדל בת רחל ב' שמואל מרדכי , ב' לוי יצחק, ב' יוסף חיים, ב' איילה . נחמן בן רחל לזיווג הגון בקרוב ממש , אליה בן שירה רחלי לגדול לתורה ויר"ש, חנוך בן איטקא וזוג' בתיה בת עליזה לבריאות איתנה ב' נצר עופרי , ב' דגן , ב' תלם  לחזרה בתשובה הם ומשפחותיהם, חיה קלרה בת גיטל לרפואה שלמה ואריכות ימים וחזרה בתשובה של כל משפחתה</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>ש-0225</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr"/>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>נתניאל דואק</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>נתניאל אהרון הכהן בן בתיה רחל
+ליאורה מיכל בת זלדה
+שרה יונינה בת ליאורה מיכל
+לברכה והצלחה בכל העניינים וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ש-0226</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr"/>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>סנדרה גרוס</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>שרה ג'ינה בת פנינה לברכה והצלחה, אלישע בן שרה ג'ינה לפרנסה בשפע, פנינה בת מניה באשע לרפואה שלמה, רבקה פייגא בת חנה לזיווג הגון בקרוב ממש, דינה בת שרה ג'ינה ובעלה שלמה בן לאה גיטל שיזכו לגדל את ילדם לתורה , לחופה ולמעשים טובים. שלמה אפרים בן חיה ברכה וזוגתו שירה בת שרה רבקה לזרע של קיימא.</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>ש-0227</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr"/>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>סקוט מוסקוביץ</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>רחל ברכה בת פייגא לאה לבריאות שלמה לה ולרך הנולד</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>ש-0228</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr"/>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>עזריאל פלור</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>עזריאל זאב בן שושנה חיה רחל וזוגתו שרה חנה בת שולמית , ב' אסתר מלכה , ב' יצחק אהרן , ב' עדינה מרים , ב' פייגא דבורה , ב' שמשון דוד, ב' צבי אליעזר , להצלחה וברכה וכל טוב</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>ש-0229</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr"/>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>עמוס בן ציון הרמן</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>עמוס בן ציון בן חנה לרפואה שלמה במהרה ובריאת איתנה, נחמן בן שרה לזיווג הגון בקרוב ממש והצלחה ועליה בתורה ויר"ש וחשקת התורה נתן בן שרה ואהרן בן שרה שיהיו לומדי תורה צדיקים ובעלי מידות טובות</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>ש-0230</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr"/>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>פייגא גרוסמן</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>פייגא בת רייזל לזיווג הגון בקרוב ממש, נחת מהילדים, בית של שמחה ואמונה, צבי יהודה בן פייגא שיהיה צדיק ותלמיד חכם, חשקת התורה עם מתיקות, יראת שמים, שמחה אמונה בה', הצלחה בכל.</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>ש-0231</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr"/>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>פינק מאיר</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>ישראל מאיר בן רייזל יהודית להצלחה בכל הענינים, חווה אסתר בת גיטל להצלחה בכל הענינים, שלמה בן חווה אסתר לרפואה שלמה, יצחק בן רחל לפרנסה ברווח ובשפע.</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>ש-0232</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr"/>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>פנחס האשען</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>גיטל הינדא בת קילא
+רפואה שלמה בנקל ובמהרה
+שרה מרים בת דריזא חנה
+פינחס ניסן בן גיטל הינדא
+לפרנסה בנקל  להרחבת הדעת
+שיזכו לקרבת ה' ואהבת ה' והצלחה בכל מעשי ידיהם
+לזש"ק בקרוב ממש</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל לא פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>ש-0233</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr"/>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>פנינה יאיש</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>שירלי לור בת אסתר לרפואה שלמה, ראובן שלום אברהם בן פנינה להתקרב לה' ולתורה ומצוות, ציפורה בת פנינה לחזור בתשובה ולב טהור התקרב לה' ולתורה ומצוות וחזרה בתשובה וזיווג הגון בקרוב ממש, פנינה בת שירלי לברכה והצלחה ונחת וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>ש-0234</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr"/>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>צבי אריה קרמר</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>צבי אריה בן גיטא גינענדל וזוג' טויבא רחל בת שרון, ב' יצחק מתתיהו, ב' נחמן, ב' ציפורה שירה, ב' לאה תהילה, ב' נתן מאיר, ב' יהודה אליהו  - לברכה והצלחה בכל הענינים , ולזכות להיות ברסלבר חסידים אמיתיים אמן</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>ש-0235</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr"/>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>צבי גייקובס</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>צבי יוסף בן אסתר עליזה שמחה שינה מאשה בת ברכה, אריה לייב בן עליזה שמחה שינה מאשה שיזכו להקים בית נאמן בישראל בית עם שמחה ואהבת ה', בית של תורה, בית של חסד, בית עם אור של התורה ובריאות איתנה ושפע של פרנסה כדי שיוכל להמשיך לעזור לאחרים, אסתר בת פורטונה כתון לרפואה שלמה ובריאות איתנה, טליה רחל בת צבי יוסף להצלחה בכל הענינים</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>ש-0236</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr"/>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>שיינא לנדאו</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>רבקה דבורה בת שיינא שרה רייזל לרפואה שלמה, גבריאל דוד בן לאה לרפואה שלמה במהרה, נח צבי בן יוכבד לאה לרפואה שלמה, עליזא פראדל בת מלכה לאה לרפואה שלמה ובריאות איתנה, מאיר בן רבקה דבורה לרפואה שלמה בקרוב אמן</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>ש-0237</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr"/>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>שלמה גרין</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>שלמה בן בלימה פערל וזוגתו מרים לאה בת רייזל, משה אליהו בן מרים לאה, אסתר יוטא בת מרים לאה, אברהם מאיר בן מרים לאה , לברכה והצלחה ובריאות וכל טוב אמן. רבקה פערל בת רייזל לרפואה שלמה במהרה אמן</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>ש-0238</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr"/>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>שלמה סמיילו</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>שלמה בן ציון בן ביילא ברכה לרפואה שלמה ,מרדכי יצחק בן הענטשע לרפואה שלמה, רוחמה חיה פרומה בת פערל מרים מלכה לרפואה שלמה, אברהם יוסף בן הינדה קריינדל להצלחה בעבודת ה' יתברך</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>ש-0239</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr"/>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>שמואל גולדבורד</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>שמואל בן חנה רייזל וזוגתו מרים רחל בת שרה, זונדל אריה בן מרים רחל, דניאל בן מרים רחל , עליזה בתיה בת מרים רחל, מרדכי שלמה בן מרים רחל לברכה והצלחה . אליהו בן נחמה לברכה והצלחה ופרנסה ברווח וכל טוב אמן</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ש-0240</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr"/>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>שמואל ואסתר אינגבר</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>שמואל נחמן בן פנינה וזוג' אסתר רינה בת רחל , ב' שירה שפרה , ב' נתן מרדכי , ב' שושנה פייגא להצלחה ופרנסה טובה , בריאות וכל טוב</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>ש-0241</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr"/>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>שמואל כהן</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>חנה בת פנינה רחל לברכה והצלחה בגשמיות וברוחניות. ברכה בת פנינה רחל לברכה והצלחה בגשמיות וברוחניות. נתן צבי בן פנינה רחל לברכה והצלחה בגשמיות וברחוניות. אליעזר דוד בן פנינה רחל לברכה והצלחה בגשמיות וברוחניות</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>ש-0242</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr"/>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>שמחה גיטל הרליץ</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>שלום צבי בן שמחה גיטל
+חיים בן משה שמחה גיטל
+שמואל מרדכי דוד בן שמחה גיטל
+ישראל נחמן בן שמחה גיטל
+אברהם מאור בן שמחה גיטל
+לסייעתא דשמיא והצלחה ופרט בלימוד התורה ועבודת השם</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>ש-0243</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr"/>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>שרגא שריייבר</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>שרגא פייוול בן לאה להצלחה גדולה בעסק, וזוג' מינדל רעכל בת מרים להצלחה בענין הדירה בירושלים, ב' שלום וכל המשפחה יהיו בריאים ושלמים. אברהם יעקב בן מינדל רעכל וזוג' פנינה שרה בת מינדל רייזל, ב' לאה, ב' רבקה אסתר , ב' עטל , ב' יהודה ישעיה, ב' הדסה, ב' יצחק, ב' טובה גיטל, ב' משה, ב' מרים , ב' בנימין בייניש, אליעזר בן בריינדל חנה וזוג' חנה פערל בת מינדל רעכל לבריאות ועוד בנים ובנות ב' יעקב , ב' משה, ב' בריינדל רחל, ב' לאה .אליעזר צבי בן מינדל רעכל וזוג' הדסה בת לאה, ב' שמואל, ב' רבקה, ב' מאיר, ב' מרים</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ש-0244</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr"/>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>שרה ברודי</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>יענטא בלומא בת שרה חנה לרפואה שלמה ובשורות טובות
+ישי בן לאה פינה מינדל פרנסה ברווח 
+יהודית בת שרה חנה הצלחה בכל העניינים
+יואל בן אסתר וזוגתו שרה חנה בת אלטא פרידא ,שלום בית, פרנסה
+בשפע, נחת ,בריאות והצלחה בכל הענינים ,
+משה שמעון בן שרה חנה להצלחה בכל הענינים, זיווג הגון.</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל_כללי</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>קוויטל</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -578,7 +578,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+1 941-730-4495</t>
+          <t>+1 (941) 730-4495</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>718-9516797 / +1 917-417-0809</t>
+          <t>+1 (718) 951-6797 / +1 (917) 417-0809</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+1 718-534-0126 / +1 718-871-0724 / +19175024040</t>
+          <t>+1 (718) 534-0126 / +1 (718) 871-0724 / +1 (917) 502-4040</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>053-276-6667</t>
+          <t>+972 532766667</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -831,7 +831,7 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>+1 917-497-0682</t>
+          <t>+1 (917) 497-0682</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -878,7 +878,11 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>+1 (347) 623-1444</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -900,7 +904,7 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -978,7 +982,7 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>+1 718-614-1968</t>
+          <t>+1 (718) 614-1968</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1031,7 +1035,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>⁦+1 (718) 594-4717⁩</t>
+          <t>+1 (718) 594-4717</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1178,7 +1182,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>+1 646-812-2241</t>
+          <t>+1 (646) 812-2241</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,7 +1276,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>+17329770104</t>
+          <t>+1 (732) 977-0104</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1368,7 +1372,11 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 892-7865</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1390,7 +1398,7 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1623,7 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>+1 516-791-3311</t>
+          <t>+1 (516) 791-3311</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1668,7 +1676,7 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>+1 917-951-4252</t>
+          <t>+1 (917) 951-4252</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1717,7 +1725,7 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>+19177017148 / +19177017148</t>
+          <t>+1 (917) 701-7148 / +1 (917) 701-7148</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1766,7 +1774,7 @@
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>+1 917-538-6532</t>
+          <t>+1 (917) 538-6532</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1819,7 +1827,7 @@
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>00 1 718-384-2494 / 347-409-8045 / +380 68 704 6906</t>
+          <t>+1 (718) 384-2494 / +1 (347) 409-8045 / +380687046906</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1868,7 +1876,7 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>+1 917-613-0192 / 012-171-82525005 / (917) 613-0349 / 212-4201999</t>
+          <t>+1 (917) 613-0192 / 012-171-82525005 / +1 (917) 613-0349 / +1 (212) 420-1999</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1917,7 +1925,7 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>+1 914-391-9146</t>
+          <t>+1 (914) 391-9146</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1970,7 +1978,7 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>+1732664-1000</t>
+          <t>+1 (732) 664-1000</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2023,7 +2031,7 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>+1 718-338-9198 / +1 (718) 938-7353</t>
+          <t>+1 (718) 338-9198 / +1 (718) 938-7353</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2129,7 +2137,7 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>+49 6530 1758 / +49 1515 4701110</t>
+          <t>+4965301758 / +4915154701110</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2231,7 +2239,7 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0131 954-647-0021 / +972 53-836-0021</t>
+          <t>0131 954-647-0021 / +972 538360021</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2378,7 +2386,7 @@
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>+13479468768</t>
+          <t>+1 (347) 946-8768</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2462,7 +2470,11 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>+1 (305) 930-4470</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
@@ -2472,7 +2484,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2484,7 +2496,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2515,11 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>+1 (347) 576-3770</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
@@ -2513,7 +2529,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2525,7 +2541,7 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2566,7 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>+1 718-252-9641 / +1 (917) 440-2674</t>
+          <t>+1 (718) 252-9641 / +1 (917) 440-2674</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2603,7 +2619,7 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>+17736782708</t>
+          <t>+1 (773) 678-2708</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2656,7 +2672,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>+17186440307</t>
+          <t>+1 (718) 644-0307</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2762,7 +2778,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1 (917) 613-0306</t>
+          <t>+1 (917) 613-0306</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2819,7 +2835,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>+1 917-803-1478</t>
+          <t>+1 (917) 803-1478</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2866,7 +2882,11 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>+1 (347) 804-6125</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -2888,7 +2908,7 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2933,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>+1 718 309-3493</t>
+          <t>+1 (718) 309-3493</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2966,7 +2986,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>+1 / +1917 754-6634</t>
+          <t>+1 / +1 (917) 754-6634</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3019,7 +3039,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>+1 347-218-2340</t>
+          <t>+1 (347) 218-2340</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3077,7 +3097,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>+1-516-807-2618</t>
+          <t>+1 (516) 807-2618</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3187,7 +3207,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>845-3681172 / +13107337014</t>
+          <t>+1 (845) 368-1172 / +1 (310) 733-7014</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3285,7 +3305,7 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>+1 347-986-0779</t>
+          <t>+1 (347) 986-0779</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3391,7 +3411,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>+972 52-286-8141</t>
+          <t>+972 522868141</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3440,7 +3460,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>+19176572762</t>
+          <t>+1 (917) 657-2762</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3532,7 +3552,11 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 865-6597</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
@@ -3542,7 +3566,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -3554,7 +3578,7 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3697,7 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>917-943-6381 / +1 (917) 943-6381</t>
+          <t>+1 (917) 943-6381 / +1 (917) 943-6381</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3777,7 +3801,11 @@
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 238-9393</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
@@ -3787,7 +3815,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -3799,7 +3827,7 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3852,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>(917) 359-3255 / (718) 763-8769 / (212) 801-2110</t>
+          <t>+1 (917) 359-3255 / +1 (718) 763-8769 / +1 (212) 801-2110</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4073,7 +4101,7 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>+1 347-308-3664</t>
+          <t>+1 (347) 308-3664</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4126,7 +4154,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>+1516-761-2375</t>
+          <t>+1 (516) 761-2375</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4179,7 +4207,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>+19175892813</t>
+          <t>+1 (917) 589-2813</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4330,7 +4358,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>718-821-6800 / +1 (917) 359-1866</t>
+          <t>+1 (718) 821-6800 / +1 (917) 359-1866</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4432,7 +4460,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>+1 216-785-9235 / ‪+1 (248) 752-4723‬</t>
+          <t>+1 (216) 785-9235 / +1 (248) 752-4723</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4477,7 +4505,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>058-688-1592 / +620586881592</t>
+          <t>+972 586881592 / +620586881592</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4616,7 +4644,7 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>718-8713701</t>
+          <t>+1 (718) 871-3701</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4796,7 +4824,7 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>+1-732-239-2033 / 001 732-239-2033 / +1 732-239-2033</t>
+          <t>+1 (732) 239-2033 / +1 (732) 239-2033 / +1 (732) 239-2033</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4841,7 +4869,7 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>+1-347-909-1845 / +1 347-909-1845</t>
+          <t>+1 (347) 909-1845 / +1 (347) 909-1845</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4882,7 +4910,7 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>+1 732-300-9494 / +17323009494</t>
+          <t>+1 (732) 300-9494 / +1 (732) 300-9494</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5017,7 +5045,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>646-4525572</t>
+          <t>+1 (646) 452-5572</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5064,7 +5092,11 @@
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 574-9470</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
@@ -5074,7 +5106,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -5086,7 +5118,7 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5139,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>+972 54-205-0550 / 0527653301</t>
+          <t>+972 542050550 / +972 527653301</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5201,7 +5233,7 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 705-8635 / 718-258-1776</t>
+          <t>+1 (917) 705-8635 / +1 (718) 258-1776</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5602,7 +5634,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>+1 404-788-4308</t>
+          <t>+1 (404) 788-4308</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5647,7 +5679,7 @@
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>+97254-5280772</t>
+          <t>+972 545280772</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5700,7 +5732,7 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>054-848-0099</t>
+          <t>+972 548480099</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5741,7 +5773,7 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>+1 732-604-2669</t>
+          <t>+1 (732) 604-2669</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5827,7 +5859,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>054-311-0420</t>
+          <t>+972 543110420</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6146,7 +6178,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>+1917-274-9101</t>
+          <t>+1 (917) 274-9101</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -6228,7 +6260,7 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>+44 7968 156680</t>
+          <t>+447968156680</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6269,7 +6301,7 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>+17186648508</t>
+          <t>+1 (718) 664-8508</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6404,7 +6436,7 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>+1 917-991-3695</t>
+          <t>+1 (917) 991-3695</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6502,7 +6534,7 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>+1 718-813-5314</t>
+          <t>+1 (718) 813-5314</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6590,7 +6622,11 @@
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>055-674-0657 ::: +972 53-726-8037</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>aitanzacharin@gmail.com</t>
@@ -6604,7 +6640,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>מדויק</t>
+          <t>מדויק +טלפון</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -6614,7 +6650,11 @@
       </c>
       <c r="M127" s="2" t="inlineStr"/>
       <c r="N127" s="2" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>טלפון חובר לפי צליל</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6678,7 +6718,7 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>+1 773-274-1934</t>
+          <t>+1 (773) 274-1934</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6723,7 +6763,7 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>+1-917-968-8585 / 718-338-8282</t>
+          <t>+1 (917) 968-8585 / +1 (718) 338-8282</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6768,7 +6808,7 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>+18452167657</t>
+          <t>+1 (845) 216-7657</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6813,7 +6853,7 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2084552714</t>
+          <t>+1 (208) 455-2714</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6919,7 +6959,7 @@
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>212-609-3753 / +1 (917) 838-8333</t>
+          <t>+1 (212) 609-3753 / +1 (917) 838-8333</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6997,7 +7037,7 @@
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>+44 2085184848</t>
+          <t>+442085184848</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7087,7 +7127,7 @@
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>+1-917-301-7153</t>
+          <t>+1 (917) 301-7153</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7122,7 +7162,11 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 577-3284</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr">
@@ -7132,7 +7176,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -7144,7 +7188,7 @@
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7213,7 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>+1(347) 762-6766</t>
+          <t>+1 (347) 762-6766</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7292,7 +7336,7 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>+1 303-960-7393</t>
+          <t>+1 (303) 960-7393</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7337,7 +7381,7 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>+1 718-327-1214</t>
+          <t>+1 (718) 327-1214</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7382,7 +7426,7 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>+1-416-878-7609 / +1 416-878-7609 / 012-141-67429332</t>
+          <t>+1 (416) 878-7609 / +1 (416) 878-7609 / 012-141-67429332</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7435,7 +7479,7 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>+32 475 25 15 85</t>
+          <t>+32475251585</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7533,7 +7577,7 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>+1(917) 943-7479</t>
+          <t>+1 (917) 943-7479</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7676,7 +7720,7 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>+1 718-261-3446</t>
+          <t>+1 (718) 261-3446</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -7721,7 +7765,7 @@
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>+1 786-387-5307</t>
+          <t>+1 (786) 387-5307</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -7766,7 +7810,7 @@
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>718-338-5103</t>
+          <t>+1 (718) 338-5103</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -7805,7 +7849,11 @@
       <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>+32475251585</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
@@ -7815,7 +7863,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -7827,7 +7875,7 @@
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7896,7 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>+1 718-377-4603 / +17189867975</t>
+          <t>+1 (718) 377-4603 / +1 (718) 986-7975</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -7893,7 +7941,7 @@
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>+1-914-879-9761</t>
+          <t>+1 (914) 879-9761</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -8057,7 +8105,7 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>+1 212-724-2625</t>
+          <t>+1 (212) 724-2625</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8110,7 +8158,7 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>+1 718-677-7481</t>
+          <t>+1 (718) 677-7481</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8253,7 +8301,7 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>+19143565175 / +1 (917) 579-9290</t>
+          <t>+1 (914) 356-5175 / +1 (917) 579-9290</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8392,7 +8440,7 @@
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>+1 917-940-0866</t>
+          <t>+1 (917) 940-0866</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8747,7 +8795,7 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>+1 718-715-0794 / +19176130676</t>
+          <t>+1 (718) 715-0794 / +1 (917) 613-0676</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8970,7 +9018,11 @@
       <c r="D180" s="2" t="inlineStr"/>
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>+1 (516) 330-9971</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
@@ -8980,7 +9032,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -8992,7 +9044,7 @@
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9069,7 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>516-6339149 / 516-7737332</t>
+          <t>+1 (516) 633-9149 / +1 (516) 773-7332</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9062,7 +9114,7 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>+1 310-461-6173</t>
+          <t>+1 (310) 461-6173</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -9115,7 +9167,7 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>+1 289-597-1461 / +1 905-597-4901</t>
+          <t>+1 (289) 597-1461 / +1 (905) 597-4901</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9197,7 +9249,7 @@
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>+1 917-613-0355 / 1-718-252-3980 / 212-420-1910 / 718-207-9531</t>
+          <t>+1 (917) 613-0355 / +1 (718) 252-3980 / +1 (212) 420-1910 / +1 (718) 207-9531</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9242,7 +9294,7 @@
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>+1 347-768-1680</t>
+          <t>+1 (347) 768-1680</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9332,7 +9384,7 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>+1 516-484-7014</t>
+          <t>+1 (516) 484-7014</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9496,7 +9548,7 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>+19734777849</t>
+          <t>+1 (973) 477-7849</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9668,7 +9720,7 @@
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>516-4674557 / +191-75844901</t>
+          <t>+1 (516) 467-4557 / +1 (917) 584-4901</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9836,7 +9888,7 @@
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>+1 (732) 552-8425 / +1-212-869-4361</t>
+          <t>+1 (732) 552-8425 / +1 (212) 869-4361</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9881,7 +9933,7 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>+1 732-300-2672</t>
+          <t>+1 (732) 300-2672</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10008,7 +10060,7 @@
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>+1 917-399-5315</t>
+          <t>+1 (917) 399-5315</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10098,7 +10150,7 @@
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>+1 374-541-3163 / +13475413163</t>
+          <t>+1 (374) 541-3163 / +1 (347) 541-3163</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10184,7 +10236,7 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>+1 917-499-5135</t>
+          <t>+1 (917) 499-5135</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -10266,7 +10318,7 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>+1 (786) 241-7650 / +972557291421</t>
+          <t>+1 (786) 241-7650 / +972 557291421</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10368,7 +10420,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>+1 516-724-3428</t>
+          <t>+1 (516) 724-3428</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10409,7 +10461,7 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>+1 973-851-4335 / +1 973-471-3127</t>
+          <t>+1 (973) 851-4335 / +1 (973) 471-3127</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10628,7 +10680,11 @@
       <c r="D218" s="2" t="inlineStr"/>
       <c r="E218" s="2" t="inlineStr"/>
       <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 399-5315</t>
+        </is>
+      </c>
       <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="2" t="inlineStr"/>
       <c r="J218" s="2" t="inlineStr">
@@ -10638,7 +10694,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -10650,7 +10706,7 @@
       <c r="N218" s="2" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10725,11 @@
       <c r="D219" s="2" t="inlineStr"/>
       <c r="E219" s="2" t="inlineStr"/>
       <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 399-5315</t>
+        </is>
+      </c>
       <c r="H219" s="2" t="inlineStr"/>
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
@@ -10679,7 +10739,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -10691,7 +10751,7 @@
       <c r="N219" s="2" t="inlineStr"/>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10854,7 @@
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>+19172976782</t>
+          <t>+1 (917) 297-6782</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -10839,7 +10899,7 @@
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>+1516-263-6660</t>
+          <t>+1 (516) 263-6660</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -10884,7 +10944,7 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>02-6725466 / 054-8460330 / +972 54-569-9070</t>
+          <t>+972 26725466 / +972 548460330 / +972 545699070</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10929,7 +10989,7 @@
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>+16469635777</t>
+          <t>+1 (646) 963-5777</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11056,7 +11116,7 @@
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>+1 484-716-5637</t>
+          <t>+1 (484) 716-5637</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11101,7 +11161,7 @@
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>+1 917-346-3742</t>
+          <t>+1 (917) 346-3742</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11349,7 @@
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>+1718-261-3446</t>
+          <t>+1 (718) 261-3446</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11338,7 +11398,7 @@
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>0585164585 / +97226732467 / +972542120882</t>
+          <t>+972 585164585 / +972 26732467 / +972 542120882</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11391,7 +11451,7 @@
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>191-74996125 / 1-718-336-6866</t>
+          <t>+1 (917) 499-6125 / +1 (718) 336-6866</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11432,7 +11492,7 @@
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>+972 52-768-0481</t>
+          <t>+972 527680481</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
@@ -11522,7 +11582,7 @@
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>02-999-3876</t>
+          <t>+972 29993876</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -11561,7 +11621,11 @@
       <c r="D239" s="2" t="inlineStr"/>
       <c r="E239" s="2" t="inlineStr"/>
       <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 714-5476</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr"/>
       <c r="I239" s="2" t="inlineStr"/>
       <c r="J239" s="2" t="inlineStr">
@@ -11571,7 +11635,7 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L239" s="2" t="inlineStr">
@@ -11583,7 +11647,7 @@
       <c r="N239" s="2" t="inlineStr"/>
       <c r="O239" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -11641,7 +11705,7 @@
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>+13123153707</t>
+          <t>+1 (312) 315-3707</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -11719,7 +11783,7 @@
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>0548-431-861 / +1 845-826-3721</t>
+          <t>+972 548431861 / +1 (845) 826-3721</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -11870,7 +11934,7 @@
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>1-732-901-7783</t>
+          <t>+1 (732) 901-7783</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -11915,7 +11979,7 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>718-253-8633 / +1 (917) 613-2965</t>
+          <t>+1 (718) 253-8633 / +1 (917) 613-2965</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -11960,7 +12024,7 @@
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>+1 718-471-1626</t>
+          <t>+1 (718) 471-1626</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12017,7 +12081,7 @@
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 370-9063 / 718-376-3903</t>
+          <t>+1 (917) 370-9063 / +1 (718) 376-3903</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12152,7 +12216,7 @@
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>+19172077397</t>
+          <t>+1 (917) 207-7397</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12328,7 +12392,7 @@
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>+1 917-202-8974</t>
+          <t>+1 (917) 202-8974</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12373,7 +12437,7 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>+1 917-855-9214</t>
+          <t>+1 (917) 855-9214</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12496,7 +12560,7 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>+1 718-368-0181 / +19175209278</t>
+          <t>+1 (718) 368-0181 / +1 (917) 520-9278</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12578,7 +12642,7 @@
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>718-3758210 / +1 (718) 755-2333</t>
+          <t>+1 (718) 375-8210 / +1 (718) 755-2333</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -12705,7 +12769,7 @@
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>+17322995142</t>
+          <t>+1 (732) 299-5142</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -12746,7 +12810,7 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>718-5964242 / 917-3098354</t>
+          <t>+1 (718) 596-4242 / +1 (917) 309-8354</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -12992,7 +13056,7 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>+1 646-642-3447</t>
+          <t>+1 (646) 642-3447</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13172,7 +13236,7 @@
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>+1 914-582-0999</t>
+          <t>+1 (914) 582-0999</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13295,7 +13359,7 @@
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>+12148970147</t>
+          <t>+1 (214) 897-0147</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13381,7 +13445,7 @@
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>+1 818 3196124</t>
+          <t>+1 (818) 319-6124</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13500,7 +13564,7 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>718-8516069 / 718-8514416</t>
+          <t>+1 (718) 851-6069 / +1 (718) 851-4416</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13594,7 +13658,7 @@
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>+1516510-1478</t>
+          <t>+1 (516) 510-1478</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13647,7 +13711,7 @@
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>054-569-1160</t>
+          <t>+972 545691160</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -13682,7 +13746,11 @@
       <c r="D288" s="2" t="inlineStr"/>
       <c r="E288" s="2" t="inlineStr"/>
       <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>+972 545691160</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr"/>
       <c r="J288" s="2" t="inlineStr">
@@ -13692,7 +13760,7 @@
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L288" s="2" t="inlineStr">
@@ -13704,7 +13772,7 @@
       <c r="N288" s="2" t="inlineStr"/>
       <c r="O288" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13797,7 @@
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>1917-873-1342 / +1 (917) 873-1342</t>
+          <t>+1 (917) 873-1342 / +1 (917) 873-1342</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -13774,7 +13842,7 @@
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>+1 917-763-5836</t>
+          <t>+1 (917) 763-5836</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -13813,7 +13881,11 @@
       <c r="D291" s="2" t="inlineStr"/>
       <c r="E291" s="2" t="inlineStr"/>
       <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>1917-873-1342 ::: +1 (917) 873-1342</t>
+        </is>
+      </c>
       <c r="H291" s="2" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr"/>
       <c r="J291" s="2" t="inlineStr">
@@ -13823,7 +13895,7 @@
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
-          <t>אושר: חדש</t>
+          <t>אושר: חדש +טלפון</t>
         </is>
       </c>
       <c r="L291" s="2" t="inlineStr">
@@ -13835,7 +13907,7 @@
       <c r="N291" s="2" t="inlineStr"/>
       <c r="O291" s="2" t="inlineStr">
         <is>
-          <t>תורם חדש (אושר ידנית)</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -13987,7 +14059,7 @@
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>058-422-748 / 845-5588902</t>
+          <t>+972 58422748 / +1 (845) 558-8902</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14040,7 +14112,7 @@
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>+1 845-548-5514</t>
+          <t>+1 (845) 548-5514</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14085,7 +14157,7 @@
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>1 917-753-1628</t>
+          <t>+1 (917) 753-1628</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14175,7 +14247,7 @@
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>+13476809514</t>
+          <t>+1 (347) 680-9514</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14269,7 +14341,7 @@
       <c r="F301" s="2" t="inlineStr"/>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>+972 50-974-8815</t>
+          <t>+972 509748815</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14310,7 +14382,7 @@
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>+191 76965 109</t>
+          <t>+1 (917) 696-5109</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14355,7 +14427,7 @@
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 613-6767 / +1 718-627-0558</t>
+          <t>+1 (917) 613-6767 / +1 (718) 627-0558</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14445,7 +14517,7 @@
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>+1 917-755-5383</t>
+          <t>+1 (917) 755-5383</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr"/>
@@ -14482,7 +14554,7 @@
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>+1 647-863-3623</t>
+          <t>+1 (647) 863-3623</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -14560,7 +14632,7 @@
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>+44 7792 695845</t>
+          <t>+447792695845</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr"/>
@@ -14605,7 +14677,7 @@
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>+972 52-717-5049 / +972 55-993-4072</t>
+          <t>+972 527175049 / +972 559934072</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr"/>
@@ -14654,7 +14726,7 @@
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>+1-773-508-0086 / +1 773-425-7861 / +1 (773) 969-3227</t>
+          <t>+1 (773) 508-0086 / +1 (773) 425-7861 / +1 (773) 969-3227</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14703,7 +14775,7 @@
       <c r="F311" s="2" t="inlineStr"/>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>+1 516-371-6118</t>
+          <t>+1 (516) 371-6118</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14801,7 +14873,7 @@
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>+19179036260</t>
+          <t>+1 (917) 903-6260</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14854,7 +14926,7 @@
       <c r="F314" s="2" t="inlineStr"/>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>+1 848-300-0303</t>
+          <t>+1 (848) 300-0303</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -14936,7 +15008,7 @@
       <c r="F316" s="2" t="inlineStr"/>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>+1 786-779-6120</t>
+          <t>+1 (786) 779-6120</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -14981,7 +15053,7 @@
       <c r="F317" s="2" t="inlineStr"/>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>+972 58-461-3200</t>
+          <t>+972 584613200</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15030,7 +15102,7 @@
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>718-252-5454</t>
+          <t>+1 (718) 252-5454</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15112,7 +15184,7 @@
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>+1 917-757-2523</t>
+          <t>+1 (917) 757-2523</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15268,7 +15340,7 @@
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>+972526802149</t>
+          <t>+972 526802149</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr"/>
@@ -15485,7 +15557,7 @@
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>+1 574-383-0723</t>
+          <t>+1 (574) 383-0723</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15636,7 +15708,7 @@
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>+1 954-289-2350</t>
+          <t>+1 (954) 289-2350</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -15849,7 +15921,7 @@
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>+972522752299</t>
+          <t>+972 522752299</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -15894,7 +15966,7 @@
       <c r="F338" s="2" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>+972 52-309-0654 / +1 917-605-4140</t>
+          <t>+972 523090654 / +1 (917) 605-4140</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15943,7 +16015,7 @@
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>+1 917-841-7950</t>
+          <t>+1 (917) 841-7950</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -15996,7 +16068,7 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>+1 410-654-3500 / +1 (443) 414-6432</t>
+          <t>+1 (410) 654-3500 / +1 (443) 414-6432</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16086,7 +16158,7 @@
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>052-302-8080</t>
+          <t>+972 523028080</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -16139,7 +16211,7 @@
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>+1 347-244-52</t>
+          <t>+134724452</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -16184,7 +16256,7 @@
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>1-845-304-2244</t>
+          <t>+1 (845) 304-2244</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16270,7 +16342,7 @@
       <c r="F346" s="2" t="inlineStr"/>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>+1732-3061356</t>
+          <t>+1 (732) 306-1356</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -16323,7 +16395,7 @@
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>+1 718-338-0362 / +1 917-568-2968</t>
+          <t>+1 (718) 338-0362 / +1 (917) 568-2968</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -16405,7 +16477,7 @@
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>+972502193527 / +972 502193527 / +17187579915</t>
+          <t>+972 502193527 / +972 502193527 / +1 (718) 757-9915</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16458,7 +16530,7 @@
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>+1 646-296-5035</t>
+          <t>+1 (646) 296-5035</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16503,7 +16575,7 @@
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>+972 54-588-5573</t>
+          <t>+972 545885573</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -16552,7 +16624,7 @@
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>054-846-1629</t>
+          <t>+972 548461629</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -16728,7 +16800,7 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 587-6283 / 516-371-3672</t>
+          <t>+1 (917) 587-6283 / +1 (516) 371-3672</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr"/>
@@ -16777,7 +16849,7 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>+1 347 576 3770</t>
+          <t>+1 (347) 576-3770</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -16863,7 +16935,7 @@
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>(718) 253-9856 / +1917 846-6162 / 001 718-309-7999</t>
+          <t>+1 (718) 253-9856 / +1 (917) 846-6162 / +1 (718) 309-7999</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -16908,7 +16980,7 @@
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>+1917750-8422</t>
+          <t>+1 (917) 750-8422</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -16947,7 +17019,11 @@
       <c r="D361" s="2" t="inlineStr"/>
       <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" s="2" t="inlineStr"/>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 750-8422</t>
+        </is>
+      </c>
       <c r="H361" s="2" t="inlineStr"/>
       <c r="I361" s="2" t="inlineStr"/>
       <c r="J361" s="2" t="inlineStr">
@@ -16957,7 +17033,7 @@
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L361" s="2" t="inlineStr">
@@ -16969,7 +17045,7 @@
       <c r="N361" s="2" t="inlineStr"/>
       <c r="O361" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -17039,7 +17115,7 @@
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 697-6540 / (718) 258-7343</t>
+          <t>+1 (917) 697-6540 / +1 (718) 258-7343</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -17129,7 +17205,7 @@
       <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>052-8739781</t>
+          <t>+972 528739781</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -17170,7 +17246,7 @@
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>+19175431178</t>
+          <t>+1 (917) 543-1178</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17436,7 +17512,7 @@
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>+1 516 5091544</t>
+          <t>+1 (516) 509-1544</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17567,7 +17643,7 @@
       <c r="F375" s="2" t="inlineStr"/>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>+18482245504</t>
+          <t>+1 (848) 224-5504</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
@@ -17653,7 +17729,7 @@
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>+1 718-419-1651 / 347 372 7254</t>
+          <t>+1 (718) 419-1651 / +1 (347) 372-7254</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
@@ -17706,7 +17782,7 @@
       <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>+1 917-474-9784 / 1-718-758-9007</t>
+          <t>+1 (917) 474-9784 / +1 (718) 758-9007</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
@@ -17919,7 +17995,7 @@
       <c r="F383" s="2" t="inlineStr"/>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>+32  489 79 12 95</t>
+          <t>+32489791295</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
@@ -17960,7 +18036,7 @@
       <c r="F384" s="2" t="inlineStr"/>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>+32 489 79 12 95</t>
+          <t>+32489791295</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr"/>
@@ -18009,7 +18085,7 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>+1 917-627-4972</t>
+          <t>+1 (917) 627-4972</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -18050,7 +18126,7 @@
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>+1 212-420-1999 / +1 718-252-5005 / +1 917-613-0192</t>
+          <t>+1 (212) 420-1999 / +1 (718) 252-5005 / +1 (917) 613-0192</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -18095,7 +18171,7 @@
       <c r="F387" s="2" t="inlineStr"/>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>+1 646-755-1949</t>
+          <t>+1 (646) 755-1949</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
@@ -18136,7 +18212,7 @@
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>+19175791944</t>
+          <t>+1 (917) 579-1944</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr"/>
@@ -18185,7 +18261,7 @@
       <c r="F389" s="2" t="inlineStr"/>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>+1 847-287-4758</t>
+          <t>+1 (847) 287-4758</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -18320,7 +18396,7 @@
       <c r="F392" s="2" t="inlineStr"/>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>+1 718-951-1088 / +1 (917) 922-0029</t>
+          <t>+1 (718) 951-1088 / +1 (917) 922-0029</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
@@ -18373,7 +18449,7 @@
       <c r="F393" s="2" t="inlineStr"/>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>+1 914-633-7171</t>
+          <t>+1 (914) 633-7171</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -18463,7 +18539,7 @@
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>+1 (416) 219-8391 / 416-2226362</t>
+          <t>+1 (416) 219-8391 / +1 (416) 222-6362</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18733,7 +18809,7 @@
       <c r="F401" s="2" t="inlineStr"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>+1 (845) 418-6138 / +1 347-556-4597</t>
+          <t>+1 (845) 418-6138 / +1 (347) 556-4597</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -18999,7 +19075,7 @@
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>+1 917-923-2412</t>
+          <t>+1 (917) 923-2412</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19040,7 +19116,7 @@
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>+19177760967 / +19177760967</t>
+          <t>+1 (917) 776-0967 / +1 (917) 776-0967</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr"/>
@@ -19085,7 +19161,7 @@
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>+1 917-703-1783</t>
+          <t>+1 (917) 703-1783</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -19208,7 +19284,7 @@
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>+1 917-270-8913</t>
+          <t>+1 (917) 270-8913</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19290,7 +19366,7 @@
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>+1 213-798-2409</t>
+          <t>+1 (213) 798-2409</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -19540,7 +19616,7 @@
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>+1 917-846-0730</t>
+          <t>+1 (917) 846-0730</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -19745,7 +19821,7 @@
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>+1 718-339-2468</t>
+          <t>+1 (718) 339-2468</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19790,7 +19866,7 @@
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>+1-718-755-0369</t>
+          <t>+1 (718) 755-0369</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -19917,7 +19993,7 @@
       <c r="F429" s="2" t="inlineStr"/>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>+1 347-409-5061 / 012-121-22021695 / 718-253-5497</t>
+          <t>+1 (347) 409-5061 / 012-121-22021695 / +1 (718) 253-5497</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -19970,7 +20046,7 @@
       <c r="F430" s="2" t="inlineStr"/>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>+17323631817 / +1 (484) 680-0768</t>
+          <t>+1 (732) 363-1817 / +1 (484) 680-0768</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -20064,7 +20140,7 @@
       <c r="F432" s="2" t="inlineStr"/>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>053-5203285</t>
+          <t>+972 535203285</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
@@ -20193,7 +20269,7 @@
       <c r="F435" s="2" t="inlineStr"/>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>+1 857-234-6666</t>
+          <t>+1 (857) 234-6666</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -20324,7 +20400,7 @@
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>+1 646-712-9409</t>
+          <t>+1 (646) 712-9409</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
@@ -20369,7 +20445,7 @@
       <c r="F439" s="2" t="inlineStr"/>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>+14167819175</t>
+          <t>+1 (416) 781-9175</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -20410,7 +20486,7 @@
       <c r="F440" s="2" t="inlineStr"/>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>9087834354</t>
+          <t>+1 (908) 783-4354</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -20508,7 +20584,7 @@
       <c r="F442" s="2" t="inlineStr"/>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>+1 347-865-2361</t>
+          <t>+1 (347) 865-2361</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -20598,7 +20674,7 @@
       <c r="F444" s="2" t="inlineStr"/>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>+17322676746</t>
+          <t>+1 (732) 267-6746</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -20639,7 +20715,7 @@
       <c r="F445" s="2" t="inlineStr"/>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>+1 917-299-2819</t>
+          <t>+1 (917) 299-2819</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -20905,7 +20981,7 @@
       <c r="F451" s="2" t="inlineStr"/>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>+1 917-299-2819</t>
+          <t>+1 (917) 299-2819</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -21007,7 +21083,7 @@
       <c r="F453" s="2" t="inlineStr"/>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>+972 58-523-0476</t>
+          <t>+972 585230476</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21189,7 @@
       <c r="F455" s="2" t="inlineStr"/>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>+1 347-263-3294</t>
+          <t>+1 (347) 263-3294</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -21240,7 +21316,7 @@
       <c r="F458" s="2" t="inlineStr"/>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>+1 347-266-7998</t>
+          <t>+1 (347) 266-7998</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -21449,7 +21525,7 @@
       <c r="F463" s="2" t="inlineStr"/>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>+1-314-973-2914</t>
+          <t>+1 (314) 973-2914</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -21498,7 +21574,7 @@
       <c r="F464" s="2" t="inlineStr"/>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>+1 314-973-2914</t>
+          <t>+1 (314) 973-2914</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -21543,7 +21619,7 @@
       <c r="F465" s="2" t="inlineStr"/>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>+1 (773) 505-8825 / 00 1 773-897-9227</t>
+          <t>+1 (773) 505-8825 / +1 (773) 897-9227</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -21588,7 +21664,7 @@
       <c r="F466" s="2" t="inlineStr"/>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>+1 845-641-0892</t>
+          <t>+1 (845) 641-0892</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -21633,7 +21709,7 @@
       <c r="F467" s="2" t="inlineStr"/>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>+1 516-423-0575</t>
+          <t>+1 (516) 423-0575</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -21821,7 +21897,7 @@
       <c r="F471" s="2" t="inlineStr"/>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>+1 416-782-5662</t>
+          <t>+1 (416) 782-5662</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -21915,7 +21991,7 @@
       <c r="F473" s="2" t="inlineStr"/>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>+1 516-610-5047</t>
+          <t>+1 (516) 610-5047</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -21972,7 +22048,7 @@
       <c r="F474" s="2" t="inlineStr"/>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>+972 54-668-4600</t>
+          <t>+972 546684600</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
@@ -22107,7 +22183,7 @@
       <c r="F477" s="2" t="inlineStr"/>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>718-290-5182</t>
+          <t>+1 (718) 290-5182</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -22422,7 +22498,7 @@
       <c r="F484" s="2" t="inlineStr"/>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>+1 316-648-9188</t>
+          <t>+1 (316) 648-9188</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22463,7 +22539,7 @@
       <c r="F485" s="2" t="inlineStr"/>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>054-8455843</t>
+          <t>+972 548455843</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr"/>
@@ -22512,7 +22588,7 @@
       <c r="F486" s="2" t="inlineStr"/>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>(516) 295-3181 / +1 (516) 633-3548</t>
+          <t>+1 (516) 295-3181 / +1 (516) 633-3548</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -22594,7 +22670,7 @@
       <c r="F488" s="2" t="inlineStr"/>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>+16092870283</t>
+          <t>+1 (609) 287-0283</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -22643,7 +22719,7 @@
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>+1 917-655-4431</t>
+          <t>+1 (917) 655-4431</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -22813,7 +22889,11 @@
       <c r="D493" s="2" t="inlineStr"/>
       <c r="E493" s="2" t="inlineStr"/>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>+1 (917) 655-4431</t>
+        </is>
+      </c>
       <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr"/>
       <c r="J493" s="2" t="inlineStr">
@@ -22823,7 +22903,7 @@
       </c>
       <c r="K493" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל</t>
+          <t>מהקוויטל +טלפון</t>
         </is>
       </c>
       <c r="L493" s="2" t="inlineStr">
@@ -22835,7 +22915,7 @@
       <c r="N493" s="2" t="inlineStr"/>
       <c r="O493" s="2" t="inlineStr">
         <is>
-          <t>מהקוויטל — אין טלפון עדיין</t>
+          <t>טלפון חובר לפי צליל</t>
         </is>
       </c>
     </row>
@@ -22975,7 +23055,7 @@
       <c r="F497" s="2" t="inlineStr"/>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>+1 917-572-8674</t>
+          <t>+1 (917) 572-8674</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
@@ -23016,7 +23096,7 @@
       <c r="F498" s="2" t="inlineStr"/>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>(718) 377-5304 / +1 (917) 929-2101</t>
+          <t>+1 (718) 377-5304 / +1 (917) 929-2101</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
@@ -23061,7 +23141,7 @@
       <c r="F499" s="2" t="inlineStr"/>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>+1917359-3480</t>
+          <t>+1 (917) 359-3480</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
@@ -23143,7 +23223,7 @@
       <c r="F501" s="2" t="inlineStr"/>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>+1 613-798-6249</t>
+          <t>+1 (613) 798-6249</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
@@ -23311,7 +23391,7 @@
       <c r="F505" s="2" t="inlineStr"/>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>1 718-763-7274 / +1 917-626-5488 / +1 (917) 968-0235</t>
+          <t>+1 (718) 763-7274 / +1 (917) 626-5488 / +1 (917) 968-0235</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
@@ -23356,7 +23436,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>+56 9 8824 3863 / +1 (302) 390-3926</t>
+          <t>+56988243863 / +1 (302) 390-3926</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23446,7 +23526,7 @@
       <c r="F508" s="2" t="inlineStr"/>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>+1 484-272-7910</t>
+          <t>+1 (484) 272-7910</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23577,7 +23657,7 @@
       <c r="F511" s="2" t="inlineStr"/>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>00 1 888-850-4273 / 00 1 917-518-5353</t>
+          <t>+1 (888) 850-4273 / +1 (917) 518-5353</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
@@ -23745,7 +23825,7 @@
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>+1 416-356-4966</t>
+          <t>+1 (416) 356-4966</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -23827,7 +23907,7 @@
       <c r="F517" s="2" t="inlineStr"/>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>+1 516-528-2421 / +1 (516) 203-8382</t>
+          <t>+1 (516) 528-2421 / +1 (516) 203-8382</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -24118,7 +24198,7 @@
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>+1 561-302-6779</t>
+          <t>+1 (561) 302-6779</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">
@@ -24163,7 +24243,7 @@
       <c r="F525" s="2" t="inlineStr"/>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>917-2389393</t>
+          <t>+1 (917) 238-9393</t>
         </is>
       </c>
       <c r="H525" s="2" t="inlineStr">
@@ -24208,7 +24288,7 @@
       <c r="F526" s="2" t="inlineStr"/>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>077-5412540</t>
+          <t>+972 775412540</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr">
@@ -24425,7 +24505,7 @@
       <c r="F531" s="2" t="inlineStr"/>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>845-5218126</t>
+          <t>+1 (845) 521-8126</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
@@ -24470,7 +24550,7 @@
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>+1 347-262-2123 / +1-347-262-2123</t>
+          <t>+1 (347) 262-2123 / +1 (347) 262-2123</t>
         </is>
       </c>
       <c r="H532" s="2" t="inlineStr">
@@ -24556,7 +24636,7 @@
       <c r="F534" s="2" t="inlineStr"/>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>1 718-263-5517 / +19177056936</t>
+          <t>+1 (718) 263-5517 / +1 (917) 705-6936</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24609,7 +24689,7 @@
       <c r="F535" s="2" t="inlineStr"/>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>+1 312-719-7552 / +972 53-928-3632 / +1561-302-6779</t>
+          <t>+1 (312) 719-7552 / +972 539283632 / +1 (561) 302-6779</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24699,7 +24779,7 @@
       <c r="F537" s="2" t="inlineStr"/>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>+1 (310) 435-3080 / +13107537950</t>
+          <t>+1 (310) 435-3080 / +1 (310) 753-7950</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24744,7 +24824,7 @@
       <c r="F538" s="2" t="inlineStr"/>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>+1 848-240-2913 / +17322795635</t>
+          <t>+1 (848) 240-2913 / +1 (732) 279-5635</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
@@ -24830,7 +24910,7 @@
       <c r="F540" s="2" t="inlineStr"/>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>647-7610174</t>
+          <t>+1 (647) 761-0174</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24875,7 +24955,7 @@
       <c r="F541" s="2" t="inlineStr"/>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>+1 650-703-1237</t>
+          <t>+1 (650) 703-1237</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25002,7 +25082,7 @@
       <c r="F544" s="2" t="inlineStr"/>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>+1 516-305-9739 / +15165691978</t>
+          <t>+1 (516) 305-9739 / +1 (516) 569-1978</t>
         </is>
       </c>
       <c r="H544" s="2" t="inlineStr">
@@ -25088,7 +25168,7 @@
       <c r="F546" s="2" t="inlineStr"/>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>+1 732-317-2673 / +19732627186</t>
+          <t>+1 (732) 317-2673 / +1 (973) 262-7186</t>
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr">
@@ -25133,7 +25213,7 @@
       <c r="F547" s="2" t="inlineStr"/>
       <c r="G547" s="2" t="inlineStr">
         <is>
-          <t>+1 954-289-1662</t>
+          <t>+1 (954) 289-1662</t>
         </is>
       </c>
       <c r="H547" s="2" t="inlineStr">
@@ -25215,7 +25295,7 @@
       <c r="F549" s="2" t="inlineStr"/>
       <c r="G549" s="2" t="inlineStr">
         <is>
-          <t>+44 7577 332072 / +4407340662802 / 013 44 7554 567733</t>
+          <t>+447577332072 / +4407340662802 / 013 44 7554 567733</t>
         </is>
       </c>
       <c r="H549" s="2" t="inlineStr">
@@ -25313,7 +25393,7 @@
       <c r="F551" s="2" t="inlineStr"/>
       <c r="G551" s="2" t="inlineStr">
         <is>
-          <t>+1 917-692-2872</t>
+          <t>+1 (917) 692-2872</t>
         </is>
       </c>
       <c r="H551" s="2" t="inlineStr">
@@ -25358,7 +25438,7 @@
       <c r="F552" s="2" t="inlineStr"/>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>+44514 826 3015</t>
+          <t>+445148263015</t>
         </is>
       </c>
       <c r="H552" s="2" t="inlineStr">
@@ -25407,7 +25487,7 @@
       <c r="F553" s="2" t="inlineStr"/>
       <c r="G553" s="2" t="inlineStr">
         <is>
-          <t>+1 718-637-3464</t>
+          <t>+1 (718) 637-3464</t>
         </is>
       </c>
       <c r="H553" s="2" t="inlineStr">
@@ -25501,7 +25581,7 @@
       <c r="F555" s="2" t="inlineStr"/>
       <c r="G555" s="2" t="inlineStr">
         <is>
-          <t>+17183389023</t>
+          <t>+1 (718) 338-9023</t>
         </is>
       </c>
       <c r="H555" s="2" t="inlineStr">
@@ -25599,7 +25679,7 @@
       <c r="F557" s="2" t="inlineStr"/>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>+1 718-763-1333 / +1 718-968-8650 / +1 (917) 662-0381</t>
+          <t>+1 (718) 763-1333 / +1 (718) 968-8650 / +1 (917) 662-0381</t>
         </is>
       </c>
       <c r="H557" s="2" t="inlineStr">
@@ -25771,7 +25851,7 @@
       <c r="F561" s="2" t="inlineStr"/>
       <c r="G561" s="2" t="inlineStr">
         <is>
-          <t>+1 917-589-1661</t>
+          <t>+1 (917) 589-1661</t>
         </is>
       </c>
       <c r="H561" s="2" t="inlineStr">
@@ -25824,7 +25904,7 @@
       <c r="F562" s="2" t="inlineStr"/>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>+1 917-995-6888</t>
+          <t>+1 (917) 995-6888</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -26045,7 +26125,7 @@
       <c r="F567" s="2" t="inlineStr"/>
       <c r="G567" s="2" t="inlineStr">
         <is>
-          <t>+1 917-603-0982 / +1 732-555-1212 / +1 732-555-1212</t>
+          <t>+1 (917) 603-0982 / +1 (732) 555-1212 / +1 (732) 555-1212</t>
         </is>
       </c>
       <c r="H567" s="2" t="inlineStr">
@@ -26102,7 +26182,7 @@
       <c r="F568" s="2" t="inlineStr"/>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>+44 7941 237928</t>
+          <t>+447941237928</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26147,7 +26227,7 @@
       <c r="F569" s="2" t="inlineStr"/>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>+13479490002</t>
+          <t>+1 (347) 949-0002</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26237,7 +26317,7 @@
       <c r="F571" s="2" t="inlineStr"/>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>+1 213-842-9207</t>
+          <t>+1 (213) 842-9207</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
@@ -26409,7 +26489,7 @@
       <c r="F575" s="2" t="inlineStr"/>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>+17185518636 / +1 718-528-3700 / +1 718-528-3809</t>
+          <t>+1 (718) 551-8636 / +1 (718) 528-3700 / +1 (718) 528-3809</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
@@ -26544,7 +26624,7 @@
       <c r="F578" s="2" t="inlineStr"/>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>+1 (917) 825-4336 / +972 53-317-8430</t>
+          <t>+1 (917) 825-4336 / +972 533178430</t>
         </is>
       </c>
       <c r="H578" s="2" t="inlineStr">
@@ -26671,7 +26751,7 @@
       <c r="F581" s="2" t="inlineStr"/>
       <c r="G581" s="2" t="inlineStr">
         <is>
-          <t>347-806-4020 / 7183843717</t>
+          <t>+1 (347) 806-4020 / +1 (718) 384-3717</t>
         </is>
       </c>
       <c r="H581" s="2" t="inlineStr">
@@ -26761,7 +26841,7 @@
       <c r="F583" s="2" t="inlineStr"/>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>+1 773-338-3468</t>
+          <t>+1 (773) 338-3468</t>
         </is>
       </c>
       <c r="H583" s="2" t="inlineStr">
@@ -26806,7 +26886,7 @@
       <c r="F584" s="2" t="inlineStr"/>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>0527601526</t>
+          <t>+972 527601526</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr">
@@ -26925,7 +27005,7 @@
       <c r="F587" s="2" t="inlineStr"/>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>718-2367342 / +1 (917) 699-5336</t>
+          <t>+1 (718) 236-7342 / +1 (917) 699-5336</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr"/>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -3896,7 +3896,7 @@
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>+1 / +1 917-754-6634</t>
+          <t>+1 917-754-6634</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3947,11 +3947,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>sbrody11211@yahoo.com</t>
@@ -4002,7 +3998,7 @@
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+1 374-541-3163 / +1 347-541-3163</t>
+          <t>+1 347-541-3163</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4135,11 +4131,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>rlb6723@hotmail.com</t>
@@ -6406,7 +6398,7 @@
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>+1 917-943-6381 / +1 917-943-6381</t>
+          <t>+1 917-943-6381</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -7201,11 +7193,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>PinchasGarf@aol.com</t>
@@ -11301,11 +11289,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr"/>
       <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
           <t>rac1836@yahoo.com.br</t>
@@ -13163,7 +13147,7 @@
       <c r="E273" s="2" t="inlineStr"/>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>+1 917-603-0982 / +1 732-555-1212 / +1 732-555-1212</t>
+          <t>+1 917-603-0982 / +1 732-555-1212</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -13363,7 +13347,7 @@
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>+1 917-701-7148 / +1 917-701-7148</t>
+          <t>+1 917-701-7148</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr"/>
@@ -14578,7 +14562,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>לינאם</t>
+          <t>ליניאם</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -14590,17 +14574,17 @@
       <c r="E304" s="2" t="inlineStr"/>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>+1 / +1 214-897-0147</t>
+          <t>+1 214-897-0147</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>tannerlynam@me.com</t>
+          <t>pineanddeer@gmail.com</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>110 Park Ln, Lewisville, TX 75077-8221, US</t>
+          <t>1005 Lake Bluff Dr, Flower Mound, TX 75028-7225, US</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
@@ -14943,7 +14927,7 @@
       <c r="E311" s="2" t="inlineStr"/>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>+1 347-262-2123 / +1 347-262-2123</t>
+          <t>+1 347-262-2123</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
@@ -19015,7 +18999,7 @@
       <c r="E399" s="2" t="inlineStr"/>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>+1 917-776-0967 / +1 917-776-0967</t>
+          <t>+1 917-776-0967</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr"/>
@@ -20286,7 +20270,7 @@
       <c r="E426" s="2" t="inlineStr"/>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>+1 732-239-2033 / +1 732-239-2033 / +1 732-239-2033</t>
+          <t>+1 732-239-2033</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -21116,7 +21100,7 @@
       <c r="E444" s="2" t="inlineStr"/>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>+972 502193527 / +972 502193527 / +1 718-757-9915</t>
+          <t>+972 502193527 / +1 718-757-9915</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
@@ -21423,7 +21407,7 @@
       <c r="E451" s="2" t="inlineStr"/>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>+1 416-878-7609 / +1 416-878-7609 / 012-141-67429332</t>
+          <t>+1 416-878-7609 / 012-141-67429332</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -21962,7 +21946,7 @@
       <c r="E462" s="2" t="inlineStr"/>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>+1 347-909-1845 / +1 347-909-1845</t>
+          <t>+1 347-909-1845</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
@@ -22800,7 +22784,7 @@
       <c r="E480" s="2" t="inlineStr"/>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>+1 732-300-9494 / +1 732-300-9494</t>
+          <t>+1 732-300-9494</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
@@ -24955,11 +24939,7 @@
       </c>
       <c r="D528" s="2" t="inlineStr"/>
       <c r="E528" s="2" t="inlineStr"/>
-      <c r="F528" s="2" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr">
         <is>
           <t>baruchsebat@gmail.com</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -684,12 +684,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>שותפות יששכר-זבולון</t>
+          <t>שותפות יששכר-זבולון + נוסף</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -743,7 +743,11 @@
           <t>לאה</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>shraege Abramowitz</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
@@ -752,12 +756,36 @@
           <t>3406 Kings highwayBrooklyn, N.Y 11234, U.S.A</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -1022,27 +1050,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>חודשי</t>
+          <t>חודשי + נוסף</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>העברה_בנקאית</t>
+          <t>צק</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>שולם 6 חודשים, 1 נדחו</t>
+          <t>שולם 6 חודשים</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>יולי</t>
+          <t>יוני</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1993,7 +2021,11 @@
           <t>אברהם משה יוסף</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Alan Irni</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2010,12 +2042,36 @@
           <t>Unit B 2846 W Touhy Ave, Chicago, IL 60645, US</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -2209,7 +2265,11 @@
           <t>ברוך</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Baruch Amzel</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2218,12 +2278,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -2311,7 +2395,11 @@
           <t>שלום ורבקי</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Shalom &amp; Rivkah Antin</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
@@ -2320,12 +2408,36 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -2905,7 +3017,11 @@
           <t>אסתר</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>esther Baum</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2922,12 +3038,36 @@
           <t>Korte Leemstraat 13, 2018 Antwerpen, BE</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -3121,17 +3261,45 @@
           <t>נפתלי</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Buchinger</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>שולם 5 חודשים</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -3806,7 +3974,11 @@
           <t>יצחק</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Steven Blisko</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3823,12 +3995,36 @@
           <t>2649 W Jarlath St, Chicago, IL 60645-1422, US</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -4050,17 +4246,45 @@
           <t>שטטפלד</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin &amp; Joel Statfeld</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>דונורס_פאנד</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים, 1 נדחו</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -4176,12 +4400,12 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>שותפות יששכר-זבולון</t>
+          <t>שותפות יששכר-זבולון + נוסף</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>551</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -4652,7 +4876,11 @@
           <t>סנדר</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Berger</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4665,12 +4893,36 @@
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr"/>
       <c r="Q71" s="2" t="inlineStr">
@@ -4742,7 +4994,11 @@
           <t>ישראל</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Israel Brody</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4759,12 +5015,36 @@
           <t>3911 Avenue P, Brooklyn, NY 11234-3501, US</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>דונורס_פאנד</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -4801,7 +5081,11 @@
           <t>שרה</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Sara Brody</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
@@ -4814,12 +5098,36 @@
           <t>105 Lorimer St. #4, Brooklyn, NY 11206, US</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>OJC</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>שולם 3 חודשים, 3 נדחו</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -5194,7 +5502,11 @@
           <t>צבי</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Tzvi Jacobs</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5211,12 +5523,36 @@
           <t>966 Harbor View S, Hollywood, FL 33019-5058, US</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -5387,7 +5723,11 @@
           <t>יצחק ישראל</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Isaac Goldstein</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
@@ -5400,12 +5740,36 @@
           <t>1138 E 24th St, Brooklyn, NY 11210-4507, US</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr"/>
       <c r="Q84" s="2" t="inlineStr">
@@ -5795,7 +6159,11 @@
           <t>יהודה</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Yheudah Gutwein</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5812,12 +6180,36 @@
           <t>1632-42 StBrooklyn, N.Y 11204, IL</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
       <c r="Q92" s="2" t="inlineStr">
@@ -6143,12 +6535,36 @@
           <t>1243 E 7th St, Brooklyn 11230-4003, IL</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -6185,7 +6601,11 @@
           <t>יוסי</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Joseph Goldburd</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -6202,12 +6622,36 @@
           <t>1041 E 28th St 3741Brooklyn, NY, NY 11210, US</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -6265,12 +6709,36 @@
           <t>1243 E 72nd St, Brooklyn, NY 11234-5816, US</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -6307,7 +6775,11 @@
           <t>שמואל</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Goldburd</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6324,12 +6796,36 @@
           <t>1719 Burnett St, Brooklyn, NY 11229-2623, US</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -6802,17 +7298,45 @@
           <t>אברהם מנחם</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>A Menachem Goldstein</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Zelle</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>שולם 5 חודשים</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -6912,7 +7436,11 @@
           <t>יעקב</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Jacob T Goldstein</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6929,12 +7457,36 @@
           <t>6305 LINCOLN AVE, BALTIMORE, MD 21209, US</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Zelle</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -8091,7 +8643,11 @@
           <t>לאוניד</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr"/>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Leonid &amp; Marina Grossman</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -8104,12 +8660,36 @@
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -8786,7 +9366,11 @@
           <t>פריינד</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Dvora Rosenthal</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8803,12 +9387,36 @@
           <t>E 17th St, Brooklyn, NY 11230, US</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="2" t="inlineStr"/>
-      <c r="N145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr"/>
       <c r="Q145" s="2" t="inlineStr">
@@ -9325,17 +9933,45 @@
           <t>אריק</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Eric Djemshidoff</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -9789,27 +10425,27 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>שותפות יששכר-זבולון</t>
+          <t>שותפות יששכר-זבולון + נוסף</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Annualy</t>
+          <t>העברה_בנקאית</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>שולם 12 חודשים</t>
+          <t>שולם 3 חודשים, 3 נדחו</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>דצמבר</t>
+          <t>יוני</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr"/>
@@ -10025,7 +10661,11 @@
           <t>איגור</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Igor Olshteyn</t>
+        </is>
+      </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -10034,12 +10674,36 @@
       </c>
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -10131,7 +10795,11 @@
           <t>דוד</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>David Ofman</t>
+        </is>
+      </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -10148,12 +10816,36 @@
           <t>627 Oakland Ave, Cedarhurst, NY 11516, US</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -10281,7 +10973,11 @@
           <t>יעקב קלמן</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Jacob Horowitz</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -10298,12 +10994,36 @@
           <t>8-02 Dorian Ct, Far Rockaway, NY 11691-5206, US</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
-      <c r="N170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -10442,7 +11162,11 @@
           <t>ליאורה</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr"/>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Leora Hirsch</t>
+        </is>
+      </c>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -10459,12 +11183,36 @@
           <t>1282 East 27th Street, BROOKLYN, NY 11210, US</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="2" t="inlineStr"/>
-      <c r="N173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -11142,17 +11890,17 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>בניין</t>
+          <t>חודשי + נוסף</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>Zelle</t>
+          <t>צק</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -11193,7 +11941,11 @@
           <t>אהרן מרדכי</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr"/>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Herzog</t>
+        </is>
+      </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -11210,12 +11962,36 @@
           <t>1425 47th St 2635Brooklyn, NY, NY 11219, US</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -11346,7 +12122,11 @@
           <t>חיים</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr"/>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Howard Herskowitz</t>
+        </is>
+      </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -11363,12 +12143,36 @@
           <t>102 Woodmere Blvd 2128, Woodmere, NY 11598, US</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="2" t="inlineStr"/>
-      <c r="M189" s="2" t="inlineStr"/>
-      <c r="N189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -11464,7 +12268,11 @@
           <t>מיכאל</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr"/>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Micahel Vago</t>
+        </is>
+      </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -11481,12 +12289,36 @@
           <t>10 Slevin Court, Monsey, NY 10952, U.S.A</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr"/>
-      <c r="L191" s="2" t="inlineStr"/>
-      <c r="M191" s="2" t="inlineStr"/>
-      <c r="N191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>OJC</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -11527,7 +12359,11 @@
           <t>דב</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr"/>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Michael (Dovi) Weiser</t>
+        </is>
+      </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -11544,12 +12380,36 @@
           <t>1368 E 26th St, Brooklyn, NY 11210-5241, US</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr"/>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="inlineStr"/>
-      <c r="N192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -11965,17 +12825,45 @@
           <t>אליעזר שמואל</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr"/>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>eliezer Weingarden</t>
+        </is>
+      </c>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr"/>
-      <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="2" t="inlineStr"/>
-      <c r="M198" s="2" t="inlineStr"/>
-      <c r="N198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -12126,17 +13014,45 @@
           <t>חיים פסח</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr"/>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Eva Weinschneider</t>
+        </is>
+      </c>
       <c r="E201" s="2" t="inlineStr"/>
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr"/>
-      <c r="I201" s="2" t="inlineStr"/>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="inlineStr"/>
-      <c r="N201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -12721,12 +13637,12 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>חודשי</t>
+          <t>חודשי + נוסף</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>420</t>
         </is>
       </c>
       <c r="L213" s="2" t="inlineStr">
@@ -13157,7 +14073,11 @@
           <t>מוטי</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr"/>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Mark Sonnenschine</t>
+        </is>
+      </c>
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -13174,12 +14094,36 @@
           <t>2083 New York AveBrooklyn, NY, NY 11210, US</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr"/>
-      <c r="N221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -14290,7 +15234,11 @@
           <t>יצחק</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr"/>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Joseph Tepper</t>
+        </is>
+      </c>
       <c r="E240" s="2" t="inlineStr"/>
       <c r="F240" s="2" t="inlineStr">
         <is>
@@ -14307,12 +15255,36 @@
           <t>3903 Avenue R, Brooklyn, NY 11234-4328, US</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr"/>
-      <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="inlineStr"/>
-      <c r="M240" s="2" t="inlineStr"/>
-      <c r="N240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O240" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -14353,7 +15325,11 @@
           <t>יהושע</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr"/>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Jerry Teppfer</t>
+        </is>
+      </c>
       <c r="E241" s="2" t="inlineStr"/>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -14370,12 +15346,36 @@
           <t>2093 N.Y. AveBrooklyn, 11210, IL</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr"/>
-      <c r="J241" s="2" t="inlineStr"/>
-      <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="inlineStr"/>
-      <c r="M241" s="2" t="inlineStr"/>
-      <c r="N241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>צק</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O241" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -14416,7 +15416,11 @@
           <t>נתן יחזקאל</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr"/>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Tepfer</t>
+        </is>
+      </c>
       <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr">
         <is>
@@ -14433,12 +15437,36 @@
           <t>1070 E 27th St, Brooklyn, NY 11210-3740, US</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr"/>
-      <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="inlineStr"/>
-      <c r="M242" s="2" t="inlineStr"/>
-      <c r="N242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O242" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -14998,7 +16026,11 @@
           <t>דוב יוסף</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr"/>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Yosef Dov Kupperwasser</t>
+        </is>
+      </c>
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr">
         <is>
@@ -15015,12 +16047,36 @@
           <t>16 Gefen Dr, Lakewood, NJ 08701, US</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="inlineStr"/>
-      <c r="M252" s="2" t="inlineStr"/>
-      <c r="N252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O252" s="2" t="inlineStr"/>
       <c r="P252" s="2" t="inlineStr"/>
       <c r="Q252" s="2" t="inlineStr">
@@ -15186,7 +16242,11 @@
           <t>שמואל</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr"/>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>shmuel jacoby</t>
+        </is>
+      </c>
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr">
         <is>
@@ -15199,12 +16259,36 @@
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" s="2" t="inlineStr"/>
-      <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="inlineStr"/>
-      <c r="M256" s="2" t="inlineStr"/>
-      <c r="N256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O256" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -15241,7 +16325,11 @@
           <t>דניאל</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr"/>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Jacobson Daniel</t>
+        </is>
+      </c>
       <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr">
         <is>
@@ -15258,12 +16346,36 @@
           <t>526 Island Ave, Woodmere, NY 11598-2331, US</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr"/>
-      <c r="J257" s="2" t="inlineStr"/>
-      <c r="K257" s="2" t="inlineStr"/>
-      <c r="L257" s="2" t="inlineStr"/>
-      <c r="M257" s="2" t="inlineStr"/>
-      <c r="N257" s="2" t="inlineStr"/>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O257" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -15608,12 +16720,36 @@
           <t>164 Harborview N, Lawrence, NY 11559, USA</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr"/>
-      <c r="J263" s="2" t="inlineStr"/>
-      <c r="K263" s="2" t="inlineStr"/>
-      <c r="L263" s="2" t="inlineStr"/>
-      <c r="M263" s="2" t="inlineStr"/>
-      <c r="N263" s="2" t="inlineStr"/>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O263" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -15984,7 +17120,11 @@
           <t>מנחם</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr"/>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Menachem Cohen</t>
+        </is>
+      </c>
       <c r="E270" s="2" t="inlineStr"/>
       <c r="F270" s="2" t="inlineStr">
         <is>
@@ -16001,12 +17141,36 @@
           <t>140-11 68th Dr, Flushing, NY 11367-1634, US</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr"/>
-      <c r="J270" s="2" t="inlineStr"/>
-      <c r="K270" s="2" t="inlineStr"/>
-      <c r="L270" s="2" t="inlineStr"/>
-      <c r="M270" s="2" t="inlineStr"/>
-      <c r="N270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>העברה_בנקאית</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O270" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -16043,7 +17207,11 @@
           <t>שמואל</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr"/>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Shmuel Cohen</t>
+        </is>
+      </c>
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr">
         <is>
@@ -16060,12 +17228,36 @@
           <t>3715 Shannon Road, Cleveland, OH 44118, US ::: PO Box 2076, Elberon NJ, NJ 07740, US ::: PO Box 2076, Elberon NJ 07740, IL</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr"/>
-      <c r="J271" s="2" t="inlineStr"/>
-      <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="inlineStr"/>
-      <c r="M271" s="2" t="inlineStr"/>
-      <c r="N271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>Zelle</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O271" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -16185,12 +17377,12 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>חודשי</t>
+          <t>חודשי + נוסף</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L273" s="2" t="inlineStr">
@@ -19289,7 +20481,11 @@
           <t>יעקב</t>
         </is>
       </c>
-      <c r="D327" s="2" t="inlineStr"/>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Jacob Mokay</t>
+        </is>
+      </c>
       <c r="E327" s="2" t="inlineStr"/>
       <c r="F327" s="2" t="inlineStr">
         <is>
@@ -19302,12 +20498,36 @@
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="2" t="inlineStr"/>
-      <c r="J327" s="2" t="inlineStr"/>
-      <c r="K327" s="2" t="inlineStr"/>
-      <c r="L327" s="2" t="inlineStr"/>
-      <c r="M327" s="2" t="inlineStr"/>
-      <c r="N327" s="2" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>Zelle</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O327" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -19581,17 +20801,17 @@
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>חודשי</t>
+          <t>חודשי + נוסף</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>בנק_ווסט</t>
+          <t>העברה_בנקאית</t>
         </is>
       </c>
       <c r="M331" s="2" t="inlineStr">
@@ -19640,7 +20860,11 @@
           <t>שניאור זלמן</t>
         </is>
       </c>
-      <c r="D332" s="2" t="inlineStr"/>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Steven Mittman</t>
+        </is>
+      </c>
       <c r="E332" s="2" t="inlineStr"/>
       <c r="F332" s="2" t="inlineStr">
         <is>
@@ -19657,12 +20881,36 @@
           <t>4-34 2nd St, Fair Lawn, NJ 07410-1030, US</t>
         </is>
       </c>
-      <c r="I332" s="2" t="inlineStr"/>
-      <c r="J332" s="2" t="inlineStr"/>
-      <c r="K332" s="2" t="inlineStr"/>
-      <c r="L332" s="2" t="inlineStr"/>
-      <c r="M332" s="2" t="inlineStr"/>
-      <c r="N332" s="2" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O332" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -20148,17 +21396,45 @@
           <t>יוסף מרדכי</t>
         </is>
       </c>
-      <c r="D340" s="2" t="inlineStr"/>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Motti Mendelson</t>
+        </is>
+      </c>
       <c r="E340" s="2" t="inlineStr"/>
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr"/>
       <c r="H340" s="2" t="inlineStr"/>
-      <c r="I340" s="2" t="inlineStr"/>
-      <c r="J340" s="2" t="inlineStr"/>
-      <c r="K340" s="2" t="inlineStr"/>
-      <c r="L340" s="2" t="inlineStr"/>
-      <c r="M340" s="2" t="inlineStr"/>
-      <c r="N340" s="2" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O340" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -20199,7 +21475,11 @@
           <t>לאה</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr"/>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Alferd Mendelson</t>
+        </is>
+      </c>
       <c r="E341" s="2" t="inlineStr"/>
       <c r="F341" s="2" t="inlineStr">
         <is>
@@ -20208,12 +21488,36 @@
       </c>
       <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr"/>
-      <c r="I341" s="2" t="inlineStr"/>
-      <c r="J341" s="2" t="inlineStr"/>
-      <c r="K341" s="2" t="inlineStr"/>
-      <c r="L341" s="2" t="inlineStr"/>
-      <c r="M341" s="2" t="inlineStr"/>
-      <c r="N341" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>צק</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O341" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -21359,7 +22663,11 @@
           <t>סנדר</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr"/>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Neuwirth</t>
+        </is>
+      </c>
       <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr">
         <is>
@@ -21376,12 +22684,36 @@
           <t>272 Whitman .DriveBrooklyn, 11234, US</t>
         </is>
       </c>
-      <c r="I361" s="2" t="inlineStr"/>
-      <c r="J361" s="2" t="inlineStr"/>
-      <c r="K361" s="2" t="inlineStr"/>
-      <c r="L361" s="2" t="inlineStr"/>
-      <c r="M361" s="2" t="inlineStr"/>
-      <c r="N361" s="2" t="inlineStr"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O361" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -21738,7 +23070,11 @@
           <t>שמואל</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr"/>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Mark Zefir</t>
+        </is>
+      </c>
       <c r="E366" s="2" t="inlineStr"/>
       <c r="F366" s="2" t="inlineStr">
         <is>
@@ -21755,12 +23091,36 @@
           <t>53 Neptune ave, Woodmere</t>
         </is>
       </c>
-      <c r="I366" s="2" t="inlineStr"/>
-      <c r="J366" s="2" t="inlineStr"/>
-      <c r="K366" s="2" t="inlineStr"/>
-      <c r="L366" s="2" t="inlineStr"/>
-      <c r="M366" s="2" t="inlineStr"/>
-      <c r="N366" s="2" t="inlineStr"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>בניין</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>שולם 2 חודשים, 5 נדחו</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O366" s="2" t="inlineStr"/>
       <c r="P366" s="2" t="inlineStr"/>
       <c r="Q366" s="2" t="inlineStr">
@@ -21832,7 +23192,11 @@
           <t>דוד</t>
         </is>
       </c>
-      <c r="D368" s="2" t="inlineStr"/>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>David Sutton</t>
+        </is>
+      </c>
       <c r="E368" s="2" t="inlineStr"/>
       <c r="F368" s="2" t="inlineStr">
         <is>
@@ -21851,14 +23215,34 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
-        </is>
-      </c>
-      <c r="J368" s="2" t="inlineStr"/>
-      <c r="K368" s="2" t="inlineStr"/>
-      <c r="L368" s="2" t="inlineStr"/>
-      <c r="M368" s="2" t="inlineStr"/>
-      <c r="N368" s="2" t="inlineStr"/>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O368" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -23289,12 +24673,36 @@
           <t>71-35 147th StApt 1A, Flushing, NY 11367, US</t>
         </is>
       </c>
-      <c r="I392" s="2" t="inlineStr"/>
-      <c r="J392" s="2" t="inlineStr"/>
-      <c r="K392" s="2" t="inlineStr"/>
-      <c r="L392" s="2" t="inlineStr"/>
-      <c r="M392" s="2" t="inlineStr"/>
-      <c r="N392" s="2" t="inlineStr"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O392" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -23520,7 +24928,11 @@
           <t>מוטי</t>
         </is>
       </c>
-      <c r="D396" s="2" t="inlineStr"/>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Yitzchok Pollak</t>
+        </is>
+      </c>
       <c r="E396" s="2" t="inlineStr"/>
       <c r="F396" s="2" t="inlineStr">
         <is>
@@ -23529,12 +24941,36 @@
       </c>
       <c r="G396" s="2" t="inlineStr"/>
       <c r="H396" s="2" t="inlineStr"/>
-      <c r="I396" s="2" t="inlineStr"/>
-      <c r="J396" s="2" t="inlineStr"/>
-      <c r="K396" s="2" t="inlineStr"/>
-      <c r="L396" s="2" t="inlineStr"/>
-      <c r="M396" s="2" t="inlineStr"/>
-      <c r="N396" s="2" t="inlineStr"/>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O396" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -23826,7 +25262,11 @@
           <t>יצחק</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr"/>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Yitzchak Fuchs</t>
+        </is>
+      </c>
       <c r="E402" s="2" t="inlineStr"/>
       <c r="F402" s="2" t="inlineStr">
         <is>
@@ -23839,12 +25279,36 @@
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr"/>
-      <c r="I402" s="2" t="inlineStr"/>
-      <c r="J402" s="2" t="inlineStr"/>
-      <c r="K402" s="2" t="inlineStr"/>
-      <c r="L402" s="2" t="inlineStr"/>
-      <c r="M402" s="2" t="inlineStr"/>
-      <c r="N402" s="2" t="inlineStr"/>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O402" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -23894,12 +25358,36 @@
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr"/>
-      <c r="I403" s="2" t="inlineStr"/>
-      <c r="J403" s="2" t="inlineStr"/>
-      <c r="K403" s="2" t="inlineStr"/>
-      <c r="L403" s="2" t="inlineStr"/>
-      <c r="M403" s="2" t="inlineStr"/>
-      <c r="N403" s="2" t="inlineStr"/>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O403" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -23936,7 +25424,11 @@
           <t>רונן</t>
         </is>
       </c>
-      <c r="D404" s="2" t="inlineStr"/>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Ronen Fuksbrumer</t>
+        </is>
+      </c>
       <c r="E404" s="2" t="inlineStr"/>
       <c r="F404" s="2" t="inlineStr">
         <is>
@@ -23953,12 +25445,36 @@
           <t>2224 E 66 StBrooklyn, 11234, US</t>
         </is>
       </c>
-      <c r="I404" s="2" t="inlineStr"/>
-      <c r="J404" s="2" t="inlineStr"/>
-      <c r="K404" s="2" t="inlineStr"/>
-      <c r="L404" s="2" t="inlineStr"/>
-      <c r="M404" s="2" t="inlineStr"/>
-      <c r="N404" s="2" t="inlineStr"/>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O404" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -24093,7 +25609,11 @@
           <t>אברהם</t>
         </is>
       </c>
-      <c r="D407" s="2" t="inlineStr"/>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Fiene</t>
+        </is>
+      </c>
       <c r="E407" s="2" t="inlineStr"/>
       <c r="F407" s="2" t="inlineStr">
         <is>
@@ -24110,12 +25630,36 @@
           <t>34 Sandy Hook Rd S, Siesta Key, FL 34242, US</t>
         </is>
       </c>
-      <c r="I407" s="2" t="inlineStr"/>
-      <c r="J407" s="2" t="inlineStr"/>
-      <c r="K407" s="2" t="inlineStr"/>
-      <c r="L407" s="2" t="inlineStr"/>
-      <c r="M407" s="2" t="inlineStr"/>
-      <c r="N407" s="2" t="inlineStr"/>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O407" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -24152,17 +25696,45 @@
           <t>אווילין וולסין</t>
         </is>
       </c>
-      <c r="D408" s="2" t="inlineStr"/>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn Finegold</t>
+        </is>
+      </c>
       <c r="E408" s="2" t="inlineStr"/>
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr"/>
       <c r="H408" s="2" t="inlineStr"/>
-      <c r="I408" s="2" t="inlineStr"/>
-      <c r="J408" s="2" t="inlineStr"/>
-      <c r="K408" s="2" t="inlineStr"/>
-      <c r="L408" s="2" t="inlineStr"/>
-      <c r="M408" s="2" t="inlineStr"/>
-      <c r="N408" s="2" t="inlineStr"/>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O408" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -25411,7 +26983,11 @@
           <t>שלמה</t>
         </is>
       </c>
-      <c r="D429" s="2" t="inlineStr"/>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Sheldon Perl</t>
+        </is>
+      </c>
       <c r="E429" s="2" t="inlineStr"/>
       <c r="F429" s="2" t="inlineStr">
         <is>
@@ -25424,12 +27000,36 @@
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr"/>
-      <c r="I429" s="2" t="inlineStr"/>
-      <c r="J429" s="2" t="inlineStr"/>
-      <c r="K429" s="2" t="inlineStr"/>
-      <c r="L429" s="2" t="inlineStr"/>
-      <c r="M429" s="2" t="inlineStr"/>
-      <c r="N429" s="2" t="inlineStr"/>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr">
+        <is>
+          <t>שולם 5 חודשים, 2 נדחו</t>
+        </is>
+      </c>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O429" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -26001,7 +27601,11 @@
           <t>יהושע (רולנד)</t>
         </is>
       </c>
-      <c r="D439" s="2" t="inlineStr"/>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Roland Friedman</t>
+        </is>
+      </c>
       <c r="E439" s="2" t="inlineStr"/>
       <c r="F439" s="2" t="inlineStr">
         <is>
@@ -26018,12 +27622,36 @@
           <t>Gottfried-Keller-Straße 52, Frankfurt am Main 60431, DE</t>
         </is>
       </c>
-      <c r="I439" s="2" t="inlineStr"/>
-      <c r="J439" s="2" t="inlineStr"/>
-      <c r="K439" s="2" t="inlineStr"/>
-      <c r="L439" s="2" t="inlineStr"/>
-      <c r="M439" s="2" t="inlineStr"/>
-      <c r="N439" s="2" t="inlineStr"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K439" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N439" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O439" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -26107,7 +27735,11 @@
           <t>יעקב</t>
         </is>
       </c>
-      <c r="D441" s="2" t="inlineStr"/>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Yaakov Friedman</t>
+        </is>
+      </c>
       <c r="E441" s="2" t="inlineStr"/>
       <c r="F441" s="2" t="inlineStr">
         <is>
@@ -26122,17 +27754,29 @@
       <c r="H441" s="2" t="inlineStr"/>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
-        </is>
-      </c>
-      <c r="J441" s="2" t="inlineStr"/>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="L441" s="2" t="inlineStr"/>
-      <c r="M441" s="2" t="inlineStr"/>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L441" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
       <c r="N441" s="2" t="inlineStr">
         <is>
           <t>מאי</t>
@@ -26366,17 +28010,45 @@
           <t>יעקב דוב</t>
         </is>
       </c>
-      <c r="D446" s="2" t="inlineStr"/>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Jay Frechter</t>
+        </is>
+      </c>
       <c r="E446" s="2" t="inlineStr"/>
       <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr"/>
-      <c r="I446" s="2" t="inlineStr"/>
-      <c r="J446" s="2" t="inlineStr"/>
-      <c r="K446" s="2" t="inlineStr"/>
-      <c r="L446" s="2" t="inlineStr"/>
-      <c r="M446" s="2" t="inlineStr"/>
-      <c r="N446" s="2" t="inlineStr"/>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N446" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O446" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>
@@ -27038,7 +28710,11 @@
           <t>נתנאל</t>
         </is>
       </c>
-      <c r="D458" s="2" t="inlineStr"/>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Netanel Zion</t>
+        </is>
+      </c>
       <c r="E458" s="2" t="inlineStr"/>
       <c r="F458" s="2" t="inlineStr">
         <is>
@@ -27055,12 +28731,36 @@
           <t>112 Steamboat Rd, Great Neck, NY 11024, US</t>
         </is>
       </c>
-      <c r="I458" s="2" t="inlineStr"/>
-      <c r="J458" s="2" t="inlineStr"/>
-      <c r="K458" s="2" t="inlineStr"/>
-      <c r="L458" s="2" t="inlineStr"/>
-      <c r="M458" s="2" t="inlineStr"/>
-      <c r="N458" s="2" t="inlineStr"/>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K458" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L458" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M458" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N458" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O458" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -27415,7 +29115,11 @@
           <t>מנחם</t>
         </is>
       </c>
-      <c r="D465" s="2" t="inlineStr"/>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Marvin Kohn</t>
+        </is>
+      </c>
       <c r="E465" s="2" t="inlineStr"/>
       <c r="F465" s="2" t="inlineStr"/>
       <c r="G465" s="2" t="inlineStr">
@@ -27424,12 +29128,36 @@
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr"/>
-      <c r="I465" s="2" t="inlineStr"/>
-      <c r="J465" s="2" t="inlineStr"/>
-      <c r="K465" s="2" t="inlineStr"/>
-      <c r="L465" s="2" t="inlineStr"/>
-      <c r="M465" s="2" t="inlineStr"/>
-      <c r="N465" s="2" t="inlineStr"/>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>חודשי</t>
+        </is>
+      </c>
+      <c r="K465" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M465" s="2" t="inlineStr">
+        <is>
+          <t>שולם 2 חודשים</t>
+        </is>
+      </c>
+      <c r="N465" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O465" s="2" t="inlineStr"/>
       <c r="P465" s="2" t="inlineStr"/>
       <c r="Q465" s="2" t="inlineStr">
@@ -27509,7 +29237,11 @@
           <t>אריה לייב</t>
         </is>
       </c>
-      <c r="D467" s="2" t="inlineStr"/>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Arye Kaufman</t>
+        </is>
+      </c>
       <c r="E467" s="2" t="inlineStr"/>
       <c r="F467" s="2" t="inlineStr">
         <is>
@@ -27526,12 +29258,36 @@
           <t>274 Ashewood Ct, Toms River, NJ 08755-1104, US</t>
         </is>
       </c>
-      <c r="I467" s="2" t="inlineStr"/>
-      <c r="J467" s="2" t="inlineStr"/>
-      <c r="K467" s="2" t="inlineStr"/>
-      <c r="L467" s="2" t="inlineStr"/>
-      <c r="M467" s="2" t="inlineStr"/>
-      <c r="N467" s="2" t="inlineStr"/>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K467" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O467" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -28048,7 +29804,11 @@
           <t>חיים יעקב</t>
         </is>
       </c>
-      <c r="D476" s="2" t="inlineStr"/>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>chaim Korland</t>
+        </is>
+      </c>
       <c r="E476" s="2" t="inlineStr"/>
       <c r="F476" s="2" t="inlineStr">
         <is>
@@ -28057,12 +29817,36 @@
       </c>
       <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr"/>
-      <c r="I476" s="2" t="inlineStr"/>
-      <c r="J476" s="2" t="inlineStr"/>
-      <c r="K476" s="2" t="inlineStr"/>
-      <c r="L476" s="2" t="inlineStr"/>
-      <c r="M476" s="2" t="inlineStr"/>
-      <c r="N476" s="2" t="inlineStr"/>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K476" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O476" s="2" t="inlineStr">
         <is>
           <t>קוויטל_101</t>
@@ -28162,17 +29946,45 @@
           <t>יוסף</t>
         </is>
       </c>
-      <c r="D478" s="2" t="inlineStr"/>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Yossi Kirzner</t>
+        </is>
+      </c>
       <c r="E478" s="2" t="inlineStr"/>
       <c r="F478" s="2" t="inlineStr"/>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr"/>
-      <c r="I478" s="2" t="inlineStr"/>
-      <c r="J478" s="2" t="inlineStr"/>
-      <c r="K478" s="2" t="inlineStr"/>
-      <c r="L478" s="2" t="inlineStr"/>
-      <c r="M478" s="2" t="inlineStr"/>
-      <c r="N478" s="2" t="inlineStr"/>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O478" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -28430,12 +30242,36 @@
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr"/>
-      <c r="I483" s="2" t="inlineStr"/>
-      <c r="J483" s="2" t="inlineStr"/>
-      <c r="K483" s="2" t="inlineStr"/>
-      <c r="L483" s="2" t="inlineStr"/>
-      <c r="M483" s="2" t="inlineStr"/>
-      <c r="N483" s="2" t="inlineStr"/>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
+      <c r="K483" s="2" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N483" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O483" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -30034,7 +31870,11 @@
           <t>יהושע</t>
         </is>
       </c>
-      <c r="D514" s="2" t="inlineStr"/>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Schia Rosenfeld</t>
+        </is>
+      </c>
       <c r="E514" s="2" t="inlineStr"/>
       <c r="F514" s="2" t="inlineStr">
         <is>
@@ -30053,17 +31893,29 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
-        </is>
-      </c>
-      <c r="J514" s="2" t="inlineStr"/>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
-        </is>
-      </c>
-      <c r="L514" s="2" t="inlineStr"/>
-      <c r="M514" s="2" t="inlineStr"/>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
       <c r="N514" s="2" t="inlineStr">
         <is>
           <t>יולי</t>
@@ -30164,7 +32016,11 @@
           <t>ישראל אבא</t>
         </is>
       </c>
-      <c r="D516" s="2" t="inlineStr"/>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Jerry Rosenfeld</t>
+        </is>
+      </c>
       <c r="E516" s="2" t="inlineStr"/>
       <c r="F516" s="2" t="inlineStr">
         <is>
@@ -30181,12 +32037,36 @@
           <t>441 Albemarle Rd</t>
         </is>
       </c>
-      <c r="I516" s="2" t="inlineStr"/>
-      <c r="J516" s="2" t="inlineStr"/>
-      <c r="K516" s="2" t="inlineStr"/>
-      <c r="L516" s="2" t="inlineStr"/>
-      <c r="M516" s="2" t="inlineStr"/>
-      <c r="N516" s="2" t="inlineStr"/>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K516" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>צק</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N516" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O516" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -30279,7 +32159,11 @@
           <t>אהרן יהושע</t>
         </is>
       </c>
-      <c r="D518" s="2" t="inlineStr"/>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Roz</t>
+        </is>
+      </c>
       <c r="E518" s="2" t="inlineStr"/>
       <c r="F518" s="2" t="inlineStr">
         <is>
@@ -30296,12 +32180,36 @@
           <t>1633 East 29th StreetBrooklyn, N.Y. 11229, U.S.A</t>
         </is>
       </c>
-      <c r="I518" s="2" t="inlineStr"/>
-      <c r="J518" s="2" t="inlineStr"/>
-      <c r="K518" s="2" t="inlineStr"/>
-      <c r="L518" s="2" t="inlineStr"/>
-      <c r="M518" s="2" t="inlineStr"/>
-      <c r="N518" s="2" t="inlineStr"/>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K518" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L518" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M518" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N518" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O518" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -31207,12 +33115,12 @@
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>שותפות יששכר-זבולון</t>
+          <t>שותפות יששכר-זבולון + נוסף</t>
         </is>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="L534" s="2" t="inlineStr">
@@ -32218,7 +34126,11 @@
           <t>יעקב בן</t>
         </is>
       </c>
-      <c r="D551" s="2" t="inlineStr"/>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Jacob Ben shmuel</t>
+        </is>
+      </c>
       <c r="E551" s="2" t="inlineStr"/>
       <c r="F551" s="2" t="inlineStr">
         <is>
@@ -32235,12 +34147,36 @@
           <t>4 Gedera St, Jerusalem 9442708, IL</t>
         </is>
       </c>
-      <c r="I551" s="2" t="inlineStr"/>
-      <c r="J551" s="2" t="inlineStr"/>
-      <c r="K551" s="2" t="inlineStr"/>
-      <c r="L551" s="2" t="inlineStr"/>
-      <c r="M551" s="2" t="inlineStr"/>
-      <c r="N551" s="2" t="inlineStr"/>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>חודשי + נוסף</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L551" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="inlineStr">
+        <is>
+          <t>שולם 6 חודשים</t>
+        </is>
+      </c>
+      <c r="N551" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O551" s="2" t="inlineStr">
         <is>
           <t>קוויטל_כללי</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U568"/>
+  <dimension ref="A1:V568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,7 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -590,6 +591,11 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>כינויים</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>סטטוס_חודשים</t>
         </is>
       </c>
     </row>
@@ -643,6 +649,7 @@
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -726,6 +733,11 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -805,6 +817,11 @@
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -856,6 +873,7 @@
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -907,6 +925,7 @@
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -958,6 +977,7 @@
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1005,6 +1025,7 @@
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr"/>
       <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1092,6 +1113,11 @@
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1181,6 +1207,11 @@
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>זאב אדלקופף;זאוויל אדלקוף</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
         </is>
       </c>
     </row>
@@ -1254,6 +1285,11 @@
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>ppppppx-----</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1305,6 +1341,7 @@
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1356,6 +1393,7 @@
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1403,6 +1441,7 @@
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1462,6 +1501,7 @@
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1513,6 +1553,7 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1556,6 +1597,7 @@
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1599,6 +1641,7 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1658,6 +1701,7 @@
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1713,6 +1757,7 @@
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1764,6 +1809,7 @@
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1851,6 +1897,11 @@
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1902,6 +1953,7 @@
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1961,6 +2013,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2012,6 +2065,7 @@
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2075,6 +2129,7 @@
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2162,6 +2217,11 @@
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2217,6 +2277,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2268,6 +2329,7 @@
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2319,6 +2381,7 @@
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2402,6 +2465,11 @@
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2449,6 +2517,7 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2528,6 +2597,11 @@
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2579,6 +2653,7 @@
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2622,6 +2697,7 @@
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2665,6 +2741,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2752,6 +2829,11 @@
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr"/>
       <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2839,6 +2921,11 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2890,6 +2977,7 @@
       <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2941,6 +3029,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2992,6 +3081,7 @@
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3071,6 +3161,11 @@
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3162,6 +3257,11 @@
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>ppppp-p-----</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3213,6 +3313,7 @@
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3264,6 +3365,7 @@
       <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3315,6 +3417,7 @@
       <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3386,6 +3489,11 @@
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>xxxxxx------</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3465,6 +3573,11 @@
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>pppp--p-----</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3552,6 +3665,11 @@
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3639,6 +3757,11 @@
       <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3710,6 +3833,11 @@
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3769,6 +3897,7 @@
       <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3820,6 +3949,7 @@
       <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3871,6 +4001,7 @@
       <c r="S54" s="2" t="inlineStr"/>
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3922,6 +4053,7 @@
       <c r="S55" s="2" t="inlineStr"/>
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3981,6 +4113,7 @@
       <c r="S56" s="2" t="inlineStr"/>
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4068,6 +4201,11 @@
       <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4119,6 +4257,7 @@
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4170,6 +4309,7 @@
       <c r="S59" s="2" t="inlineStr"/>
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4257,6 +4397,11 @@
       <c r="S60" s="2" t="inlineStr"/>
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4340,6 +4485,11 @@
       </c>
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>p--pppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4391,6 +4541,7 @@
       <c r="S62" s="2" t="inlineStr"/>
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4442,6 +4593,7 @@
       <c r="S63" s="2" t="inlineStr"/>
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4521,6 +4673,11 @@
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>ppppppx-----</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4572,6 +4729,7 @@
       <c r="S65" s="2" t="inlineStr"/>
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4659,6 +4817,11 @@
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>xxpppx------</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4714,6 +4877,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4793,6 +4957,11 @@
       <c r="S68" s="2" t="inlineStr"/>
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>xxppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4844,6 +5013,7 @@
       <c r="S69" s="2" t="inlineStr"/>
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4907,6 +5077,7 @@
       <c r="S70" s="2" t="inlineStr"/>
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4958,6 +5129,7 @@
       <c r="S71" s="2" t="inlineStr"/>
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5009,6 +5181,7 @@
       <c r="S72" s="2" t="inlineStr"/>
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5072,6 +5245,7 @@
       <c r="S73" s="2" t="inlineStr"/>
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5147,6 +5321,11 @@
       <c r="S74" s="2" t="inlineStr"/>
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5190,6 +5369,7 @@
       <c r="S75" s="2" t="inlineStr"/>
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5277,6 +5457,11 @@
       <c r="S76" s="2" t="inlineStr"/>
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5360,6 +5545,11 @@
       <c r="S77" s="2" t="inlineStr"/>
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>pppxxx------</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5411,6 +5601,7 @@
       <c r="S78" s="2" t="inlineStr"/>
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5482,6 +5673,11 @@
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5533,6 +5729,7 @@
       <c r="S80" s="2" t="inlineStr"/>
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5584,6 +5781,7 @@
       <c r="S81" s="2" t="inlineStr"/>
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5631,6 +5829,7 @@
       <c r="S82" s="2" t="inlineStr"/>
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5682,6 +5881,7 @@
       <c r="S83" s="2" t="inlineStr"/>
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5769,6 +5969,11 @@
       <c r="S84" s="2" t="inlineStr"/>
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>pppppx------</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5860,6 +6065,11 @@
       </c>
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5911,6 +6121,7 @@
       <c r="S86" s="2" t="inlineStr"/>
       <c r="T86" s="2" t="inlineStr"/>
       <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5990,6 +6201,11 @@
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6065,6 +6281,11 @@
       <c r="S88" s="2" t="inlineStr"/>
       <c r="T88" s="2" t="inlineStr"/>
       <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6124,6 +6345,7 @@
       <c r="S89" s="2" t="inlineStr"/>
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6167,6 +6389,7 @@
       <c r="S90" s="2" t="inlineStr"/>
       <c r="T90" s="2" t="inlineStr"/>
       <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6218,6 +6441,7 @@
       <c r="S91" s="2" t="inlineStr"/>
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6273,6 +6497,7 @@
       <c r="S92" s="2" t="inlineStr"/>
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6332,6 +6557,7 @@
           <t>גאי גוארי;ישראל גיא גוארי</t>
         </is>
       </c>
+      <c r="V93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6375,6 +6601,7 @@
       <c r="S94" s="2" t="inlineStr"/>
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6426,6 +6653,7 @@
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6505,6 +6733,11 @@
       <c r="S96" s="2" t="inlineStr"/>
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6548,6 +6781,7 @@
       <c r="S97" s="2" t="inlineStr"/>
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6635,6 +6869,11 @@
       <c r="S98" s="2" t="inlineStr"/>
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6690,6 +6929,7 @@
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6781,6 +7021,11 @@
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>ppxxxpp-----</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6868,6 +7113,11 @@
       <c r="S101" s="2" t="inlineStr"/>
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>pp-pppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6955,6 +7205,11 @@
       <c r="S102" s="2" t="inlineStr"/>
       <c r="T102" s="2" t="inlineStr"/>
       <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7042,6 +7297,11 @@
       <c r="S103" s="2" t="inlineStr"/>
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7129,6 +7389,11 @@
       <c r="S104" s="2" t="inlineStr"/>
       <c r="T104" s="2" t="inlineStr"/>
       <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7172,6 +7437,7 @@
       <c r="S105" s="2" t="inlineStr"/>
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7215,6 +7481,7 @@
       <c r="S106" s="2" t="inlineStr"/>
       <c r="T106" s="2" t="inlineStr"/>
       <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7274,6 +7541,7 @@
       <c r="S107" s="2" t="inlineStr"/>
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7313,6 +7581,7 @@
       <c r="S108" s="2" t="inlineStr"/>
       <c r="T108" s="2" t="inlineStr"/>
       <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7364,6 +7633,7 @@
       <c r="S109" s="2" t="inlineStr"/>
       <c r="T109" s="2" t="inlineStr"/>
       <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7451,6 +7721,11 @@
       <c r="S110" s="2" t="inlineStr"/>
       <c r="T110" s="2" t="inlineStr"/>
       <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7514,6 +7789,7 @@
       <c r="S111" s="2" t="inlineStr"/>
       <c r="T111" s="2" t="inlineStr"/>
       <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7565,6 +7841,7 @@
       <c r="S112" s="2" t="inlineStr"/>
       <c r="T112" s="2" t="inlineStr"/>
       <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7644,6 +7921,11 @@
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>--ppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7703,6 +7985,7 @@
       <c r="S114" s="2" t="inlineStr"/>
       <c r="T114" s="2" t="inlineStr"/>
       <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7790,6 +8073,11 @@
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7841,6 +8129,7 @@
       <c r="S116" s="2" t="inlineStr"/>
       <c r="T116" s="2" t="inlineStr"/>
       <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7888,6 +8177,7 @@
       <c r="S117" s="2" t="inlineStr"/>
       <c r="T117" s="2" t="inlineStr"/>
       <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7939,6 +8229,7 @@
       <c r="S118" s="2" t="inlineStr"/>
       <c r="T118" s="2" t="inlineStr"/>
       <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7990,6 +8281,7 @@
       <c r="S119" s="2" t="inlineStr"/>
       <c r="T119" s="2" t="inlineStr"/>
       <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8041,6 +8333,7 @@
       <c r="S120" s="2" t="inlineStr"/>
       <c r="T120" s="2" t="inlineStr"/>
       <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8092,6 +8385,7 @@
       <c r="S121" s="2" t="inlineStr"/>
       <c r="T121" s="2" t="inlineStr"/>
       <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8143,6 +8437,7 @@
       <c r="S122" s="2" t="inlineStr"/>
       <c r="T122" s="2" t="inlineStr"/>
       <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8186,6 +8481,7 @@
       <c r="S123" s="2" t="inlineStr"/>
       <c r="T123" s="2" t="inlineStr"/>
       <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8241,6 +8537,7 @@
       </c>
       <c r="T124" s="2" t="inlineStr"/>
       <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8328,6 +8625,11 @@
       <c r="S125" s="2" t="inlineStr"/>
       <c r="T125" s="2" t="inlineStr"/>
       <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8379,6 +8681,7 @@
       <c r="S126" s="2" t="inlineStr"/>
       <c r="T126" s="2" t="inlineStr"/>
       <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8438,6 +8741,7 @@
       <c r="S127" s="2" t="inlineStr"/>
       <c r="T127" s="2" t="inlineStr"/>
       <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8489,6 +8793,7 @@
       <c r="S128" s="2" t="inlineStr"/>
       <c r="T128" s="2" t="inlineStr"/>
       <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8532,6 +8837,7 @@
       <c r="S129" s="2" t="inlineStr"/>
       <c r="T129" s="2" t="inlineStr"/>
       <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8619,6 +8925,11 @@
       <c r="S130" s="2" t="inlineStr"/>
       <c r="T130" s="2" t="inlineStr"/>
       <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8670,6 +8981,7 @@
       <c r="S131" s="2" t="inlineStr"/>
       <c r="T131" s="2" t="inlineStr"/>
       <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8721,6 +9033,7 @@
       <c r="S132" s="2" t="inlineStr"/>
       <c r="T132" s="2" t="inlineStr"/>
       <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8772,6 +9085,7 @@
       <c r="S133" s="2" t="inlineStr"/>
       <c r="T133" s="2" t="inlineStr"/>
       <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8823,6 +9137,7 @@
       <c r="S134" s="2" t="inlineStr"/>
       <c r="T134" s="2" t="inlineStr"/>
       <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8910,6 +9225,11 @@
       <c r="S135" s="2" t="inlineStr"/>
       <c r="T135" s="2" t="inlineStr"/>
       <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8993,6 +9313,11 @@
       <c r="S136" s="2" t="inlineStr"/>
       <c r="T136" s="2" t="inlineStr"/>
       <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -9048,6 +9373,7 @@
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9099,6 +9425,7 @@
       <c r="S138" s="2" t="inlineStr"/>
       <c r="T138" s="2" t="inlineStr"/>
       <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9158,6 +9485,7 @@
       <c r="S139" s="2" t="inlineStr"/>
       <c r="T139" s="2" t="inlineStr"/>
       <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -9201,6 +9529,7 @@
       <c r="S140" s="2" t="inlineStr"/>
       <c r="T140" s="2" t="inlineStr"/>
       <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9288,6 +9617,11 @@
       <c r="S141" s="2" t="inlineStr"/>
       <c r="T141" s="2" t="inlineStr"/>
       <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9339,6 +9673,7 @@
       <c r="S142" s="2" t="inlineStr"/>
       <c r="T142" s="2" t="inlineStr"/>
       <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9394,6 +9729,7 @@
       <c r="S143" s="2" t="inlineStr"/>
       <c r="T143" s="2" t="inlineStr"/>
       <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9445,6 +9781,7 @@
       <c r="S144" s="2" t="inlineStr"/>
       <c r="T144" s="2" t="inlineStr"/>
       <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9492,6 +9829,7 @@
       <c r="S145" s="2" t="inlineStr"/>
       <c r="T145" s="2" t="inlineStr"/>
       <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9543,6 +9881,7 @@
       <c r="S146" s="2" t="inlineStr"/>
       <c r="T146" s="2" t="inlineStr"/>
       <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9590,6 +9929,7 @@
       <c r="S147" s="2" t="inlineStr"/>
       <c r="T147" s="2" t="inlineStr"/>
       <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9633,6 +9973,7 @@
       <c r="S148" s="2" t="inlineStr"/>
       <c r="T148" s="2" t="inlineStr"/>
       <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9712,6 +10053,11 @@
       <c r="S149" s="2" t="inlineStr"/>
       <c r="T149" s="2" t="inlineStr"/>
       <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9795,6 +10141,11 @@
         </is>
       </c>
       <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>pppppxx-----</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9842,6 +10193,7 @@
       <c r="S151" s="2" t="inlineStr"/>
       <c r="T151" s="2" t="inlineStr"/>
       <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9933,6 +10285,11 @@
         </is>
       </c>
       <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9984,6 +10341,7 @@
       <c r="S153" s="2" t="inlineStr"/>
       <c r="T153" s="2" t="inlineStr"/>
       <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10047,6 +10405,7 @@
         </is>
       </c>
       <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10098,6 +10457,7 @@
         </is>
       </c>
       <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10149,6 +10509,7 @@
       <c r="S156" s="2" t="inlineStr"/>
       <c r="T156" s="2" t="inlineStr"/>
       <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10200,6 +10561,7 @@
       <c r="S157" s="2" t="inlineStr"/>
       <c r="T157" s="2" t="inlineStr"/>
       <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10279,6 +10641,11 @@
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10330,6 +10697,7 @@
       <c r="S159" s="2" t="inlineStr"/>
       <c r="T159" s="2" t="inlineStr"/>
       <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10417,6 +10785,11 @@
       <c r="S160" s="2" t="inlineStr"/>
       <c r="T160" s="2" t="inlineStr"/>
       <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -10468,6 +10841,7 @@
       <c r="S161" s="2" t="inlineStr"/>
       <c r="T161" s="2" t="inlineStr"/>
       <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -10519,6 +10893,7 @@
       <c r="S162" s="2" t="inlineStr"/>
       <c r="T162" s="2" t="inlineStr"/>
       <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -10570,6 +10945,7 @@
       <c r="S163" s="2" t="inlineStr"/>
       <c r="T163" s="2" t="inlineStr"/>
       <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -10621,6 +10997,7 @@
       <c r="S164" s="2" t="inlineStr"/>
       <c r="T164" s="2" t="inlineStr"/>
       <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -10668,6 +11045,7 @@
       <c r="S165" s="2" t="inlineStr"/>
       <c r="T165" s="2" t="inlineStr"/>
       <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -10743,6 +11121,11 @@
       <c r="S166" s="2" t="inlineStr"/>
       <c r="T166" s="2" t="inlineStr"/>
       <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>pppxxx------</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10806,6 +11189,7 @@
         </is>
       </c>
       <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10877,6 +11261,7 @@
       <c r="S168" s="2" t="inlineStr"/>
       <c r="T168" s="2" t="inlineStr"/>
       <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10928,6 +11313,7 @@
       <c r="S169" s="2" t="inlineStr"/>
       <c r="T169" s="2" t="inlineStr"/>
       <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11011,6 +11397,11 @@
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11062,6 +11453,7 @@
       <c r="S171" s="2" t="inlineStr"/>
       <c r="T171" s="2" t="inlineStr"/>
       <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -11153,6 +11545,11 @@
         </is>
       </c>
       <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -11240,6 +11637,11 @@
       <c r="S173" s="2" t="inlineStr"/>
       <c r="T173" s="2" t="inlineStr"/>
       <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11331,6 +11733,11 @@
         </is>
       </c>
       <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11382,6 +11789,7 @@
         </is>
       </c>
       <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11429,6 +11837,7 @@
       <c r="S176" s="2" t="inlineStr"/>
       <c r="T176" s="2" t="inlineStr"/>
       <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -11516,6 +11925,11 @@
       <c r="S177" s="2" t="inlineStr"/>
       <c r="T177" s="2" t="inlineStr"/>
       <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -11563,6 +11977,7 @@
       <c r="S178" s="2" t="inlineStr"/>
       <c r="T178" s="2" t="inlineStr"/>
       <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -11630,6 +12045,7 @@
         </is>
       </c>
       <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -11709,6 +12125,11 @@
         </is>
       </c>
       <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>ppppppx-----</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -11752,6 +12173,7 @@
       <c r="S181" s="2" t="inlineStr"/>
       <c r="T181" s="2" t="inlineStr"/>
       <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -11807,6 +12229,7 @@
         </is>
       </c>
       <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -11850,6 +12273,7 @@
       <c r="S183" s="2" t="inlineStr"/>
       <c r="T183" s="2" t="inlineStr"/>
       <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -11901,6 +12325,7 @@
       <c r="S184" s="2" t="inlineStr"/>
       <c r="T184" s="2" t="inlineStr"/>
       <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11948,6 +12373,7 @@
       <c r="S185" s="2" t="inlineStr"/>
       <c r="T185" s="2" t="inlineStr"/>
       <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -12035,6 +12461,11 @@
       <c r="S186" s="2" t="inlineStr"/>
       <c r="T186" s="2" t="inlineStr"/>
       <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -12086,6 +12517,7 @@
         </is>
       </c>
       <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -12137,6 +12569,7 @@
       <c r="S188" s="2" t="inlineStr"/>
       <c r="T188" s="2" t="inlineStr"/>
       <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -12208,6 +12641,11 @@
       <c r="S189" s="2" t="inlineStr"/>
       <c r="T189" s="2" t="inlineStr"/>
       <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -12295,6 +12733,11 @@
       <c r="S190" s="2" t="inlineStr"/>
       <c r="T190" s="2" t="inlineStr"/>
       <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -12346,6 +12789,7 @@
       <c r="S191" s="2" t="inlineStr"/>
       <c r="T191" s="2" t="inlineStr"/>
       <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -12389,6 +12833,7 @@
       <c r="S192" s="2" t="inlineStr"/>
       <c r="T192" s="2" t="inlineStr"/>
       <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -12476,6 +12921,11 @@
       <c r="S193" s="2" t="inlineStr"/>
       <c r="T193" s="2" t="inlineStr"/>
       <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -12535,6 +12985,7 @@
       <c r="S194" s="2" t="inlineStr"/>
       <c r="T194" s="2" t="inlineStr"/>
       <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -12626,6 +13077,11 @@
         </is>
       </c>
       <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -12719,6 +13175,11 @@
       <c r="U196" s="2" t="inlineStr">
         <is>
           <t>דב וויזער;דובי ווייזר</t>
+        </is>
+      </c>
+      <c r="V196" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
         </is>
       </c>
     </row>
@@ -12784,6 +13245,7 @@
         </is>
       </c>
       <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -12835,6 +13297,7 @@
       <c r="S198" s="2" t="inlineStr"/>
       <c r="T198" s="2" t="inlineStr"/>
       <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -12918,6 +13381,11 @@
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -13005,6 +13473,11 @@
       <c r="S200" s="2" t="inlineStr"/>
       <c r="T200" s="2" t="inlineStr"/>
       <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -13092,6 +13565,11 @@
       <c r="S201" s="2" t="inlineStr"/>
       <c r="T201" s="2" t="inlineStr"/>
       <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr">
+        <is>
+          <t>ppppp-------</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13171,6 +13649,11 @@
         </is>
       </c>
       <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -13222,6 +13705,7 @@
         </is>
       </c>
       <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -13281,6 +13765,7 @@
       <c r="S204" s="2" t="inlineStr"/>
       <c r="T204" s="2" t="inlineStr"/>
       <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -13352,6 +13837,11 @@
         </is>
       </c>
       <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -13431,6 +13921,11 @@
         </is>
       </c>
       <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -13482,6 +13977,7 @@
       <c r="S207" s="2" t="inlineStr"/>
       <c r="T207" s="2" t="inlineStr"/>
       <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -13525,6 +14021,7 @@
       <c r="S208" s="2" t="inlineStr"/>
       <c r="T208" s="2" t="inlineStr"/>
       <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -13568,6 +14065,7 @@
       <c r="S209" s="2" t="inlineStr"/>
       <c r="T209" s="2" t="inlineStr"/>
       <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -13623,6 +14121,7 @@
         </is>
       </c>
       <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -13681,6 +14180,7 @@
       </c>
       <c r="T211" s="2" t="inlineStr"/>
       <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -13732,6 +14232,7 @@
       <c r="S212" s="2" t="inlineStr"/>
       <c r="T212" s="2" t="inlineStr"/>
       <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -13775,6 +14276,7 @@
       <c r="S213" s="2" t="inlineStr"/>
       <c r="T213" s="2" t="inlineStr"/>
       <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -13822,6 +14324,7 @@
       <c r="S214" s="2" t="inlineStr"/>
       <c r="T214" s="2" t="inlineStr"/>
       <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -13869,6 +14372,7 @@
       <c r="S215" s="2" t="inlineStr"/>
       <c r="T215" s="2" t="inlineStr"/>
       <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -13912,6 +14416,7 @@
       <c r="S216" s="2" t="inlineStr"/>
       <c r="T216" s="2" t="inlineStr"/>
       <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -13955,6 +14460,7 @@
       <c r="S217" s="2" t="inlineStr"/>
       <c r="T217" s="2" t="inlineStr"/>
       <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -14034,6 +14540,11 @@
       <c r="S218" s="2" t="inlineStr"/>
       <c r="T218" s="2" t="inlineStr"/>
       <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -14085,6 +14596,7 @@
       <c r="S219" s="2" t="inlineStr"/>
       <c r="T219" s="2" t="inlineStr"/>
       <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -14136,6 +14648,7 @@
       <c r="S220" s="2" t="inlineStr"/>
       <c r="T220" s="2" t="inlineStr"/>
       <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -14187,6 +14700,7 @@
       <c r="S221" s="2" t="inlineStr"/>
       <c r="T221" s="2" t="inlineStr"/>
       <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -14230,6 +14744,7 @@
       <c r="S222" s="2" t="inlineStr"/>
       <c r="T222" s="2" t="inlineStr"/>
       <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -14281,6 +14796,7 @@
       <c r="S223" s="2" t="inlineStr"/>
       <c r="T223" s="2" t="inlineStr"/>
       <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -14332,6 +14848,7 @@
       <c r="S224" s="2" t="inlineStr"/>
       <c r="T224" s="2" t="inlineStr"/>
       <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -14411,6 +14928,11 @@
       <c r="S225" s="2" t="inlineStr"/>
       <c r="T225" s="2" t="inlineStr"/>
       <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -14502,6 +15024,11 @@
       </c>
       <c r="T226" s="2" t="inlineStr"/>
       <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -14581,6 +15108,11 @@
         </is>
       </c>
       <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr">
+        <is>
+          <t>-----pp-----</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -14628,6 +15160,7 @@
       <c r="S228" s="2" t="inlineStr"/>
       <c r="T228" s="2" t="inlineStr"/>
       <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -14671,6 +15204,7 @@
       <c r="S229" s="2" t="inlineStr"/>
       <c r="T229" s="2" t="inlineStr"/>
       <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -14718,6 +15252,7 @@
       <c r="S230" s="2" t="inlineStr"/>
       <c r="T230" s="2" t="inlineStr"/>
       <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -14797,6 +15332,11 @@
       <c r="S231" s="2" t="inlineStr"/>
       <c r="T231" s="2" t="inlineStr"/>
       <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -14852,6 +15392,7 @@
       <c r="S232" s="2" t="inlineStr"/>
       <c r="T232" s="2" t="inlineStr"/>
       <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -14939,6 +15480,11 @@
         </is>
       </c>
       <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -14982,6 +15528,7 @@
       <c r="S234" s="2" t="inlineStr"/>
       <c r="T234" s="2" t="inlineStr"/>
       <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -15037,6 +15584,7 @@
         </is>
       </c>
       <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -15092,6 +15640,7 @@
       <c r="S236" s="2" t="inlineStr"/>
       <c r="T236" s="2" t="inlineStr"/>
       <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -15143,6 +15692,7 @@
       <c r="S237" s="2" t="inlineStr"/>
       <c r="T237" s="2" t="inlineStr"/>
       <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -15186,6 +15736,7 @@
       <c r="S238" s="2" t="inlineStr"/>
       <c r="T238" s="2" t="inlineStr"/>
       <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -15229,6 +15780,7 @@
       <c r="S239" s="2" t="inlineStr"/>
       <c r="T239" s="2" t="inlineStr"/>
       <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -15316,6 +15868,11 @@
       <c r="S240" s="2" t="inlineStr"/>
       <c r="T240" s="2" t="inlineStr"/>
       <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -15403,6 +15960,11 @@
       <c r="S241" s="2" t="inlineStr"/>
       <c r="T241" s="2" t="inlineStr"/>
       <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr">
+        <is>
+          <t>pppxpp------</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -15446,6 +16008,7 @@
       <c r="S242" s="2" t="inlineStr"/>
       <c r="T242" s="2" t="inlineStr"/>
       <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -15525,6 +16088,11 @@
       <c r="S243" s="2" t="inlineStr"/>
       <c r="T243" s="2" t="inlineStr"/>
       <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -15572,6 +16140,7 @@
       <c r="S244" s="2" t="inlineStr"/>
       <c r="T244" s="2" t="inlineStr"/>
       <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -15663,6 +16232,11 @@
         </is>
       </c>
       <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -15754,6 +16328,11 @@
         </is>
       </c>
       <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -15845,6 +16424,11 @@
         </is>
       </c>
       <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -15888,6 +16472,7 @@
       <c r="S248" s="2" t="inlineStr"/>
       <c r="T248" s="2" t="inlineStr"/>
       <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -15939,6 +16524,7 @@
       <c r="S249" s="2" t="inlineStr"/>
       <c r="T249" s="2" t="inlineStr"/>
       <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -16026,6 +16612,11 @@
       <c r="S250" s="2" t="inlineStr"/>
       <c r="T250" s="2" t="inlineStr"/>
       <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -16105,6 +16696,11 @@
         </is>
       </c>
       <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -16160,6 +16756,7 @@
         </is>
       </c>
       <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -16211,6 +16808,7 @@
       <c r="S253" s="2" t="inlineStr"/>
       <c r="T253" s="2" t="inlineStr"/>
       <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -16262,6 +16860,7 @@
       <c r="S254" s="2" t="inlineStr"/>
       <c r="T254" s="2" t="inlineStr"/>
       <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -16313,6 +16912,7 @@
       <c r="S255" s="2" t="inlineStr"/>
       <c r="T255" s="2" t="inlineStr"/>
       <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -16364,6 +16964,7 @@
       <c r="S256" s="2" t="inlineStr"/>
       <c r="T256" s="2" t="inlineStr"/>
       <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -16443,6 +17044,11 @@
       <c r="S257" s="2" t="inlineStr"/>
       <c r="T257" s="2" t="inlineStr"/>
       <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -16486,6 +17092,7 @@
       <c r="S258" s="2" t="inlineStr"/>
       <c r="T258" s="2" t="inlineStr"/>
       <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -16537,6 +17144,7 @@
       <c r="S259" s="2" t="inlineStr"/>
       <c r="T259" s="2" t="inlineStr"/>
       <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -16580,6 +17188,7 @@
       <c r="S260" s="2" t="inlineStr"/>
       <c r="T260" s="2" t="inlineStr"/>
       <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -16663,6 +17272,11 @@
       <c r="S261" s="2" t="inlineStr"/>
       <c r="T261" s="2" t="inlineStr"/>
       <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -16750,6 +17364,11 @@
       <c r="S262" s="2" t="inlineStr"/>
       <c r="T262" s="2" t="inlineStr"/>
       <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -16793,6 +17412,7 @@
       <c r="S263" s="2" t="inlineStr"/>
       <c r="T263" s="2" t="inlineStr"/>
       <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -16880,6 +17500,11 @@
       <c r="S264" s="2" t="inlineStr"/>
       <c r="T264" s="2" t="inlineStr"/>
       <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -16935,6 +17560,7 @@
       </c>
       <c r="T265" s="2" t="inlineStr"/>
       <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -16986,6 +17612,7 @@
       <c r="S266" s="2" t="inlineStr"/>
       <c r="T266" s="2" t="inlineStr"/>
       <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -17037,6 +17664,7 @@
         </is>
       </c>
       <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -17124,6 +17752,11 @@
       <c r="S268" s="2" t="inlineStr"/>
       <c r="T268" s="2" t="inlineStr"/>
       <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -17195,6 +17828,11 @@
       <c r="S269" s="2" t="inlineStr"/>
       <c r="T269" s="2" t="inlineStr"/>
       <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -17246,6 +17884,7 @@
       <c r="S270" s="2" t="inlineStr"/>
       <c r="T270" s="2" t="inlineStr"/>
       <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -17305,6 +17944,7 @@
       <c r="S271" s="2" t="inlineStr"/>
       <c r="T271" s="2" t="inlineStr"/>
       <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -17356,6 +17996,7 @@
       <c r="S272" s="2" t="inlineStr"/>
       <c r="T272" s="2" t="inlineStr"/>
       <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -17407,6 +18048,7 @@
       <c r="S273" s="2" t="inlineStr"/>
       <c r="T273" s="2" t="inlineStr"/>
       <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -17458,6 +18100,7 @@
       <c r="S274" s="2" t="inlineStr"/>
       <c r="T274" s="2" t="inlineStr"/>
       <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -17545,6 +18188,11 @@
       <c r="S275" s="2" t="inlineStr"/>
       <c r="T275" s="2" t="inlineStr"/>
       <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -17636,6 +18284,11 @@
       </c>
       <c r="T276" s="2" t="inlineStr"/>
       <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -17687,6 +18340,7 @@
       <c r="S277" s="2" t="inlineStr"/>
       <c r="T277" s="2" t="inlineStr"/>
       <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -17774,6 +18428,11 @@
       <c r="S278" s="2" t="inlineStr"/>
       <c r="T278" s="2" t="inlineStr"/>
       <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -17849,6 +18508,11 @@
       <c r="S279" s="2" t="inlineStr"/>
       <c r="T279" s="2" t="inlineStr"/>
       <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr">
+        <is>
+          <t>pppppppppppp</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -17916,6 +18580,7 @@
         </is>
       </c>
       <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -17967,6 +18632,7 @@
       <c r="S281" s="2" t="inlineStr"/>
       <c r="T281" s="2" t="inlineStr"/>
       <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -18018,6 +18684,7 @@
       <c r="S282" s="2" t="inlineStr"/>
       <c r="T282" s="2" t="inlineStr"/>
       <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -18073,6 +18740,7 @@
         </is>
       </c>
       <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -18124,6 +18792,7 @@
       <c r="S284" s="2" t="inlineStr"/>
       <c r="T284" s="2" t="inlineStr"/>
       <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -18179,6 +18848,7 @@
         </is>
       </c>
       <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -18234,6 +18904,7 @@
       <c r="S286" s="2" t="inlineStr"/>
       <c r="T286" s="2" t="inlineStr"/>
       <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -18285,6 +18956,7 @@
       <c r="S287" s="2" t="inlineStr"/>
       <c r="T287" s="2" t="inlineStr"/>
       <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -18336,6 +19008,7 @@
       <c r="S288" s="2" t="inlineStr"/>
       <c r="T288" s="2" t="inlineStr"/>
       <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -18407,6 +19080,11 @@
         </is>
       </c>
       <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -18458,6 +19136,7 @@
       <c r="S290" s="2" t="inlineStr"/>
       <c r="T290" s="2" t="inlineStr"/>
       <c r="U290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -18529,6 +19208,7 @@
       <c r="S291" s="2" t="inlineStr"/>
       <c r="T291" s="2" t="inlineStr"/>
       <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -18616,6 +19296,11 @@
       <c r="S292" s="2" t="inlineStr"/>
       <c r="T292" s="2" t="inlineStr"/>
       <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -18663,6 +19348,7 @@
       <c r="S293" s="2" t="inlineStr"/>
       <c r="T293" s="2" t="inlineStr"/>
       <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -18714,6 +19400,7 @@
       <c r="S294" s="2" t="inlineStr"/>
       <c r="T294" s="2" t="inlineStr"/>
       <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -18797,6 +19484,11 @@
       <c r="S295" s="2" t="inlineStr"/>
       <c r="T295" s="2" t="inlineStr"/>
       <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr">
+        <is>
+          <t>---pppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -18848,6 +19540,7 @@
       <c r="S296" s="2" t="inlineStr"/>
       <c r="T296" s="2" t="inlineStr"/>
       <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -18899,6 +19592,7 @@
       <c r="S297" s="2" t="inlineStr"/>
       <c r="T297" s="2" t="inlineStr"/>
       <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -18950,6 +19644,7 @@
       <c r="S298" s="2" t="inlineStr"/>
       <c r="T298" s="2" t="inlineStr"/>
       <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -18993,6 +19688,7 @@
       <c r="S299" s="2" t="inlineStr"/>
       <c r="T299" s="2" t="inlineStr"/>
       <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -19076,6 +19772,11 @@
       <c r="S300" s="2" t="inlineStr"/>
       <c r="T300" s="2" t="inlineStr"/>
       <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -19119,6 +19820,7 @@
       <c r="S301" s="2" t="inlineStr"/>
       <c r="T301" s="2" t="inlineStr"/>
       <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -19166,6 +19868,7 @@
       <c r="S302" s="2" t="inlineStr"/>
       <c r="T302" s="2" t="inlineStr"/>
       <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -19217,6 +19920,7 @@
       <c r="S303" s="2" t="inlineStr"/>
       <c r="T303" s="2" t="inlineStr"/>
       <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -19260,6 +19964,7 @@
       <c r="S304" s="2" t="inlineStr"/>
       <c r="T304" s="2" t="inlineStr"/>
       <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -19311,6 +20016,7 @@
         </is>
       </c>
       <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -19354,6 +20060,7 @@
       <c r="S306" s="2" t="inlineStr"/>
       <c r="T306" s="2" t="inlineStr"/>
       <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -19417,6 +20124,7 @@
         </is>
       </c>
       <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -19472,6 +20180,7 @@
         </is>
       </c>
       <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -19537,6 +20246,7 @@
       </c>
       <c r="T309" s="2" t="inlineStr"/>
       <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -19592,6 +20302,7 @@
       <c r="S310" s="2" t="inlineStr"/>
       <c r="T310" s="2" t="inlineStr"/>
       <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -19643,6 +20354,7 @@
         </is>
       </c>
       <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -19702,6 +20414,7 @@
       <c r="S312" s="2" t="inlineStr"/>
       <c r="T312" s="2" t="inlineStr"/>
       <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -19753,6 +20466,7 @@
       <c r="S313" s="2" t="inlineStr"/>
       <c r="T313" s="2" t="inlineStr"/>
       <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -19812,6 +20526,7 @@
       <c r="S314" s="2" t="inlineStr"/>
       <c r="T314" s="2" t="inlineStr"/>
       <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -19859,6 +20574,7 @@
       <c r="S315" s="2" t="inlineStr"/>
       <c r="T315" s="2" t="inlineStr"/>
       <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -19942,6 +20658,11 @@
         </is>
       </c>
       <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -20029,6 +20750,11 @@
       <c r="S317" s="2" t="inlineStr"/>
       <c r="T317" s="2" t="inlineStr"/>
       <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr">
+        <is>
+          <t>pppp--p-----</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -20080,6 +20806,7 @@
       <c r="S318" s="2" t="inlineStr"/>
       <c r="T318" s="2" t="inlineStr"/>
       <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -20131,6 +20858,7 @@
         </is>
       </c>
       <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -20218,6 +20946,11 @@
       <c r="S320" s="2" t="inlineStr"/>
       <c r="T320" s="2" t="inlineStr"/>
       <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -20305,6 +21038,11 @@
       <c r="S321" s="2" t="inlineStr"/>
       <c r="T321" s="2" t="inlineStr"/>
       <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -20364,6 +21102,7 @@
       <c r="S322" s="2" t="inlineStr"/>
       <c r="T322" s="2" t="inlineStr"/>
       <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -20415,6 +21154,7 @@
         </is>
       </c>
       <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -20462,6 +21202,7 @@
       <c r="S324" s="2" t="inlineStr"/>
       <c r="T324" s="2" t="inlineStr"/>
       <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -20513,6 +21254,7 @@
       <c r="S325" s="2" t="inlineStr"/>
       <c r="T325" s="2" t="inlineStr"/>
       <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -20572,6 +21314,7 @@
           <t>שאנא מונוקר;שיינא מונקור</t>
         </is>
       </c>
+      <c r="V326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -20615,6 +21358,7 @@
       <c r="S327" s="2" t="inlineStr"/>
       <c r="T327" s="2" t="inlineStr"/>
       <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -20662,6 +21406,7 @@
       <c r="S328" s="2" t="inlineStr"/>
       <c r="T328" s="2" t="inlineStr"/>
       <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -20717,6 +21462,7 @@
       <c r="S329" s="2" t="inlineStr"/>
       <c r="T329" s="2" t="inlineStr"/>
       <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -20772,6 +21518,7 @@
       </c>
       <c r="T330" s="2" t="inlineStr"/>
       <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -20815,6 +21562,7 @@
       <c r="S331" s="2" t="inlineStr"/>
       <c r="T331" s="2" t="inlineStr"/>
       <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -20890,6 +21638,7 @@
         </is>
       </c>
       <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -20973,6 +21722,11 @@
       <c r="S333" s="2" t="inlineStr"/>
       <c r="T333" s="2" t="inlineStr"/>
       <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -21024,6 +21778,7 @@
       <c r="S334" s="2" t="inlineStr"/>
       <c r="T334" s="2" t="inlineStr"/>
       <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -21111,6 +21866,11 @@
       <c r="S335" s="2" t="inlineStr"/>
       <c r="T335" s="2" t="inlineStr"/>
       <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -21182,6 +21942,11 @@
       <c r="S336" s="2" t="inlineStr"/>
       <c r="T336" s="2" t="inlineStr"/>
       <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -21269,6 +22034,11 @@
       <c r="S337" s="2" t="inlineStr"/>
       <c r="T337" s="2" t="inlineStr"/>
       <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -21356,6 +22126,11 @@
       <c r="S338" s="2" t="inlineStr"/>
       <c r="T338" s="2" t="inlineStr"/>
       <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -21435,6 +22210,11 @@
       <c r="S339" s="2" t="inlineStr"/>
       <c r="T339" s="2" t="inlineStr"/>
       <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -21522,6 +22302,11 @@
       <c r="S340" s="2" t="inlineStr"/>
       <c r="T340" s="2" t="inlineStr"/>
       <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -21573,6 +22358,7 @@
       <c r="S341" s="2" t="inlineStr"/>
       <c r="T341" s="2" t="inlineStr"/>
       <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -21624,6 +22410,7 @@
       <c r="S342" s="2" t="inlineStr"/>
       <c r="T342" s="2" t="inlineStr"/>
       <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -21667,6 +22454,7 @@
       <c r="S343" s="2" t="inlineStr"/>
       <c r="T343" s="2" t="inlineStr"/>
       <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -21746,6 +22534,11 @@
       <c r="S344" s="2" t="inlineStr"/>
       <c r="T344" s="2" t="inlineStr"/>
       <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -21805,6 +22598,7 @@
       <c r="S345" s="2" t="inlineStr"/>
       <c r="T345" s="2" t="inlineStr"/>
       <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -21884,6 +22678,11 @@
         </is>
       </c>
       <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -21967,6 +22766,11 @@
         </is>
       </c>
       <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -22054,6 +22858,11 @@
       <c r="S348" s="2" t="inlineStr"/>
       <c r="T348" s="2" t="inlineStr"/>
       <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -22105,6 +22914,7 @@
       <c r="S349" s="2" t="inlineStr"/>
       <c r="T349" s="2" t="inlineStr"/>
       <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -22192,6 +23002,11 @@
       <c r="S350" s="2" t="inlineStr"/>
       <c r="T350" s="2" t="inlineStr"/>
       <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -22275,6 +23090,11 @@
       <c r="S351" s="2" t="inlineStr"/>
       <c r="T351" s="2" t="inlineStr"/>
       <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr">
+        <is>
+          <t>pppppppp----</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -22326,6 +23146,7 @@
       <c r="S352" s="2" t="inlineStr"/>
       <c r="T352" s="2" t="inlineStr"/>
       <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -22369,6 +23190,7 @@
       <c r="S353" s="2" t="inlineStr"/>
       <c r="T353" s="2" t="inlineStr"/>
       <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -22412,6 +23234,7 @@
       <c r="S354" s="2" t="inlineStr"/>
       <c r="T354" s="2" t="inlineStr"/>
       <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -22471,6 +23294,7 @@
       <c r="S355" s="2" t="inlineStr"/>
       <c r="T355" s="2" t="inlineStr"/>
       <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -22518,6 +23342,7 @@
       <c r="S356" s="2" t="inlineStr"/>
       <c r="T356" s="2" t="inlineStr"/>
       <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -22569,6 +23394,7 @@
         </is>
       </c>
       <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -22644,6 +23470,11 @@
       <c r="S358" s="2" t="inlineStr"/>
       <c r="T358" s="2" t="inlineStr"/>
       <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -22699,6 +23530,7 @@
       <c r="S359" s="2" t="inlineStr"/>
       <c r="T359" s="2" t="inlineStr"/>
       <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -22750,6 +23582,7 @@
       <c r="S360" s="2" t="inlineStr"/>
       <c r="T360" s="2" t="inlineStr"/>
       <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -22797,6 +23630,7 @@
       <c r="S361" s="2" t="inlineStr"/>
       <c r="T361" s="2" t="inlineStr"/>
       <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -22884,6 +23718,11 @@
       <c r="S362" s="2" t="inlineStr"/>
       <c r="T362" s="2" t="inlineStr"/>
       <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -22927,6 +23766,7 @@
       <c r="S363" s="2" t="inlineStr"/>
       <c r="T363" s="2" t="inlineStr"/>
       <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -22978,6 +23818,7 @@
       <c r="S364" s="2" t="inlineStr"/>
       <c r="T364" s="2" t="inlineStr"/>
       <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -23029,6 +23870,7 @@
       <c r="S365" s="2" t="inlineStr"/>
       <c r="T365" s="2" t="inlineStr"/>
       <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -23072,6 +23914,7 @@
       <c r="S366" s="2" t="inlineStr"/>
       <c r="T366" s="2" t="inlineStr"/>
       <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -23159,6 +24002,11 @@
       <c r="S367" s="2" t="inlineStr"/>
       <c r="T367" s="2" t="inlineStr"/>
       <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -23246,6 +24094,11 @@
       <c r="S368" s="2" t="inlineStr"/>
       <c r="T368" s="2" t="inlineStr"/>
       <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -23333,6 +24186,11 @@
       <c r="S369" s="2" t="inlineStr"/>
       <c r="T369" s="2" t="inlineStr"/>
       <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -23384,6 +24242,7 @@
         </is>
       </c>
       <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -23479,6 +24338,11 @@
       </c>
       <c r="T371" s="2" t="inlineStr"/>
       <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -23558,6 +24422,11 @@
       <c r="S372" s="2" t="inlineStr"/>
       <c r="T372" s="2" t="inlineStr"/>
       <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr">
+        <is>
+          <t>pxxxxxp-----</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -23601,6 +24470,7 @@
       <c r="S373" s="2" t="inlineStr"/>
       <c r="T373" s="2" t="inlineStr"/>
       <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -23688,6 +24558,11 @@
       <c r="S374" s="2" t="inlineStr"/>
       <c r="T374" s="2" t="inlineStr"/>
       <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -23743,6 +24618,7 @@
       <c r="S375" s="2" t="inlineStr"/>
       <c r="T375" s="2" t="inlineStr"/>
       <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -23822,6 +24698,11 @@
       <c r="S376" s="2" t="inlineStr"/>
       <c r="T376" s="2" t="inlineStr"/>
       <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -23873,6 +24754,7 @@
       <c r="S377" s="2" t="inlineStr"/>
       <c r="T377" s="2" t="inlineStr"/>
       <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -23924,6 +24806,7 @@
       <c r="S378" s="2" t="inlineStr"/>
       <c r="T378" s="2" t="inlineStr"/>
       <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -24011,6 +24894,11 @@
       <c r="S379" s="2" t="inlineStr"/>
       <c r="T379" s="2" t="inlineStr"/>
       <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -24098,6 +24986,11 @@
       <c r="S380" s="2" t="inlineStr"/>
       <c r="T380" s="2" t="inlineStr"/>
       <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -24149,6 +25042,7 @@
       <c r="S381" s="2" t="inlineStr"/>
       <c r="T381" s="2" t="inlineStr"/>
       <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -24236,6 +25130,11 @@
       <c r="S382" s="2" t="inlineStr"/>
       <c r="T382" s="2" t="inlineStr"/>
       <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -24291,6 +25190,7 @@
       <c r="S383" s="2" t="inlineStr"/>
       <c r="T383" s="2" t="inlineStr"/>
       <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -24342,6 +25242,7 @@
       <c r="S384" s="2" t="inlineStr"/>
       <c r="T384" s="2" t="inlineStr"/>
       <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -24421,6 +25322,11 @@
         </is>
       </c>
       <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr">
+        <is>
+          <t>pxxxppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -24492,6 +25398,7 @@
       <c r="S386" s="2" t="inlineStr"/>
       <c r="T386" s="2" t="inlineStr"/>
       <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -24535,6 +25442,7 @@
       <c r="S387" s="2" t="inlineStr"/>
       <c r="T387" s="2" t="inlineStr"/>
       <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -24578,6 +25486,7 @@
       <c r="S388" s="2" t="inlineStr"/>
       <c r="T388" s="2" t="inlineStr"/>
       <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -24625,6 +25534,7 @@
       <c r="S389" s="2" t="inlineStr"/>
       <c r="T389" s="2" t="inlineStr"/>
       <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -24668,6 +25578,7 @@
       <c r="S390" s="2" t="inlineStr"/>
       <c r="T390" s="2" t="inlineStr"/>
       <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -24743,6 +25654,11 @@
       <c r="S391" s="2" t="inlineStr"/>
       <c r="T391" s="2" t="inlineStr"/>
       <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -24794,6 +25710,7 @@
       <c r="S392" s="2" t="inlineStr"/>
       <c r="T392" s="2" t="inlineStr"/>
       <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -24845,6 +25762,7 @@
       <c r="S393" s="2" t="inlineStr"/>
       <c r="T393" s="2" t="inlineStr"/>
       <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -24904,6 +25822,7 @@
       <c r="S394" s="2" t="inlineStr"/>
       <c r="T394" s="2" t="inlineStr"/>
       <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -24959,6 +25878,7 @@
         </is>
       </c>
       <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -25010,6 +25930,7 @@
       <c r="S396" s="2" t="inlineStr"/>
       <c r="T396" s="2" t="inlineStr"/>
       <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -25061,6 +25982,7 @@
       <c r="S397" s="2" t="inlineStr"/>
       <c r="T397" s="2" t="inlineStr"/>
       <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -25152,6 +26074,11 @@
         </is>
       </c>
       <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -25203,6 +26130,7 @@
         </is>
       </c>
       <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -25290,6 +26218,11 @@
       <c r="S400" s="2" t="inlineStr"/>
       <c r="T400" s="2" t="inlineStr"/>
       <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -25337,6 +26270,7 @@
       <c r="S401" s="2" t="inlineStr"/>
       <c r="T401" s="2" t="inlineStr"/>
       <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -25420,6 +26354,11 @@
         </is>
       </c>
       <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -25471,6 +26410,7 @@
       <c r="S403" s="2" t="inlineStr"/>
       <c r="T403" s="2" t="inlineStr"/>
       <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -25518,6 +26458,7 @@
       <c r="S404" s="2" t="inlineStr"/>
       <c r="T404" s="2" t="inlineStr"/>
       <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -25569,6 +26510,7 @@
       <c r="S405" s="2" t="inlineStr"/>
       <c r="T405" s="2" t="inlineStr"/>
       <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -25620,6 +26562,7 @@
       <c r="S406" s="2" t="inlineStr"/>
       <c r="T406" s="2" t="inlineStr"/>
       <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -25671,6 +26614,7 @@
       <c r="S407" s="2" t="inlineStr"/>
       <c r="T407" s="2" t="inlineStr"/>
       <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -25754,6 +26698,11 @@
       <c r="S408" s="2" t="inlineStr"/>
       <c r="T408" s="2" t="inlineStr"/>
       <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -25833,6 +26782,11 @@
       <c r="S409" s="2" t="inlineStr"/>
       <c r="T409" s="2" t="inlineStr"/>
       <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -25924,6 +26878,11 @@
         </is>
       </c>
       <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -25975,6 +26934,7 @@
       <c r="S411" s="2" t="inlineStr"/>
       <c r="T411" s="2" t="inlineStr"/>
       <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -26018,6 +26978,7 @@
       <c r="S412" s="2" t="inlineStr"/>
       <c r="T412" s="2" t="inlineStr"/>
       <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -26105,6 +27066,11 @@
       <c r="S413" s="2" t="inlineStr"/>
       <c r="T413" s="2" t="inlineStr"/>
       <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -26184,6 +27150,11 @@
         </is>
       </c>
       <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -26271,6 +27242,11 @@
       <c r="S415" s="2" t="inlineStr"/>
       <c r="T415" s="2" t="inlineStr"/>
       <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -26322,6 +27298,7 @@
       <c r="S416" s="2" t="inlineStr"/>
       <c r="T416" s="2" t="inlineStr"/>
       <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -26369,6 +27346,7 @@
       <c r="S417" s="2" t="inlineStr"/>
       <c r="T417" s="2" t="inlineStr"/>
       <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -26456,6 +27434,11 @@
       <c r="S418" s="2" t="inlineStr"/>
       <c r="T418" s="2" t="inlineStr"/>
       <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -26511,6 +27494,7 @@
       <c r="S419" s="2" t="inlineStr"/>
       <c r="T419" s="2" t="inlineStr"/>
       <c r="U419" s="2" t="inlineStr"/>
+      <c r="V419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -26562,6 +27546,7 @@
       <c r="S420" s="2" t="inlineStr"/>
       <c r="T420" s="2" t="inlineStr"/>
       <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -26641,6 +27626,11 @@
       <c r="S421" s="2" t="inlineStr"/>
       <c r="T421" s="2" t="inlineStr"/>
       <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr">
+        <is>
+          <t>pppp--------</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -26712,6 +27702,7 @@
       <c r="S422" s="2" t="inlineStr"/>
       <c r="T422" s="2" t="inlineStr"/>
       <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -26763,6 +27754,7 @@
       <c r="S423" s="2" t="inlineStr"/>
       <c r="T423" s="2" t="inlineStr"/>
       <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -26822,6 +27814,7 @@
       <c r="S424" s="2" t="inlineStr"/>
       <c r="T424" s="2" t="inlineStr"/>
       <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -26873,6 +27866,7 @@
       <c r="S425" s="2" t="inlineStr"/>
       <c r="T425" s="2" t="inlineStr"/>
       <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -26920,6 +27914,7 @@
       <c r="S426" s="2" t="inlineStr"/>
       <c r="T426" s="2" t="inlineStr"/>
       <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -26967,6 +27962,7 @@
       <c r="S427" s="2" t="inlineStr"/>
       <c r="T427" s="2" t="inlineStr"/>
       <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -27054,6 +28050,11 @@
       <c r="S428" s="2" t="inlineStr"/>
       <c r="T428" s="2" t="inlineStr"/>
       <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -27105,6 +28106,7 @@
       <c r="S429" s="2" t="inlineStr"/>
       <c r="T429" s="2" t="inlineStr"/>
       <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -27156,6 +28158,7 @@
       <c r="S430" s="2" t="inlineStr"/>
       <c r="T430" s="2" t="inlineStr"/>
       <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -27199,6 +28202,7 @@
       <c r="S431" s="2" t="inlineStr"/>
       <c r="T431" s="2" t="inlineStr"/>
       <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -27250,6 +28254,7 @@
       <c r="S432" s="2" t="inlineStr"/>
       <c r="T432" s="2" t="inlineStr"/>
       <c r="U432" s="2" t="inlineStr"/>
+      <c r="V432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -27305,6 +28310,7 @@
       </c>
       <c r="T433" s="2" t="inlineStr"/>
       <c r="U433" s="2" t="inlineStr"/>
+      <c r="V433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -27392,6 +28398,11 @@
       <c r="S434" s="2" t="inlineStr"/>
       <c r="T434" s="2" t="inlineStr"/>
       <c r="U434" s="2" t="inlineStr"/>
+      <c r="V434" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -27475,6 +28486,11 @@
       <c r="S435" s="2" t="inlineStr"/>
       <c r="T435" s="2" t="inlineStr"/>
       <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="inlineStr">
+        <is>
+          <t>pppppxx-----</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -27562,6 +28578,11 @@
         </is>
       </c>
       <c r="U436" s="2" t="inlineStr"/>
+      <c r="V436" s="2" t="inlineStr">
+        <is>
+          <t>--pppxx-----</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -27625,6 +28646,7 @@
       <c r="S437" s="2" t="inlineStr"/>
       <c r="T437" s="2" t="inlineStr"/>
       <c r="U437" s="2" t="inlineStr"/>
+      <c r="V437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -27688,6 +28710,7 @@
         </is>
       </c>
       <c r="U438" s="2" t="inlineStr"/>
+      <c r="V438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -27731,6 +28754,7 @@
       <c r="S439" s="2" t="inlineStr"/>
       <c r="T439" s="2" t="inlineStr"/>
       <c r="U439" s="2" t="inlineStr"/>
+      <c r="V439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -27774,6 +28798,7 @@
       <c r="S440" s="2" t="inlineStr"/>
       <c r="T440" s="2" t="inlineStr"/>
       <c r="U440" s="2" t="inlineStr"/>
+      <c r="V440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -27861,6 +28886,11 @@
       <c r="S441" s="2" t="inlineStr"/>
       <c r="T441" s="2" t="inlineStr"/>
       <c r="U441" s="2" t="inlineStr"/>
+      <c r="V441" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -27912,6 +28942,7 @@
       <c r="S442" s="2" t="inlineStr"/>
       <c r="T442" s="2" t="inlineStr"/>
       <c r="U442" s="2" t="inlineStr"/>
+      <c r="V442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -27967,6 +28998,7 @@
         </is>
       </c>
       <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -28010,6 +29042,7 @@
       <c r="S444" s="2" t="inlineStr"/>
       <c r="T444" s="2" t="inlineStr"/>
       <c r="U444" s="2" t="inlineStr"/>
+      <c r="V444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -28101,6 +29134,11 @@
       </c>
       <c r="T445" s="2" t="inlineStr"/>
       <c r="U445" s="2" t="inlineStr"/>
+      <c r="V445" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -28144,6 +29182,7 @@
       <c r="S446" s="2" t="inlineStr"/>
       <c r="T446" s="2" t="inlineStr"/>
       <c r="U446" s="2" t="inlineStr"/>
+      <c r="V446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -28231,6 +29270,11 @@
       </c>
       <c r="T447" s="2" t="inlineStr"/>
       <c r="U447" s="2" t="inlineStr"/>
+      <c r="V447" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -28274,6 +29318,7 @@
       <c r="S448" s="2" t="inlineStr"/>
       <c r="T448" s="2" t="inlineStr"/>
       <c r="U448" s="2" t="inlineStr"/>
+      <c r="V448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -28317,6 +29362,7 @@
       <c r="S449" s="2" t="inlineStr"/>
       <c r="T449" s="2" t="inlineStr"/>
       <c r="U449" s="2" t="inlineStr"/>
+      <c r="V449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -28368,6 +29414,7 @@
       <c r="S450" s="2" t="inlineStr"/>
       <c r="T450" s="2" t="inlineStr"/>
       <c r="U450" s="2" t="inlineStr"/>
+      <c r="V450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -28419,6 +29466,7 @@
       <c r="S451" s="2" t="inlineStr"/>
       <c r="T451" s="2" t="inlineStr"/>
       <c r="U451" s="2" t="inlineStr"/>
+      <c r="V451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -28498,6 +29546,11 @@
         </is>
       </c>
       <c r="U452" s="2" t="inlineStr"/>
+      <c r="V452" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -28549,6 +29602,7 @@
       <c r="S453" s="2" t="inlineStr"/>
       <c r="T453" s="2" t="inlineStr"/>
       <c r="U453" s="2" t="inlineStr"/>
+      <c r="V453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -28608,6 +29662,7 @@
       <c r="S454" s="2" t="inlineStr"/>
       <c r="T454" s="2" t="inlineStr"/>
       <c r="U454" s="2" t="inlineStr"/>
+      <c r="V454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -28651,6 +29706,7 @@
       <c r="S455" s="2" t="inlineStr"/>
       <c r="T455" s="2" t="inlineStr"/>
       <c r="U455" s="2" t="inlineStr"/>
+      <c r="V455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -28702,6 +29758,7 @@
       <c r="S456" s="2" t="inlineStr"/>
       <c r="T456" s="2" t="inlineStr"/>
       <c r="U456" s="2" t="inlineStr"/>
+      <c r="V456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -28753,6 +29810,7 @@
       <c r="S457" s="2" t="inlineStr"/>
       <c r="T457" s="2" t="inlineStr"/>
       <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -28840,6 +29898,11 @@
       <c r="S458" s="2" t="inlineStr"/>
       <c r="T458" s="2" t="inlineStr"/>
       <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -28891,6 +29954,7 @@
       <c r="S459" s="2" t="inlineStr"/>
       <c r="T459" s="2" t="inlineStr"/>
       <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -28946,6 +30010,7 @@
       </c>
       <c r="T460" s="2" t="inlineStr"/>
       <c r="U460" s="2" t="inlineStr"/>
+      <c r="V460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -29005,6 +30070,7 @@
       <c r="S461" s="2" t="inlineStr"/>
       <c r="T461" s="2" t="inlineStr"/>
       <c r="U461" s="2" t="inlineStr"/>
+      <c r="V461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -29064,6 +30130,7 @@
       <c r="S462" s="2" t="inlineStr"/>
       <c r="T462" s="2" t="inlineStr"/>
       <c r="U462" s="2" t="inlineStr"/>
+      <c r="V462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -29119,6 +30186,7 @@
       <c r="S463" s="2" t="inlineStr"/>
       <c r="T463" s="2" t="inlineStr"/>
       <c r="U463" s="2" t="inlineStr"/>
+      <c r="V463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -29210,6 +30278,11 @@
       </c>
       <c r="T464" s="2" t="inlineStr"/>
       <c r="U464" s="2" t="inlineStr"/>
+      <c r="V464" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -29257,6 +30330,7 @@
       <c r="S465" s="2" t="inlineStr"/>
       <c r="T465" s="2" t="inlineStr"/>
       <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -29320,6 +30394,7 @@
       <c r="S466" s="2" t="inlineStr"/>
       <c r="T466" s="2" t="inlineStr"/>
       <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -29371,6 +30446,7 @@
       <c r="S467" s="2" t="inlineStr"/>
       <c r="T467" s="2" t="inlineStr"/>
       <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -29422,6 +30498,7 @@
       <c r="S468" s="2" t="inlineStr"/>
       <c r="T468" s="2" t="inlineStr"/>
       <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -29473,6 +30550,7 @@
       <c r="S469" s="2" t="inlineStr"/>
       <c r="T469" s="2" t="inlineStr"/>
       <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -29524,6 +30602,7 @@
       <c r="S470" s="2" t="inlineStr"/>
       <c r="T470" s="2" t="inlineStr"/>
       <c r="U470" s="2" t="inlineStr"/>
+      <c r="V470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -29595,6 +30674,11 @@
       <c r="S471" s="2" t="inlineStr"/>
       <c r="T471" s="2" t="inlineStr"/>
       <c r="U471" s="2" t="inlineStr"/>
+      <c r="V471" s="2" t="inlineStr">
+        <is>
+          <t>--p--p------</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -29646,6 +30730,7 @@
       <c r="S472" s="2" t="inlineStr"/>
       <c r="T472" s="2" t="inlineStr"/>
       <c r="U472" s="2" t="inlineStr"/>
+      <c r="V472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -29733,6 +30818,11 @@
       <c r="S473" s="2" t="inlineStr"/>
       <c r="T473" s="2" t="inlineStr"/>
       <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -29784,6 +30874,7 @@
       <c r="S474" s="2" t="inlineStr"/>
       <c r="T474" s="2" t="inlineStr"/>
       <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -29863,6 +30954,11 @@
       <c r="S475" s="2" t="inlineStr"/>
       <c r="T475" s="2" t="inlineStr"/>
       <c r="U475" s="2" t="inlineStr"/>
+      <c r="V475" s="2" t="inlineStr">
+        <is>
+          <t>ppxxxpp-----</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -29950,6 +31046,11 @@
       </c>
       <c r="T476" s="2" t="inlineStr"/>
       <c r="U476" s="2" t="inlineStr"/>
+      <c r="V476" s="2" t="inlineStr">
+        <is>
+          <t>pppppppppppp</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -29997,6 +31098,7 @@
       <c r="S477" s="2" t="inlineStr"/>
       <c r="T477" s="2" t="inlineStr"/>
       <c r="U477" s="2" t="inlineStr"/>
+      <c r="V477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -30048,6 +31150,7 @@
         </is>
       </c>
       <c r="U478" s="2" t="inlineStr"/>
+      <c r="V478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -30107,6 +31210,7 @@
         </is>
       </c>
       <c r="U479" s="2" t="inlineStr"/>
+      <c r="V479" s="2" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -30158,6 +31262,7 @@
         </is>
       </c>
       <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -30213,6 +31318,7 @@
         </is>
       </c>
       <c r="U481" s="2" t="inlineStr"/>
+      <c r="V481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -30296,6 +31402,11 @@
         </is>
       </c>
       <c r="U482" s="2" t="inlineStr"/>
+      <c r="V482" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -30355,6 +31466,7 @@
       <c r="S483" s="2" t="inlineStr"/>
       <c r="T483" s="2" t="inlineStr"/>
       <c r="U483" s="2" t="inlineStr"/>
+      <c r="V483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -30426,6 +31538,11 @@
         </is>
       </c>
       <c r="U484" s="2" t="inlineStr"/>
+      <c r="V484" s="2" t="inlineStr">
+        <is>
+          <t>ppppxxx-----</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -30505,6 +31622,11 @@
         </is>
       </c>
       <c r="U485" s="2" t="inlineStr"/>
+      <c r="V485" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -30556,6 +31678,7 @@
       <c r="S486" s="2" t="inlineStr"/>
       <c r="T486" s="2" t="inlineStr"/>
       <c r="U486" s="2" t="inlineStr"/>
+      <c r="V486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -30607,6 +31730,7 @@
       <c r="S487" s="2" t="inlineStr"/>
       <c r="T487" s="2" t="inlineStr"/>
       <c r="U487" s="2" t="inlineStr"/>
+      <c r="V487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -30650,6 +31774,7 @@
       <c r="S488" s="2" t="inlineStr"/>
       <c r="T488" s="2" t="inlineStr"/>
       <c r="U488" s="2" t="inlineStr"/>
+      <c r="V488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -30705,6 +31830,7 @@
         </is>
       </c>
       <c r="U489" s="2" t="inlineStr"/>
+      <c r="V489" s="2" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -30792,6 +31918,11 @@
         </is>
       </c>
       <c r="U490" s="2" t="inlineStr"/>
+      <c r="V490" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -30879,6 +32010,11 @@
       <c r="S491" s="2" t="inlineStr"/>
       <c r="T491" s="2" t="inlineStr"/>
       <c r="U491" s="2" t="inlineStr"/>
+      <c r="V491" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -30958,6 +32094,11 @@
       <c r="S492" s="2" t="inlineStr"/>
       <c r="T492" s="2" t="inlineStr"/>
       <c r="U492" s="2" t="inlineStr"/>
+      <c r="V492" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -31001,6 +32142,7 @@
       <c r="S493" s="2" t="inlineStr"/>
       <c r="T493" s="2" t="inlineStr"/>
       <c r="U493" s="2" t="inlineStr"/>
+      <c r="V493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -31052,6 +32194,7 @@
       <c r="S494" s="2" t="inlineStr"/>
       <c r="T494" s="2" t="inlineStr"/>
       <c r="U494" s="2" t="inlineStr"/>
+      <c r="V494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -31103,6 +32246,7 @@
       <c r="S495" s="2" t="inlineStr"/>
       <c r="T495" s="2" t="inlineStr"/>
       <c r="U495" s="2" t="inlineStr"/>
+      <c r="V495" s="2" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -31146,6 +32290,7 @@
       <c r="S496" s="2" t="inlineStr"/>
       <c r="T496" s="2" t="inlineStr"/>
       <c r="U496" s="2" t="inlineStr"/>
+      <c r="V496" s="2" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -31233,6 +32378,11 @@
       <c r="S497" s="2" t="inlineStr"/>
       <c r="T497" s="2" t="inlineStr"/>
       <c r="U497" s="2" t="inlineStr"/>
+      <c r="V497" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -31280,6 +32430,7 @@
       <c r="S498" s="2" t="inlineStr"/>
       <c r="T498" s="2" t="inlineStr"/>
       <c r="U498" s="2" t="inlineStr"/>
+      <c r="V498" s="2" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -31331,6 +32482,7 @@
       <c r="S499" s="2" t="inlineStr"/>
       <c r="T499" s="2" t="inlineStr"/>
       <c r="U499" s="2" t="inlineStr"/>
+      <c r="V499" s="2" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -31374,6 +32526,7 @@
       <c r="S500" s="2" t="inlineStr"/>
       <c r="T500" s="2" t="inlineStr"/>
       <c r="U500" s="2" t="inlineStr"/>
+      <c r="V500" s="2" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -31425,6 +32578,7 @@
       <c r="S501" s="2" t="inlineStr"/>
       <c r="T501" s="2" t="inlineStr"/>
       <c r="U501" s="2" t="inlineStr"/>
+      <c r="V501" s="2" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -31476,6 +32630,7 @@
         </is>
       </c>
       <c r="U502" s="2" t="inlineStr"/>
+      <c r="V502" s="2" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -31527,6 +32682,7 @@
       <c r="S503" s="2" t="inlineStr"/>
       <c r="T503" s="2" t="inlineStr"/>
       <c r="U503" s="2" t="inlineStr"/>
+      <c r="V503" s="2" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -31570,6 +32726,7 @@
       <c r="S504" s="2" t="inlineStr"/>
       <c r="T504" s="2" t="inlineStr"/>
       <c r="U504" s="2" t="inlineStr"/>
+      <c r="V504" s="2" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -31621,6 +32778,7 @@
         </is>
       </c>
       <c r="U505" s="2" t="inlineStr"/>
+      <c r="V505" s="2" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -31672,6 +32830,7 @@
         </is>
       </c>
       <c r="U506" s="2" t="inlineStr"/>
+      <c r="V506" s="2" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -31723,6 +32882,7 @@
       <c r="S507" s="2" t="inlineStr"/>
       <c r="T507" s="2" t="inlineStr"/>
       <c r="U507" s="2" t="inlineStr"/>
+      <c r="V507" s="2" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -31774,6 +32934,7 @@
       <c r="S508" s="2" t="inlineStr"/>
       <c r="T508" s="2" t="inlineStr"/>
       <c r="U508" s="2" t="inlineStr"/>
+      <c r="V508" s="2" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -31817,6 +32978,7 @@
       <c r="S509" s="2" t="inlineStr"/>
       <c r="T509" s="2" t="inlineStr"/>
       <c r="U509" s="2" t="inlineStr"/>
+      <c r="V509" s="2" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -31876,6 +33038,7 @@
       <c r="S510" s="2" t="inlineStr"/>
       <c r="T510" s="2" t="inlineStr"/>
       <c r="U510" s="2" t="inlineStr"/>
+      <c r="V510" s="2" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -31919,6 +33082,7 @@
       <c r="S511" s="2" t="inlineStr"/>
       <c r="T511" s="2" t="inlineStr"/>
       <c r="U511" s="2" t="inlineStr"/>
+      <c r="V511" s="2" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -31970,6 +33134,7 @@
       <c r="S512" s="2" t="inlineStr"/>
       <c r="T512" s="2" t="inlineStr"/>
       <c r="U512" s="2" t="inlineStr"/>
+      <c r="V512" s="2" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -32017,6 +33182,7 @@
       <c r="S513" s="2" t="inlineStr"/>
       <c r="T513" s="2" t="inlineStr"/>
       <c r="U513" s="2" t="inlineStr"/>
+      <c r="V513" s="2" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -32060,6 +33226,7 @@
       <c r="S514" s="2" t="inlineStr"/>
       <c r="T514" s="2" t="inlineStr"/>
       <c r="U514" s="2" t="inlineStr"/>
+      <c r="V514" s="2" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -32107,6 +33274,7 @@
       <c r="S515" s="2" t="inlineStr"/>
       <c r="T515" s="2" t="inlineStr"/>
       <c r="U515" s="2" t="inlineStr"/>
+      <c r="V515" s="2" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -32150,6 +33318,7 @@
       <c r="S516" s="2" t="inlineStr"/>
       <c r="T516" s="2" t="inlineStr"/>
       <c r="U516" s="2" t="inlineStr"/>
+      <c r="V516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -32201,6 +33370,7 @@
       <c r="S517" s="2" t="inlineStr"/>
       <c r="T517" s="2" t="inlineStr"/>
       <c r="U517" s="2" t="inlineStr"/>
+      <c r="V517" s="2" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -32252,6 +33422,7 @@
         </is>
       </c>
       <c r="U518" s="2" t="inlineStr"/>
+      <c r="V518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -32303,6 +33474,7 @@
       <c r="S519" s="2" t="inlineStr"/>
       <c r="T519" s="2" t="inlineStr"/>
       <c r="U519" s="2" t="inlineStr"/>
+      <c r="V519" s="2" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -32350,6 +33522,7 @@
       <c r="S520" s="2" t="inlineStr"/>
       <c r="T520" s="2" t="inlineStr"/>
       <c r="U520" s="2" t="inlineStr"/>
+      <c r="V520" s="2" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -32437,6 +33610,11 @@
       <c r="S521" s="2" t="inlineStr"/>
       <c r="T521" s="2" t="inlineStr"/>
       <c r="U521" s="2" t="inlineStr"/>
+      <c r="V521" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -32496,6 +33674,7 @@
       <c r="S522" s="2" t="inlineStr"/>
       <c r="T522" s="2" t="inlineStr"/>
       <c r="U522" s="2" t="inlineStr"/>
+      <c r="V522" s="2" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -32588,6 +33767,11 @@
       </c>
       <c r="T523" s="2" t="inlineStr"/>
       <c r="U523" s="2" t="inlineStr"/>
+      <c r="V523" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -32639,6 +33823,7 @@
       <c r="S524" s="2" t="inlineStr"/>
       <c r="T524" s="2" t="inlineStr"/>
       <c r="U524" s="2" t="inlineStr"/>
+      <c r="V524" s="2" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -32726,6 +33911,11 @@
       <c r="S525" s="2" t="inlineStr"/>
       <c r="T525" s="2" t="inlineStr"/>
       <c r="U525" s="2" t="inlineStr"/>
+      <c r="V525" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -32805,6 +33995,11 @@
       <c r="S526" s="2" t="inlineStr"/>
       <c r="T526" s="2" t="inlineStr"/>
       <c r="U526" s="2" t="inlineStr"/>
+      <c r="V526" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -32884,6 +34079,11 @@
       <c r="S527" s="2" t="inlineStr"/>
       <c r="T527" s="2" t="inlineStr"/>
       <c r="U527" s="2" t="inlineStr"/>
+      <c r="V527" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -32927,6 +34127,7 @@
       <c r="S528" s="2" t="inlineStr"/>
       <c r="T528" s="2" t="inlineStr"/>
       <c r="U528" s="2" t="inlineStr"/>
+      <c r="V528" s="2" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -32978,6 +34179,7 @@
       <c r="S529" s="2" t="inlineStr"/>
       <c r="T529" s="2" t="inlineStr"/>
       <c r="U529" s="2" t="inlineStr"/>
+      <c r="V529" s="2" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -33025,6 +34227,7 @@
       <c r="S530" s="2" t="inlineStr"/>
       <c r="T530" s="2" t="inlineStr"/>
       <c r="U530" s="2" t="inlineStr"/>
+      <c r="V530" s="2" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -33084,6 +34287,7 @@
       <c r="S531" s="2" t="inlineStr"/>
       <c r="T531" s="2" t="inlineStr"/>
       <c r="U531" s="2" t="inlineStr"/>
+      <c r="V531" s="2" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -33131,6 +34335,7 @@
       <c r="S532" s="2" t="inlineStr"/>
       <c r="T532" s="2" t="inlineStr"/>
       <c r="U532" s="2" t="inlineStr"/>
+      <c r="V532" s="2" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -33182,6 +34387,7 @@
       <c r="S533" s="2" t="inlineStr"/>
       <c r="T533" s="2" t="inlineStr"/>
       <c r="U533" s="2" t="inlineStr"/>
+      <c r="V533" s="2" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -33233,6 +34439,7 @@
       <c r="S534" s="2" t="inlineStr"/>
       <c r="T534" s="2" t="inlineStr"/>
       <c r="U534" s="2" t="inlineStr"/>
+      <c r="V534" s="2" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -33304,6 +34511,11 @@
       <c r="S535" s="2" t="inlineStr"/>
       <c r="T535" s="2" t="inlineStr"/>
       <c r="U535" s="2" t="inlineStr"/>
+      <c r="V535" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -33367,6 +34579,7 @@
       <c r="S536" s="2" t="inlineStr"/>
       <c r="T536" s="2" t="inlineStr"/>
       <c r="U536" s="2" t="inlineStr"/>
+      <c r="V536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -33410,6 +34623,7 @@
       <c r="S537" s="2" t="inlineStr"/>
       <c r="T537" s="2" t="inlineStr"/>
       <c r="U537" s="2" t="inlineStr"/>
+      <c r="V537" s="2" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -33457,6 +34671,7 @@
       <c r="S538" s="2" t="inlineStr"/>
       <c r="T538" s="2" t="inlineStr"/>
       <c r="U538" s="2" t="inlineStr"/>
+      <c r="V538" s="2" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -33508,6 +34723,7 @@
       <c r="S539" s="2" t="inlineStr"/>
       <c r="T539" s="2" t="inlineStr"/>
       <c r="U539" s="2" t="inlineStr"/>
+      <c r="V539" s="2" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -33567,6 +34783,7 @@
       <c r="S540" s="2" t="inlineStr"/>
       <c r="T540" s="2" t="inlineStr"/>
       <c r="U540" s="2" t="inlineStr"/>
+      <c r="V540" s="2" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -33646,6 +34863,11 @@
       <c r="S541" s="2" t="inlineStr"/>
       <c r="T541" s="2" t="inlineStr"/>
       <c r="U541" s="2" t="inlineStr"/>
+      <c r="V541" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -33701,6 +34923,7 @@
         </is>
       </c>
       <c r="U542" s="2" t="inlineStr"/>
+      <c r="V542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -33760,6 +34983,7 @@
       <c r="S543" s="2" t="inlineStr"/>
       <c r="T543" s="2" t="inlineStr"/>
       <c r="U543" s="2" t="inlineStr"/>
+      <c r="V543" s="2" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -33815,6 +35039,7 @@
         </is>
       </c>
       <c r="U544" s="2" t="inlineStr"/>
+      <c r="V544" s="2" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -33866,6 +35091,7 @@
       <c r="S545" s="2" t="inlineStr"/>
       <c r="T545" s="2" t="inlineStr"/>
       <c r="U545" s="2" t="inlineStr"/>
+      <c r="V545" s="2" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -33953,6 +35179,11 @@
       <c r="S546" s="2" t="inlineStr"/>
       <c r="T546" s="2" t="inlineStr"/>
       <c r="U546" s="2" t="inlineStr"/>
+      <c r="V546" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -34024,6 +35255,11 @@
       <c r="S547" s="2" t="inlineStr"/>
       <c r="T547" s="2" t="inlineStr"/>
       <c r="U547" s="2" t="inlineStr"/>
+      <c r="V547" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -34067,6 +35303,7 @@
       <c r="S548" s="2" t="inlineStr"/>
       <c r="T548" s="2" t="inlineStr"/>
       <c r="U548" s="2" t="inlineStr"/>
+      <c r="V548" s="2" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -34118,6 +35355,7 @@
       <c r="S549" s="2" t="inlineStr"/>
       <c r="T549" s="2" t="inlineStr"/>
       <c r="U549" s="2" t="inlineStr"/>
+      <c r="V549" s="2" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -34169,6 +35407,7 @@
       <c r="S550" s="2" t="inlineStr"/>
       <c r="T550" s="2" t="inlineStr"/>
       <c r="U550" s="2" t="inlineStr"/>
+      <c r="V550" s="2" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -34248,6 +35487,11 @@
       <c r="S551" s="2" t="inlineStr"/>
       <c r="T551" s="2" t="inlineStr"/>
       <c r="U551" s="2" t="inlineStr"/>
+      <c r="V551" s="2" t="inlineStr">
+        <is>
+          <t>pppppx------</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -34307,6 +35551,7 @@
       <c r="S552" s="2" t="inlineStr"/>
       <c r="T552" s="2" t="inlineStr"/>
       <c r="U552" s="2" t="inlineStr"/>
+      <c r="V552" s="2" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -34358,6 +35603,7 @@
       <c r="S553" s="2" t="inlineStr"/>
       <c r="T553" s="2" t="inlineStr"/>
       <c r="U553" s="2" t="inlineStr"/>
+      <c r="V553" s="2" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -34409,6 +35655,7 @@
       <c r="S554" s="2" t="inlineStr"/>
       <c r="T554" s="2" t="inlineStr"/>
       <c r="U554" s="2" t="inlineStr"/>
+      <c r="V554" s="2" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -34460,6 +35707,7 @@
         </is>
       </c>
       <c r="U555" s="2" t="inlineStr"/>
+      <c r="V555" s="2" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -34547,6 +35795,11 @@
       <c r="S556" s="2" t="inlineStr"/>
       <c r="T556" s="2" t="inlineStr"/>
       <c r="U556" s="2" t="inlineStr"/>
+      <c r="V556" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -34606,6 +35859,7 @@
       <c r="S557" s="2" t="inlineStr"/>
       <c r="T557" s="2" t="inlineStr"/>
       <c r="U557" s="2" t="inlineStr"/>
+      <c r="V557" s="2" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -34693,6 +35947,11 @@
       <c r="S558" s="2" t="inlineStr"/>
       <c r="T558" s="2" t="inlineStr"/>
       <c r="U558" s="2" t="inlineStr"/>
+      <c r="V558" s="2" t="inlineStr">
+        <is>
+          <t>pppppp------</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -34744,6 +36003,7 @@
         </is>
       </c>
       <c r="U559" s="2" t="inlineStr"/>
+      <c r="V559" s="2" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -34787,6 +36047,7 @@
       <c r="S560" s="2" t="inlineStr"/>
       <c r="T560" s="2" t="inlineStr"/>
       <c r="U560" s="2" t="inlineStr"/>
+      <c r="V560" s="2" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -34830,6 +36091,7 @@
       <c r="S561" s="2" t="inlineStr"/>
       <c r="T561" s="2" t="inlineStr"/>
       <c r="U561" s="2" t="inlineStr"/>
+      <c r="V561" s="2" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -34873,6 +36135,7 @@
       <c r="S562" s="2" t="inlineStr"/>
       <c r="T562" s="2" t="inlineStr"/>
       <c r="U562" s="2" t="inlineStr"/>
+      <c r="V562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -34924,6 +36187,7 @@
       <c r="S563" s="2" t="inlineStr"/>
       <c r="T563" s="2" t="inlineStr"/>
       <c r="U563" s="2" t="inlineStr"/>
+      <c r="V563" s="2" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -34971,6 +36235,7 @@
       <c r="S564" s="2" t="inlineStr"/>
       <c r="T564" s="2" t="inlineStr"/>
       <c r="U564" s="2" t="inlineStr"/>
+      <c r="V564" s="2" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -35014,6 +36279,7 @@
       <c r="S565" s="2" t="inlineStr"/>
       <c r="T565" s="2" t="inlineStr"/>
       <c r="U565" s="2" t="inlineStr"/>
+      <c r="V565" s="2" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -35073,6 +36339,7 @@
       <c r="S566" s="2" t="inlineStr"/>
       <c r="T566" s="2" t="inlineStr"/>
       <c r="U566" s="2" t="inlineStr"/>
+      <c r="V566" s="2" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -35132,6 +36399,7 @@
         </is>
       </c>
       <c r="U567" s="2" t="inlineStr"/>
+      <c r="V567" s="2" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -35183,6 +36451,7 @@
       <c r="S568" s="2" t="inlineStr"/>
       <c r="T568" s="2" t="inlineStr"/>
       <c r="U568" s="2" t="inlineStr"/>
+      <c r="V568" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -11065,7 +11065,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Moshe Deutch</t>
+          <t>Itche Host</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -11087,27 +11087,27 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>שותפות יששכר-זבולון + נוסף</t>
+          <t>שותפות יששכר-זבולון</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>העברה_בנקאית</t>
+          <t>Annualy</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>שולם 3 חודשים, 3 נדחו</t>
+          <t>שולם 12 חודשים</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>יוני</t>
+          <t>דצמבר</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr"/>
@@ -11123,7 +11123,7 @@
       <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" s="2" t="inlineStr">
         <is>
-          <t>pppxxx------</t>
+          <t>pppppppppppp</t>
         </is>
       </c>
     </row>
@@ -12587,11 +12587,7 @@
           <t>חיים</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>Chaim Hochman</t>
-        </is>
-      </c>
+      <c r="D189" s="2" t="inlineStr"/>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
@@ -12600,36 +12596,12 @@
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>קבוע</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>חודשי + נוסף</t>
-        </is>
-      </c>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="inlineStr">
-        <is>
-          <t>צק</t>
-        </is>
-      </c>
-      <c r="M189" s="2" t="inlineStr">
-        <is>
-          <t>שולם 7 חודשים</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr"/>
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr"/>
       <c r="Q189" s="2" t="inlineStr">
@@ -12641,11 +12613,7 @@
       <c r="S189" s="2" t="inlineStr"/>
       <c r="T189" s="2" t="inlineStr"/>
       <c r="U189" s="2" t="inlineStr"/>
-      <c r="V189" s="2" t="inlineStr">
-        <is>
-          <t>ppppppp-----</t>
-        </is>
-      </c>
+      <c r="V189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -17774,11 +17742,7 @@
           <t>חנה</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>Chaim Lax</t>
-        </is>
-      </c>
+      <c r="D269" s="2" t="inlineStr"/>
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
@@ -17787,36 +17751,12 @@
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="2" t="inlineStr">
-        <is>
-          <t>קבוע</t>
-        </is>
-      </c>
-      <c r="J269" s="2" t="inlineStr">
-        <is>
-          <t>שותפות יששכר-זבולון</t>
-        </is>
-      </c>
-      <c r="K269" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="L269" s="2" t="inlineStr">
-        <is>
-          <t>בנק_ווסט</t>
-        </is>
-      </c>
-      <c r="M269" s="2" t="inlineStr">
-        <is>
-          <t>שולם 7 חודשים</t>
-        </is>
-      </c>
-      <c r="N269" s="2" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
+      <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr"/>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr"/>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr"/>
       <c r="Q269" s="2" t="inlineStr">
@@ -17828,11 +17768,7 @@
       <c r="S269" s="2" t="inlineStr"/>
       <c r="T269" s="2" t="inlineStr"/>
       <c r="U269" s="2" t="inlineStr"/>
-      <c r="V269" s="2" t="inlineStr">
-        <is>
-          <t>ppppppp-----</t>
-        </is>
-      </c>
+      <c r="V269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -25596,11 +25532,7 @@
           <t>טדי</t>
         </is>
       </c>
-      <c r="D391" s="2" t="inlineStr">
-        <is>
-          <t>Tova Oscherowitz</t>
-        </is>
-      </c>
+      <c r="D391" s="2" t="inlineStr"/>
       <c r="E391" s="2" t="inlineStr"/>
       <c r="F391" s="2" t="inlineStr">
         <is>
@@ -25613,36 +25545,12 @@
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr"/>
-      <c r="I391" s="2" t="inlineStr">
-        <is>
-          <t>קבוע</t>
-        </is>
-      </c>
-      <c r="J391" s="2" t="inlineStr">
-        <is>
-          <t>שותפות יששכר-זבולון</t>
-        </is>
-      </c>
-      <c r="K391" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L391" s="2" t="inlineStr">
-        <is>
-          <t>אותורייז</t>
-        </is>
-      </c>
-      <c r="M391" s="2" t="inlineStr">
-        <is>
-          <t>שולם 7 חודשים</t>
-        </is>
-      </c>
-      <c r="N391" s="2" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
+      <c r="I391" s="2" t="inlineStr"/>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr"/>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr"/>
       <c r="O391" s="2" t="inlineStr"/>
       <c r="P391" s="2" t="inlineStr"/>
       <c r="Q391" s="2" t="inlineStr">
@@ -25654,11 +25562,7 @@
       <c r="S391" s="2" t="inlineStr"/>
       <c r="T391" s="2" t="inlineStr"/>
       <c r="U391" s="2" t="inlineStr"/>
-      <c r="V391" s="2" t="inlineStr">
-        <is>
-          <t>ppppppp-----</t>
-        </is>
-      </c>
+      <c r="V391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -32032,11 +31936,7 @@
           <t>אלי</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
-        <is>
-          <t>Avi Yulano</t>
-        </is>
-      </c>
+      <c r="D492" s="2" t="inlineStr"/>
       <c r="E492" s="2" t="inlineStr"/>
       <c r="F492" s="2" t="inlineStr">
         <is>
@@ -32053,36 +31953,12 @@
           <t>US</t>
         </is>
       </c>
-      <c r="I492" s="2" t="inlineStr">
-        <is>
-          <t>קבוע</t>
-        </is>
-      </c>
-      <c r="J492" s="2" t="inlineStr">
-        <is>
-          <t>חודשי</t>
-        </is>
-      </c>
-      <c r="K492" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="L492" s="2" t="inlineStr">
-        <is>
-          <t>בנק_ווסט</t>
-        </is>
-      </c>
-      <c r="M492" s="2" t="inlineStr">
-        <is>
-          <t>שולם 7 חודשים</t>
-        </is>
-      </c>
-      <c r="N492" s="2" t="inlineStr">
-        <is>
-          <t>יולי</t>
-        </is>
-      </c>
+      <c r="I492" s="2" t="inlineStr"/>
+      <c r="J492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr"/>
+      <c r="L492" s="2" t="inlineStr"/>
+      <c r="M492" s="2" t="inlineStr"/>
+      <c r="N492" s="2" t="inlineStr"/>
       <c r="O492" s="2" t="inlineStr"/>
       <c r="P492" s="2" t="inlineStr"/>
       <c r="Q492" s="2" t="inlineStr">
@@ -32094,11 +31970,7 @@
       <c r="S492" s="2" t="inlineStr"/>
       <c r="T492" s="2" t="inlineStr"/>
       <c r="U492" s="2" t="inlineStr"/>
-      <c r="V492" s="2" t="inlineStr">
-        <is>
-          <t>ppppppp-----</t>
-        </is>
-      </c>
+      <c r="V492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -35425,11 +35297,7 @@
           <t>שיינא</t>
         </is>
       </c>
-      <c r="D551" s="2" t="inlineStr">
-        <is>
-          <t>Isaac Rosenfeld</t>
-        </is>
-      </c>
+      <c r="D551" s="2" t="inlineStr"/>
       <c r="E551" s="2" t="inlineStr"/>
       <c r="F551" s="2" t="inlineStr">
         <is>
@@ -35446,36 +35314,12 @@
           <t>7650 Courtyard Run W, Boca Raton, FL 33433, US</t>
         </is>
       </c>
-      <c r="I551" s="2" t="inlineStr">
-        <is>
-          <t>קבוע</t>
-        </is>
-      </c>
-      <c r="J551" s="2" t="inlineStr">
-        <is>
-          <t>שותפות יששכר-זבולון</t>
-        </is>
-      </c>
-      <c r="K551" s="2" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="L551" s="2" t="inlineStr">
-        <is>
-          <t>העברה_בנקאית</t>
-        </is>
-      </c>
-      <c r="M551" s="2" t="inlineStr">
-        <is>
-          <t>שולם 5 חודשים, 1 נדחו</t>
-        </is>
-      </c>
-      <c r="N551" s="2" t="inlineStr">
-        <is>
-          <t>יוני</t>
-        </is>
-      </c>
+      <c r="I551" s="2" t="inlineStr"/>
+      <c r="J551" s="2" t="inlineStr"/>
+      <c r="K551" s="2" t="inlineStr"/>
+      <c r="L551" s="2" t="inlineStr"/>
+      <c r="M551" s="2" t="inlineStr"/>
+      <c r="N551" s="2" t="inlineStr"/>
       <c r="O551" s="2" t="inlineStr"/>
       <c r="P551" s="2" t="inlineStr"/>
       <c r="Q551" s="2" t="inlineStr">
@@ -35487,11 +35331,7 @@
       <c r="S551" s="2" t="inlineStr"/>
       <c r="T551" s="2" t="inlineStr"/>
       <c r="U551" s="2" t="inlineStr"/>
-      <c r="V551" s="2" t="inlineStr">
-        <is>
-          <t>pppppx------</t>
-        </is>
-      </c>
+      <c r="V551" s="2" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -1775,7 +1775,11 @@
           <t>טובה</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Tova Oscherowitz</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1792,12 +1796,36 @@
           <t>APT 309 5604 Rhodes AveValley Village, CA 91607, US ::: #309 5604 Rhodes AveValley Village, CA 91607, US</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>אותורייז</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
@@ -1809,7 +1837,11 @@
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10475,7 +10507,11 @@
           <t>משה אלטר אפרים</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr"/>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Moshe Deutch</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
@@ -10484,12 +10520,36 @@
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון + נוסף</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>העברה_בנקאית</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>שולם 3 חודשים, 3 נדחו</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -10509,7 +10569,11 @@
       <c r="S156" s="2" t="inlineStr"/>
       <c r="T156" s="2" t="inlineStr"/>
       <c r="U156" s="2" t="inlineStr"/>
-      <c r="V156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>pppxxx------</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11207,7 +11271,11 @@
           <t>חיים</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Chaim Hochman</t>
+        </is>
+      </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -11226,17 +11294,29 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr"/>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>חודשי + נוסף</t>
+        </is>
+      </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>צק</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
           <t>יולי</t>
@@ -11261,7 +11341,11 @@
       <c r="S168" s="2" t="inlineStr"/>
       <c r="T168" s="2" t="inlineStr"/>
       <c r="U168" s="2" t="inlineStr"/>
-      <c r="V168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -18638,7 +18722,11 @@
           <t>חיים הכהן</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr"/>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Chaim Lax</t>
+        </is>
+      </c>
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr">
         <is>
@@ -18647,12 +18735,36 @@
       </c>
       <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="2" t="inlineStr"/>
-      <c r="J283" s="2" t="inlineStr"/>
-      <c r="K283" s="2" t="inlineStr"/>
-      <c r="L283" s="2" t="inlineStr"/>
-      <c r="M283" s="2" t="inlineStr"/>
-      <c r="N283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>בנק_ווסט</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>שולם 7 חודשים</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>יולי</t>
+        </is>
+      </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -18676,7 +18788,11 @@
         </is>
       </c>
       <c r="U283" s="2" t="inlineStr"/>
-      <c r="V283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr">
+        <is>
+          <t>ppppppp-----</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -33504,7 +33620,11 @@
           <t>יצחק</t>
         </is>
       </c>
-      <c r="D522" s="2" t="inlineStr"/>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Isaac Rosenfeld</t>
+        </is>
+      </c>
       <c r="E522" s="2" t="inlineStr"/>
       <c r="F522" s="2" t="inlineStr">
         <is>
@@ -33521,12 +33641,36 @@
           <t>PO Box 582, Monsey, NY, US</t>
         </is>
       </c>
-      <c r="I522" s="2" t="inlineStr"/>
-      <c r="J522" s="2" t="inlineStr"/>
-      <c r="K522" s="2" t="inlineStr"/>
-      <c r="L522" s="2" t="inlineStr"/>
-      <c r="M522" s="2" t="inlineStr"/>
-      <c r="N522" s="2" t="inlineStr"/>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>קבוע</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>שותפות יששכר-זבולון</t>
+        </is>
+      </c>
+      <c r="K522" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>העברה_בנקאית</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="inlineStr">
+        <is>
+          <t>שולם 5 חודשים, 1 נדחו</t>
+        </is>
+      </c>
+      <c r="N522" s="2" t="inlineStr">
+        <is>
+          <t>יוני</t>
+        </is>
+      </c>
       <c r="O522" s="2" t="inlineStr">
         <is>
           <t>יששכר_זבולון</t>
@@ -33546,7 +33690,11 @@
       <c r="S522" s="2" t="inlineStr"/>
       <c r="T522" s="2" t="inlineStr"/>
       <c r="U522" s="2" t="inlineStr"/>
-      <c r="V522" s="2" t="inlineStr"/>
+      <c r="V522" s="2" t="inlineStr">
+        <is>
+          <t>pppppx------</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V569"/>
+  <dimension ref="A1:W569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -596,6 +597,11 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>סטטוס_חודשים</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>עבור_מה</t>
         </is>
       </c>
     </row>
@@ -650,6 +656,7 @@
       <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -738,6 +745,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -822,6 +830,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -874,6 +883,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -926,6 +936,7 @@
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -978,6 +989,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1026,6 +1038,7 @@
       <c r="T8" s="2" t="inlineStr"/>
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1118,6 +1131,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1214,6 +1228,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1290,6 +1305,7 @@
           <t>ppppppx-----</t>
         </is>
       </c>
+      <c r="W11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1342,6 +1358,7 @@
       <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1394,6 +1411,7 @@
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1442,6 +1460,7 @@
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1502,6 +1521,7 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1554,6 +1574,7 @@
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1598,6 +1619,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1642,6 +1664,7 @@
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1702,6 +1725,7 @@
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1758,6 +1782,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1842,6 +1867,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1934,6 +1960,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1986,6 +2013,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2046,6 +2074,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2098,6 +2127,7 @@
       </c>
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2162,6 +2192,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2254,6 +2285,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2310,6 +2342,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2362,6 +2395,7 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2414,6 +2448,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2502,6 +2537,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2550,6 +2586,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2634,6 +2671,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2686,6 +2724,7 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2730,6 +2769,7 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2774,6 +2814,7 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2866,6 +2907,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2958,6 +3000,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3010,6 +3053,7 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3062,6 +3106,7 @@
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3114,6 +3159,7 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3198,6 +3244,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3294,6 +3341,7 @@
           <t>ppppp-p-----</t>
         </is>
       </c>
+      <c r="W43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3346,6 +3394,7 @@
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3398,6 +3447,7 @@
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3450,6 +3500,7 @@
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3526,6 +3577,7 @@
           <t>xxxxxx------</t>
         </is>
       </c>
+      <c r="W47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3610,6 +3662,7 @@
           <t>pppp--p-----</t>
         </is>
       </c>
+      <c r="W48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3702,6 +3755,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3794,6 +3848,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3870,6 +3925,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3930,6 +3986,7 @@
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3982,6 +4039,7 @@
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4034,6 +4092,7 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4086,6 +4145,7 @@
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4146,6 +4206,7 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4238,6 +4299,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4290,6 +4352,7 @@
       </c>
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4342,6 +4405,7 @@
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4434,6 +4498,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4522,6 +4587,7 @@
           <t>p--pppp-----</t>
         </is>
       </c>
+      <c r="W61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4574,6 +4640,7 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4626,6 +4693,7 @@
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4710,6 +4778,7 @@
           <t>ppppppx-----</t>
         </is>
       </c>
+      <c r="W64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4762,6 +4831,7 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4854,6 +4924,7 @@
           <t>xxpppx------</t>
         </is>
       </c>
+      <c r="W66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4910,6 +4981,7 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4994,6 +5066,7 @@
           <t>xxppppp-----</t>
         </is>
       </c>
+      <c r="W68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5046,6 +5119,7 @@
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5110,6 +5184,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5162,6 +5237,7 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5214,6 +5290,7 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5278,6 +5355,7 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5358,6 +5436,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5402,6 +5481,7 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5494,6 +5574,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5582,6 +5663,7 @@
           <t>pppxxx------</t>
         </is>
       </c>
+      <c r="W77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5634,6 +5716,7 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5710,6 +5793,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5762,6 +5846,7 @@
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5814,6 +5899,7 @@
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5862,6 +5948,7 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5914,6 +6001,7 @@
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6006,6 +6094,7 @@
           <t>pppppx------</t>
         </is>
       </c>
+      <c r="W84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6102,6 +6191,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6154,6 +6244,7 @@
       <c r="T86" s="2" t="inlineStr"/>
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6238,6 +6329,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6318,6 +6410,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6378,6 +6471,7 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6422,6 +6516,7 @@
       <c r="T90" s="2" t="inlineStr"/>
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6474,6 +6569,7 @@
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6530,6 +6626,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6590,6 +6687,7 @@
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6634,6 +6732,7 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6686,6 +6785,7 @@
       </c>
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6770,6 +6870,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6814,6 +6915,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6906,6 +7008,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6962,6 +7065,7 @@
       </c>
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7058,6 +7162,7 @@
           <t>ppxxxpp-----</t>
         </is>
       </c>
+      <c r="W100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7150,6 +7255,7 @@
           <t>pp-pppp-----</t>
         </is>
       </c>
+      <c r="W101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7242,6 +7348,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7334,6 +7441,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7426,6 +7534,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7470,6 +7579,7 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7514,6 +7624,7 @@
       <c r="T106" s="2" t="inlineStr"/>
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7574,6 +7685,7 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7614,6 +7726,7 @@
       <c r="T108" s="2" t="inlineStr"/>
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7666,6 +7779,7 @@
       <c r="T109" s="2" t="inlineStr"/>
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7758,6 +7872,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7822,6 +7937,7 @@
       <c r="T111" s="2" t="inlineStr"/>
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7874,6 +7990,7 @@
       <c r="T112" s="2" t="inlineStr"/>
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7958,6 +8075,7 @@
           <t>--ppppp-----</t>
         </is>
       </c>
+      <c r="W113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8018,6 +8136,7 @@
       <c r="T114" s="2" t="inlineStr"/>
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8110,6 +8229,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8162,6 +8282,7 @@
       <c r="T116" s="2" t="inlineStr"/>
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8210,6 +8331,7 @@
       <c r="T117" s="2" t="inlineStr"/>
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8262,6 +8384,7 @@
       <c r="T118" s="2" t="inlineStr"/>
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8314,6 +8437,7 @@
       <c r="T119" s="2" t="inlineStr"/>
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8366,6 +8490,7 @@
       <c r="T120" s="2" t="inlineStr"/>
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8418,6 +8543,7 @@
       <c r="T121" s="2" t="inlineStr"/>
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8470,6 +8596,7 @@
       <c r="T122" s="2" t="inlineStr"/>
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8514,6 +8641,7 @@
       <c r="T123" s="2" t="inlineStr"/>
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8570,6 +8698,7 @@
       <c r="T124" s="2" t="inlineStr"/>
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8662,6 +8791,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8714,6 +8844,7 @@
       <c r="T126" s="2" t="inlineStr"/>
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8774,6 +8905,7 @@
       <c r="T127" s="2" t="inlineStr"/>
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8826,6 +8958,7 @@
       <c r="T128" s="2" t="inlineStr"/>
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8870,6 +9003,7 @@
       <c r="T129" s="2" t="inlineStr"/>
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8962,6 +9096,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -9014,6 +9149,7 @@
       <c r="T131" s="2" t="inlineStr"/>
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9066,6 +9202,7 @@
       <c r="T132" s="2" t="inlineStr"/>
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9118,6 +9255,7 @@
       <c r="T133" s="2" t="inlineStr"/>
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -9170,6 +9308,7 @@
       <c r="T134" s="2" t="inlineStr"/>
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9262,6 +9401,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9350,6 +9490,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -9406,6 +9547,7 @@
       </c>
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9458,6 +9600,7 @@
       <c r="T138" s="2" t="inlineStr"/>
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9518,6 +9661,7 @@
       <c r="T139" s="2" t="inlineStr"/>
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -9562,6 +9706,7 @@
       <c r="T140" s="2" t="inlineStr"/>
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9654,6 +9799,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9706,6 +9852,7 @@
       <c r="T142" s="2" t="inlineStr"/>
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9762,6 +9909,7 @@
       <c r="T143" s="2" t="inlineStr"/>
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9814,6 +9962,7 @@
       <c r="T144" s="2" t="inlineStr"/>
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9862,6 +10011,7 @@
       <c r="T145" s="2" t="inlineStr"/>
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9914,6 +10064,7 @@
       <c r="T146" s="2" t="inlineStr"/>
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9962,6 +10113,7 @@
       <c r="T147" s="2" t="inlineStr"/>
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10006,6 +10158,7 @@
       <c r="T148" s="2" t="inlineStr"/>
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10090,6 +10243,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -10178,6 +10332,7 @@
           <t>pppppxx-----</t>
         </is>
       </c>
+      <c r="W150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10226,6 +10381,7 @@
       <c r="T151" s="2" t="inlineStr"/>
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10322,6 +10478,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10374,6 +10531,7 @@
       <c r="T153" s="2" t="inlineStr"/>
       <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10438,6 +10596,7 @@
       </c>
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10490,6 +10649,7 @@
       </c>
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10574,6 +10734,7 @@
           <t>pppxxx------</t>
         </is>
       </c>
+      <c r="W156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10626,6 +10787,7 @@
       <c r="T157" s="2" t="inlineStr"/>
       <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10710,6 +10872,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10762,6 +10925,7 @@
       <c r="T159" s="2" t="inlineStr"/>
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10854,6 +11018,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -10906,6 +11071,7 @@
       <c r="T161" s="2" t="inlineStr"/>
       <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -10958,6 +11124,7 @@
       <c r="T162" s="2" t="inlineStr"/>
       <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11010,6 +11177,7 @@
       <c r="T163" s="2" t="inlineStr"/>
       <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -11062,6 +11230,7 @@
       <c r="T164" s="2" t="inlineStr"/>
       <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -11110,6 +11279,7 @@
       <c r="T165" s="2" t="inlineStr"/>
       <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -11190,6 +11360,7 @@
           <t>pppppppppppp</t>
         </is>
       </c>
+      <c r="W166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -11254,6 +11425,7 @@
       </c>
       <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -11346,6 +11518,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -11398,6 +11571,7 @@
       <c r="T169" s="2" t="inlineStr"/>
       <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11486,6 +11660,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11538,6 +11713,7 @@
       <c r="T171" s="2" t="inlineStr"/>
       <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -11634,6 +11810,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -11726,6 +11903,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11822,6 +12000,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11874,6 +12053,7 @@
       </c>
       <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11922,6 +12102,7 @@
       <c r="T176" s="2" t="inlineStr"/>
       <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -12014,6 +12195,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -12062,6 +12244,7 @@
       <c r="T178" s="2" t="inlineStr"/>
       <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -12130,6 +12313,7 @@
       </c>
       <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -12214,6 +12398,7 @@
           <t>ppppppx-----</t>
         </is>
       </c>
+      <c r="W180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -12258,6 +12443,7 @@
       <c r="T181" s="2" t="inlineStr"/>
       <c r="U181" s="2" t="inlineStr"/>
       <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -12314,6 +12500,7 @@
       </c>
       <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -12358,6 +12545,7 @@
       <c r="T183" s="2" t="inlineStr"/>
       <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -12410,6 +12598,7 @@
       <c r="T184" s="2" t="inlineStr"/>
       <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -12458,6 +12647,7 @@
       <c r="T185" s="2" t="inlineStr"/>
       <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -12550,6 +12740,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -12602,6 +12793,7 @@
       </c>
       <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -12654,6 +12846,7 @@
       <c r="T188" s="2" t="inlineStr"/>
       <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -12698,6 +12891,7 @@
       <c r="T189" s="2" t="inlineStr"/>
       <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -12790,6 +12984,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -12842,6 +13037,7 @@
       <c r="T191" s="2" t="inlineStr"/>
       <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -12886,6 +13082,7 @@
       <c r="T192" s="2" t="inlineStr"/>
       <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -12978,6 +13175,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -13038,6 +13236,7 @@
       <c r="T194" s="2" t="inlineStr"/>
       <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -13134,6 +13333,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -13234,6 +13434,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -13298,6 +13499,7 @@
       </c>
       <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -13350,6 +13552,7 @@
       <c r="T198" s="2" t="inlineStr"/>
       <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -13438,6 +13641,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -13530,6 +13734,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -13622,6 +13827,7 @@
           <t>ppppp-------</t>
         </is>
       </c>
+      <c r="W201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13706,6 +13912,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -13758,6 +13965,7 @@
       </c>
       <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -13818,6 +14026,7 @@
       <c r="T204" s="2" t="inlineStr"/>
       <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -13894,6 +14103,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -13978,6 +14188,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -14030,6 +14241,7 @@
       <c r="T207" s="2" t="inlineStr"/>
       <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -14074,6 +14286,7 @@
       <c r="T208" s="2" t="inlineStr"/>
       <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -14118,6 +14331,7 @@
       <c r="T209" s="2" t="inlineStr"/>
       <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -14174,6 +14388,7 @@
       </c>
       <c r="U210" s="2" t="inlineStr"/>
       <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -14233,6 +14448,7 @@
       <c r="T211" s="2" t="inlineStr"/>
       <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -14285,6 +14501,7 @@
       <c r="T212" s="2" t="inlineStr"/>
       <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -14329,6 +14546,7 @@
       <c r="T213" s="2" t="inlineStr"/>
       <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -14377,6 +14595,7 @@
       <c r="T214" s="2" t="inlineStr"/>
       <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -14425,6 +14644,7 @@
       <c r="T215" s="2" t="inlineStr"/>
       <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -14469,6 +14689,7 @@
       <c r="T216" s="2" t="inlineStr"/>
       <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -14513,6 +14734,7 @@
       <c r="T217" s="2" t="inlineStr"/>
       <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -14597,6 +14819,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -14649,6 +14872,7 @@
       <c r="T219" s="2" t="inlineStr"/>
       <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -14701,6 +14925,7 @@
       <c r="T220" s="2" t="inlineStr"/>
       <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -14753,6 +14978,7 @@
       <c r="T221" s="2" t="inlineStr"/>
       <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -14797,6 +15023,7 @@
       <c r="T222" s="2" t="inlineStr"/>
       <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -14849,6 +15076,7 @@
       <c r="T223" s="2" t="inlineStr"/>
       <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -14901,6 +15129,7 @@
       <c r="T224" s="2" t="inlineStr"/>
       <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -14985,6 +15214,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -15081,6 +15311,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -15165,6 +15396,7 @@
           <t>-----pp-----</t>
         </is>
       </c>
+      <c r="W227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -15213,6 +15445,7 @@
       <c r="T228" s="2" t="inlineStr"/>
       <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -15257,6 +15490,7 @@
       <c r="T229" s="2" t="inlineStr"/>
       <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -15305,6 +15539,7 @@
       <c r="T230" s="2" t="inlineStr"/>
       <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -15389,6 +15624,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -15445,6 +15681,7 @@
       <c r="T232" s="2" t="inlineStr"/>
       <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -15537,6 +15774,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -15581,6 +15819,7 @@
       <c r="T234" s="2" t="inlineStr"/>
       <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -15637,6 +15876,7 @@
       </c>
       <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -15693,6 +15933,7 @@
       <c r="T236" s="2" t="inlineStr"/>
       <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -15745,6 +15986,7 @@
       <c r="T237" s="2" t="inlineStr"/>
       <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -15789,6 +16031,7 @@
       <c r="T238" s="2" t="inlineStr"/>
       <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -15833,6 +16076,7 @@
       <c r="T239" s="2" t="inlineStr"/>
       <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -15925,6 +16169,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -16017,6 +16262,7 @@
           <t>pppxpp------</t>
         </is>
       </c>
+      <c r="W241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -16061,6 +16307,7 @@
       <c r="T242" s="2" t="inlineStr"/>
       <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -16145,6 +16392,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -16193,6 +16441,7 @@
       <c r="T244" s="2" t="inlineStr"/>
       <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -16289,6 +16538,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -16385,6 +16635,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -16481,6 +16732,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -16525,6 +16777,7 @@
       <c r="T248" s="2" t="inlineStr"/>
       <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -16577,6 +16830,7 @@
       <c r="T249" s="2" t="inlineStr"/>
       <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -16669,6 +16923,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -16753,6 +17008,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -16809,6 +17065,7 @@
       </c>
       <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" s="2" t="inlineStr"/>
+      <c r="W252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -16861,6 +17118,7 @@
       <c r="T253" s="2" t="inlineStr"/>
       <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" s="2" t="inlineStr"/>
+      <c r="W253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -16913,6 +17171,7 @@
       <c r="T254" s="2" t="inlineStr"/>
       <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" s="2" t="inlineStr"/>
+      <c r="W254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -16965,6 +17224,7 @@
       <c r="T255" s="2" t="inlineStr"/>
       <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -17043,6 +17303,11 @@
       <c r="V256" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>
+        </is>
+      </c>
+      <c r="W256" s="2" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר לאברכים</t>
         </is>
       </c>
     </row>
@@ -17097,6 +17362,7 @@
       <c r="T257" s="2" t="inlineStr"/>
       <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" s="2" t="inlineStr"/>
+      <c r="W257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -17181,6 +17447,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -17225,6 +17492,7 @@
       <c r="T259" s="2" t="inlineStr"/>
       <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" s="2" t="inlineStr"/>
+      <c r="W259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -17277,6 +17545,7 @@
       <c r="T260" s="2" t="inlineStr"/>
       <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -17321,6 +17590,7 @@
       <c r="T261" s="2" t="inlineStr"/>
       <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -17409,6 +17679,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -17501,6 +17772,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -17545,6 +17817,7 @@
       <c r="T264" s="2" t="inlineStr"/>
       <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -17637,6 +17910,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -17693,6 +17967,7 @@
       <c r="T266" s="2" t="inlineStr"/>
       <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" s="2" t="inlineStr"/>
+      <c r="W266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -17745,6 +18020,7 @@
       <c r="T267" s="2" t="inlineStr"/>
       <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -17797,6 +18073,7 @@
       </c>
       <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -17889,6 +18166,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -17933,6 +18211,7 @@
       <c r="T270" s="2" t="inlineStr"/>
       <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -17985,6 +18264,7 @@
       <c r="T271" s="2" t="inlineStr"/>
       <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -18045,6 +18325,7 @@
       <c r="T272" s="2" t="inlineStr"/>
       <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" s="2" t="inlineStr"/>
+      <c r="W272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -18097,6 +18378,7 @@
       <c r="T273" s="2" t="inlineStr"/>
       <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -18149,6 +18431,7 @@
       <c r="T274" s="2" t="inlineStr"/>
       <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -18201,6 +18484,7 @@
       <c r="T275" s="2" t="inlineStr"/>
       <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -18293,6 +18577,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -18389,6 +18674,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -18441,6 +18727,7 @@
       <c r="T278" s="2" t="inlineStr"/>
       <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -18533,6 +18820,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -18613,6 +18901,7 @@
           <t>pppppppppppp</t>
         </is>
       </c>
+      <c r="W280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -18681,6 +18970,7 @@
       </c>
       <c r="U281" s="2" t="inlineStr"/>
       <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -18733,6 +19023,7 @@
       <c r="T282" s="2" t="inlineStr"/>
       <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -18785,6 +19076,7 @@
       <c r="T283" s="2" t="inlineStr"/>
       <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -18873,6 +19165,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -18925,6 +19218,7 @@
       <c r="T285" s="2" t="inlineStr"/>
       <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -18981,6 +19275,7 @@
       </c>
       <c r="U286" s="2" t="inlineStr"/>
       <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -19037,6 +19332,7 @@
       <c r="T287" s="2" t="inlineStr"/>
       <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -19089,6 +19385,7 @@
       <c r="T288" s="2" t="inlineStr"/>
       <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -19141,6 +19438,7 @@
       <c r="T289" s="2" t="inlineStr"/>
       <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -19217,6 +19515,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -19269,6 +19568,7 @@
       <c r="T291" s="2" t="inlineStr"/>
       <c r="U291" s="2" t="inlineStr"/>
       <c r="V291" s="2" t="inlineStr"/>
+      <c r="W291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -19341,6 +19641,7 @@
       <c r="T292" s="2" t="inlineStr"/>
       <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -19433,6 +19734,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -19481,6 +19783,7 @@
       <c r="T294" s="2" t="inlineStr"/>
       <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -19533,6 +19836,7 @@
       <c r="T295" s="2" t="inlineStr"/>
       <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -19621,6 +19925,7 @@
           <t>---pppp-----</t>
         </is>
       </c>
+      <c r="W296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -19673,6 +19978,7 @@
       <c r="T297" s="2" t="inlineStr"/>
       <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -19725,6 +20031,7 @@
       <c r="T298" s="2" t="inlineStr"/>
       <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -19777,6 +20084,7 @@
       <c r="T299" s="2" t="inlineStr"/>
       <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -19821,6 +20129,7 @@
       <c r="T300" s="2" t="inlineStr"/>
       <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -19909,6 +20218,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -19953,6 +20263,7 @@
       <c r="T302" s="2" t="inlineStr"/>
       <c r="U302" s="2" t="inlineStr"/>
       <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -20001,6 +20312,7 @@
       <c r="T303" s="2" t="inlineStr"/>
       <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -20053,6 +20365,7 @@
       <c r="T304" s="2" t="inlineStr"/>
       <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -20097,6 +20410,7 @@
       <c r="T305" s="2" t="inlineStr"/>
       <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -20149,6 +20463,7 @@
       </c>
       <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -20193,6 +20508,7 @@
       <c r="T307" s="2" t="inlineStr"/>
       <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -20257,6 +20573,7 @@
       </c>
       <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -20313,6 +20630,7 @@
       </c>
       <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -20379,6 +20697,7 @@
       <c r="T310" s="2" t="inlineStr"/>
       <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -20435,6 +20754,7 @@
       <c r="T311" s="2" t="inlineStr"/>
       <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -20487,6 +20807,7 @@
       </c>
       <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -20547,6 +20868,7 @@
       <c r="T313" s="2" t="inlineStr"/>
       <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -20599,6 +20921,7 @@
       <c r="T314" s="2" t="inlineStr"/>
       <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -20659,6 +20982,7 @@
       <c r="T315" s="2" t="inlineStr"/>
       <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -20707,6 +21031,7 @@
       <c r="T316" s="2" t="inlineStr"/>
       <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" s="2" t="inlineStr"/>
+      <c r="W316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -20795,6 +21120,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -20887,6 +21213,7 @@
           <t>pppp--p-----</t>
         </is>
       </c>
+      <c r="W318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -20939,6 +21266,7 @@
       <c r="T319" s="2" t="inlineStr"/>
       <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -20991,6 +21319,7 @@
       </c>
       <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -21083,6 +21412,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -21175,6 +21505,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -21235,6 +21566,7 @@
       <c r="T323" s="2" t="inlineStr"/>
       <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -21287,6 +21619,7 @@
       </c>
       <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -21335,6 +21668,7 @@
       <c r="T325" s="2" t="inlineStr"/>
       <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -21387,6 +21721,7 @@
       <c r="T326" s="2" t="inlineStr"/>
       <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -21447,6 +21782,7 @@
         </is>
       </c>
       <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -21491,6 +21827,7 @@
       <c r="T328" s="2" t="inlineStr"/>
       <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -21539,6 +21876,7 @@
       <c r="T329" s="2" t="inlineStr"/>
       <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -21595,6 +21933,7 @@
       <c r="T330" s="2" t="inlineStr"/>
       <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -21651,6 +21990,7 @@
       <c r="T331" s="2" t="inlineStr"/>
       <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -21695,6 +22035,7 @@
       <c r="T332" s="2" t="inlineStr"/>
       <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -21771,6 +22112,7 @@
       </c>
       <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -21859,6 +22201,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -21911,6 +22254,7 @@
       <c r="T335" s="2" t="inlineStr"/>
       <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -22003,6 +22347,11 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>נר למאור</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -22079,6 +22428,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -22171,6 +22521,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -22263,6 +22614,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -22347,6 +22699,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -22437,6 +22790,11 @@
       <c r="V341" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>
+        </is>
+      </c>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>נר למאור</t>
         </is>
       </c>
     </row>
@@ -22491,6 +22849,7 @@
       <c r="T342" s="2" t="inlineStr"/>
       <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -22543,6 +22902,7 @@
       <c r="T343" s="2" t="inlineStr"/>
       <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -22587,6 +22947,7 @@
       <c r="T344" s="2" t="inlineStr"/>
       <c r="U344" s="2" t="inlineStr"/>
       <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -22671,6 +23032,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -22731,6 +23093,7 @@
       <c r="T346" s="2" t="inlineStr"/>
       <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -22815,6 +23178,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -22903,6 +23267,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -22995,6 +23360,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -23047,6 +23413,7 @@
       <c r="T350" s="2" t="inlineStr"/>
       <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -23139,6 +23506,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -23227,6 +23595,7 @@
           <t>pppppppp----</t>
         </is>
       </c>
+      <c r="W352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -23279,6 +23648,7 @@
       <c r="T353" s="2" t="inlineStr"/>
       <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" s="2" t="inlineStr"/>
+      <c r="W353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -23323,6 +23693,7 @@
       <c r="T354" s="2" t="inlineStr"/>
       <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -23367,6 +23738,7 @@
       <c r="T355" s="2" t="inlineStr"/>
       <c r="U355" s="2" t="inlineStr"/>
       <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -23427,6 +23799,7 @@
       <c r="T356" s="2" t="inlineStr"/>
       <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -23475,6 +23848,7 @@
       <c r="T357" s="2" t="inlineStr"/>
       <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -23527,6 +23901,7 @@
       </c>
       <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -23607,6 +23982,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -23663,6 +24039,7 @@
       <c r="T360" s="2" t="inlineStr"/>
       <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -23715,6 +24092,7 @@
       <c r="T361" s="2" t="inlineStr"/>
       <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -23763,6 +24141,7 @@
       <c r="T362" s="2" t="inlineStr"/>
       <c r="U362" s="2" t="inlineStr"/>
       <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -23855,6 +24234,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -23899,6 +24279,7 @@
       <c r="T364" s="2" t="inlineStr"/>
       <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -23951,6 +24332,7 @@
       <c r="T365" s="2" t="inlineStr"/>
       <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -24003,6 +24385,7 @@
       <c r="T366" s="2" t="inlineStr"/>
       <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -24047,6 +24430,7 @@
       <c r="T367" s="2" t="inlineStr"/>
       <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -24139,6 +24523,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -24231,6 +24616,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -24323,6 +24709,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -24375,6 +24762,7 @@
       </c>
       <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -24475,6 +24863,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -24559,6 +24948,7 @@
           <t>pxxxxxp-----</t>
         </is>
       </c>
+      <c r="W373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -24603,6 +24993,7 @@
       <c r="T374" s="2" t="inlineStr"/>
       <c r="U374" s="2" t="inlineStr"/>
       <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -24695,6 +25086,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -24751,6 +25143,7 @@
       <c r="T376" s="2" t="inlineStr"/>
       <c r="U376" s="2" t="inlineStr"/>
       <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -24835,6 +25228,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -24887,6 +25281,7 @@
       <c r="T378" s="2" t="inlineStr"/>
       <c r="U378" s="2" t="inlineStr"/>
       <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -24939,6 +25334,7 @@
       <c r="T379" s="2" t="inlineStr"/>
       <c r="U379" s="2" t="inlineStr"/>
       <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -25031,6 +25427,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -25123,6 +25520,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -25175,6 +25573,7 @@
       <c r="T382" s="2" t="inlineStr"/>
       <c r="U382" s="2" t="inlineStr"/>
       <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -25267,6 +25666,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -25323,6 +25723,7 @@
       <c r="T384" s="2" t="inlineStr"/>
       <c r="U384" s="2" t="inlineStr"/>
       <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -25375,6 +25776,7 @@
       <c r="T385" s="2" t="inlineStr"/>
       <c r="U385" s="2" t="inlineStr"/>
       <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -25459,6 +25861,7 @@
           <t>pxxxppp-----</t>
         </is>
       </c>
+      <c r="W386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -25531,6 +25934,7 @@
       <c r="T387" s="2" t="inlineStr"/>
       <c r="U387" s="2" t="inlineStr"/>
       <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -25575,6 +25979,7 @@
       <c r="T388" s="2" t="inlineStr"/>
       <c r="U388" s="2" t="inlineStr"/>
       <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -25619,6 +26024,7 @@
       <c r="T389" s="2" t="inlineStr"/>
       <c r="U389" s="2" t="inlineStr"/>
       <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -25667,6 +26073,7 @@
       <c r="T390" s="2" t="inlineStr"/>
       <c r="U390" s="2" t="inlineStr"/>
       <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -25711,6 +26118,7 @@
       <c r="T391" s="2" t="inlineStr"/>
       <c r="U391" s="2" t="inlineStr"/>
       <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -25759,6 +26167,7 @@
       <c r="T392" s="2" t="inlineStr"/>
       <c r="U392" s="2" t="inlineStr"/>
       <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -25811,6 +26220,7 @@
       <c r="T393" s="2" t="inlineStr"/>
       <c r="U393" s="2" t="inlineStr"/>
       <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -25863,6 +26273,7 @@
       <c r="T394" s="2" t="inlineStr"/>
       <c r="U394" s="2" t="inlineStr"/>
       <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -25923,6 +26334,7 @@
       <c r="T395" s="2" t="inlineStr"/>
       <c r="U395" s="2" t="inlineStr"/>
       <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -25979,6 +26391,7 @@
       </c>
       <c r="U396" s="2" t="inlineStr"/>
       <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -26031,6 +26444,7 @@
       <c r="T397" s="2" t="inlineStr"/>
       <c r="U397" s="2" t="inlineStr"/>
       <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -26083,6 +26497,7 @@
       <c r="T398" s="2" t="inlineStr"/>
       <c r="U398" s="2" t="inlineStr"/>
       <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -26179,6 +26594,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -26231,6 +26647,7 @@
       </c>
       <c r="U400" s="2" t="inlineStr"/>
       <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -26323,6 +26740,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -26371,6 +26789,7 @@
       <c r="T402" s="2" t="inlineStr"/>
       <c r="U402" s="2" t="inlineStr"/>
       <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -26459,6 +26878,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -26511,6 +26931,7 @@
       <c r="T404" s="2" t="inlineStr"/>
       <c r="U404" s="2" t="inlineStr"/>
       <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -26559,6 +26980,7 @@
       <c r="T405" s="2" t="inlineStr"/>
       <c r="U405" s="2" t="inlineStr"/>
       <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -26611,6 +27033,7 @@
       <c r="T406" s="2" t="inlineStr"/>
       <c r="U406" s="2" t="inlineStr"/>
       <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -26663,6 +27086,7 @@
       <c r="T407" s="2" t="inlineStr"/>
       <c r="U407" s="2" t="inlineStr"/>
       <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -26715,6 +27139,7 @@
       <c r="T408" s="2" t="inlineStr"/>
       <c r="U408" s="2" t="inlineStr"/>
       <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -26803,6 +27228,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W409" s="2" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -26887,6 +27313,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -26983,6 +27410,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -27035,6 +27463,7 @@
       <c r="T412" s="2" t="inlineStr"/>
       <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -27079,6 +27508,7 @@
       <c r="T413" s="2" t="inlineStr"/>
       <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -27171,6 +27601,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -27255,6 +27686,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -27347,6 +27779,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -27399,6 +27832,7 @@
       <c r="T417" s="2" t="inlineStr"/>
       <c r="U417" s="2" t="inlineStr"/>
       <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -27447,6 +27881,7 @@
       <c r="T418" s="2" t="inlineStr"/>
       <c r="U418" s="2" t="inlineStr"/>
       <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -27539,6 +27974,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -27595,6 +28031,7 @@
       <c r="T420" s="2" t="inlineStr"/>
       <c r="U420" s="2" t="inlineStr"/>
       <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -27647,6 +28084,7 @@
       <c r="T421" s="2" t="inlineStr"/>
       <c r="U421" s="2" t="inlineStr"/>
       <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -27731,6 +28169,7 @@
           <t>pppp--------</t>
         </is>
       </c>
+      <c r="W422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -27803,6 +28242,7 @@
       <c r="T423" s="2" t="inlineStr"/>
       <c r="U423" s="2" t="inlineStr"/>
       <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -27855,6 +28295,7 @@
       <c r="T424" s="2" t="inlineStr"/>
       <c r="U424" s="2" t="inlineStr"/>
       <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -27915,6 +28356,7 @@
       <c r="T425" s="2" t="inlineStr"/>
       <c r="U425" s="2" t="inlineStr"/>
       <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -27967,6 +28409,7 @@
       <c r="T426" s="2" t="inlineStr"/>
       <c r="U426" s="2" t="inlineStr"/>
       <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -28015,6 +28458,7 @@
       <c r="T427" s="2" t="inlineStr"/>
       <c r="U427" s="2" t="inlineStr"/>
       <c r="V427" s="2" t="inlineStr"/>
+      <c r="W427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -28063,6 +28507,7 @@
       <c r="T428" s="2" t="inlineStr"/>
       <c r="U428" s="2" t="inlineStr"/>
       <c r="V428" s="2" t="inlineStr"/>
+      <c r="W428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -28155,6 +28600,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -28207,6 +28653,7 @@
       <c r="T430" s="2" t="inlineStr"/>
       <c r="U430" s="2" t="inlineStr"/>
       <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -28259,6 +28706,7 @@
       <c r="T431" s="2" t="inlineStr"/>
       <c r="U431" s="2" t="inlineStr"/>
       <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -28303,6 +28751,7 @@
       <c r="T432" s="2" t="inlineStr"/>
       <c r="U432" s="2" t="inlineStr"/>
       <c r="V432" s="2" t="inlineStr"/>
+      <c r="W432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -28355,6 +28804,7 @@
       <c r="T433" s="2" t="inlineStr"/>
       <c r="U433" s="2" t="inlineStr"/>
       <c r="V433" s="2" t="inlineStr"/>
+      <c r="W433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -28411,6 +28861,7 @@
       <c r="T434" s="2" t="inlineStr"/>
       <c r="U434" s="2" t="inlineStr"/>
       <c r="V434" s="2" t="inlineStr"/>
+      <c r="W434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -28503,6 +28954,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -28591,6 +29043,11 @@
           <t>pppppxx-----</t>
         </is>
       </c>
+      <c r="W436" s="2" t="inlineStr">
+        <is>
+          <t>נר למאור</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -28683,6 +29140,7 @@
           <t>--pppxx-----</t>
         </is>
       </c>
+      <c r="W437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -28747,6 +29205,7 @@
       <c r="T438" s="2" t="inlineStr"/>
       <c r="U438" s="2" t="inlineStr"/>
       <c r="V438" s="2" t="inlineStr"/>
+      <c r="W438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -28811,6 +29270,7 @@
       </c>
       <c r="U439" s="2" t="inlineStr"/>
       <c r="V439" s="2" t="inlineStr"/>
+      <c r="W439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -28855,6 +29315,7 @@
       <c r="T440" s="2" t="inlineStr"/>
       <c r="U440" s="2" t="inlineStr"/>
       <c r="V440" s="2" t="inlineStr"/>
+      <c r="W440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -28899,6 +29360,7 @@
       <c r="T441" s="2" t="inlineStr"/>
       <c r="U441" s="2" t="inlineStr"/>
       <c r="V441" s="2" t="inlineStr"/>
+      <c r="W441" s="2" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -28991,6 +29453,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -29043,6 +29506,7 @@
       <c r="T443" s="2" t="inlineStr"/>
       <c r="U443" s="2" t="inlineStr"/>
       <c r="V443" s="2" t="inlineStr"/>
+      <c r="W443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -29099,6 +29563,7 @@
       </c>
       <c r="U444" s="2" t="inlineStr"/>
       <c r="V444" s="2" t="inlineStr"/>
+      <c r="W444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -29143,6 +29608,7 @@
       <c r="T445" s="2" t="inlineStr"/>
       <c r="U445" s="2" t="inlineStr"/>
       <c r="V445" s="2" t="inlineStr"/>
+      <c r="W445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -29239,6 +29705,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -29283,6 +29750,7 @@
       <c r="T447" s="2" t="inlineStr"/>
       <c r="U447" s="2" t="inlineStr"/>
       <c r="V447" s="2" t="inlineStr"/>
+      <c r="W447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -29375,6 +29843,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -29419,6 +29888,7 @@
       <c r="T449" s="2" t="inlineStr"/>
       <c r="U449" s="2" t="inlineStr"/>
       <c r="V449" s="2" t="inlineStr"/>
+      <c r="W449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -29463,6 +29933,7 @@
       <c r="T450" s="2" t="inlineStr"/>
       <c r="U450" s="2" t="inlineStr"/>
       <c r="V450" s="2" t="inlineStr"/>
+      <c r="W450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -29515,6 +29986,7 @@
       <c r="T451" s="2" t="inlineStr"/>
       <c r="U451" s="2" t="inlineStr"/>
       <c r="V451" s="2" t="inlineStr"/>
+      <c r="W451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -29567,6 +30039,7 @@
       <c r="T452" s="2" t="inlineStr"/>
       <c r="U452" s="2" t="inlineStr"/>
       <c r="V452" s="2" t="inlineStr"/>
+      <c r="W452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -29651,6 +30124,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -29703,6 +30177,7 @@
       <c r="T454" s="2" t="inlineStr"/>
       <c r="U454" s="2" t="inlineStr"/>
       <c r="V454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -29763,6 +30238,7 @@
       <c r="T455" s="2" t="inlineStr"/>
       <c r="U455" s="2" t="inlineStr"/>
       <c r="V455" s="2" t="inlineStr"/>
+      <c r="W455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -29807,6 +30283,7 @@
       <c r="T456" s="2" t="inlineStr"/>
       <c r="U456" s="2" t="inlineStr"/>
       <c r="V456" s="2" t="inlineStr"/>
+      <c r="W456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -29859,6 +30336,7 @@
       <c r="T457" s="2" t="inlineStr"/>
       <c r="U457" s="2" t="inlineStr"/>
       <c r="V457" s="2" t="inlineStr"/>
+      <c r="W457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -29911,6 +30389,7 @@
       <c r="T458" s="2" t="inlineStr"/>
       <c r="U458" s="2" t="inlineStr"/>
       <c r="V458" s="2" t="inlineStr"/>
+      <c r="W458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -30003,6 +30482,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -30055,6 +30535,7 @@
       <c r="T460" s="2" t="inlineStr"/>
       <c r="U460" s="2" t="inlineStr"/>
       <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -30111,6 +30592,7 @@
       <c r="T461" s="2" t="inlineStr"/>
       <c r="U461" s="2" t="inlineStr"/>
       <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -30171,6 +30653,7 @@
       <c r="T462" s="2" t="inlineStr"/>
       <c r="U462" s="2" t="inlineStr"/>
       <c r="V462" s="2" t="inlineStr"/>
+      <c r="W462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -30231,6 +30714,7 @@
       <c r="T463" s="2" t="inlineStr"/>
       <c r="U463" s="2" t="inlineStr"/>
       <c r="V463" s="2" t="inlineStr"/>
+      <c r="W463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -30287,6 +30771,7 @@
       <c r="T464" s="2" t="inlineStr"/>
       <c r="U464" s="2" t="inlineStr"/>
       <c r="V464" s="2" t="inlineStr"/>
+      <c r="W464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -30383,6 +30868,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -30431,6 +30917,7 @@
       <c r="T466" s="2" t="inlineStr"/>
       <c r="U466" s="2" t="inlineStr"/>
       <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -30495,6 +30982,7 @@
       <c r="T467" s="2" t="inlineStr"/>
       <c r="U467" s="2" t="inlineStr"/>
       <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -30547,6 +31035,7 @@
       <c r="T468" s="2" t="inlineStr"/>
       <c r="U468" s="2" t="inlineStr"/>
       <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -30599,6 +31088,7 @@
       <c r="T469" s="2" t="inlineStr"/>
       <c r="U469" s="2" t="inlineStr"/>
       <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -30651,6 +31141,7 @@
       <c r="T470" s="2" t="inlineStr"/>
       <c r="U470" s="2" t="inlineStr"/>
       <c r="V470" s="2" t="inlineStr"/>
+      <c r="W470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -30703,6 +31194,7 @@
       <c r="T471" s="2" t="inlineStr"/>
       <c r="U471" s="2" t="inlineStr"/>
       <c r="V471" s="2" t="inlineStr"/>
+      <c r="W471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -30779,6 +31271,7 @@
           <t>--p--p------</t>
         </is>
       </c>
+      <c r="W472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -30831,6 +31324,7 @@
       <c r="T473" s="2" t="inlineStr"/>
       <c r="U473" s="2" t="inlineStr"/>
       <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -30923,6 +31417,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -30975,6 +31470,7 @@
       <c r="T475" s="2" t="inlineStr"/>
       <c r="U475" s="2" t="inlineStr"/>
       <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -31059,6 +31555,7 @@
           <t>ppxxxpp-----</t>
         </is>
       </c>
+      <c r="W476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -31151,6 +31648,7 @@
           <t>pppppppppppp</t>
         </is>
       </c>
+      <c r="W477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -31199,6 +31697,7 @@
       <c r="T478" s="2" t="inlineStr"/>
       <c r="U478" s="2" t="inlineStr"/>
       <c r="V478" s="2" t="inlineStr"/>
+      <c r="W478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -31251,6 +31750,7 @@
       </c>
       <c r="U479" s="2" t="inlineStr"/>
       <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -31311,6 +31811,7 @@
       </c>
       <c r="U480" s="2" t="inlineStr"/>
       <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -31363,6 +31864,7 @@
       </c>
       <c r="U481" s="2" t="inlineStr"/>
       <c r="V481" s="2" t="inlineStr"/>
+      <c r="W481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -31419,6 +31921,7 @@
       </c>
       <c r="U482" s="2" t="inlineStr"/>
       <c r="V482" s="2" t="inlineStr"/>
+      <c r="W482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -31507,6 +32010,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -31567,6 +32071,7 @@
       <c r="T484" s="2" t="inlineStr"/>
       <c r="U484" s="2" t="inlineStr"/>
       <c r="V484" s="2" t="inlineStr"/>
+      <c r="W484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -31643,6 +32148,7 @@
           <t>ppppxxx-----</t>
         </is>
       </c>
+      <c r="W485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -31727,6 +32233,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -31779,6 +32286,7 @@
       <c r="T487" s="2" t="inlineStr"/>
       <c r="U487" s="2" t="inlineStr"/>
       <c r="V487" s="2" t="inlineStr"/>
+      <c r="W487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -31831,6 +32339,7 @@
       <c r="T488" s="2" t="inlineStr"/>
       <c r="U488" s="2" t="inlineStr"/>
       <c r="V488" s="2" t="inlineStr"/>
+      <c r="W488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -31875,6 +32384,7 @@
       <c r="T489" s="2" t="inlineStr"/>
       <c r="U489" s="2" t="inlineStr"/>
       <c r="V489" s="2" t="inlineStr"/>
+      <c r="W489" s="2" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -31931,6 +32441,7 @@
       </c>
       <c r="U490" s="2" t="inlineStr"/>
       <c r="V490" s="2" t="inlineStr"/>
+      <c r="W490" s="2" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -32023,6 +32534,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W491" s="2" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -32115,6 +32627,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -32167,6 +32680,7 @@
       <c r="T493" s="2" t="inlineStr"/>
       <c r="U493" s="2" t="inlineStr"/>
       <c r="V493" s="2" t="inlineStr"/>
+      <c r="W493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -32211,6 +32725,7 @@
       <c r="T494" s="2" t="inlineStr"/>
       <c r="U494" s="2" t="inlineStr"/>
       <c r="V494" s="2" t="inlineStr"/>
+      <c r="W494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -32263,6 +32778,7 @@
       <c r="T495" s="2" t="inlineStr"/>
       <c r="U495" s="2" t="inlineStr"/>
       <c r="V495" s="2" t="inlineStr"/>
+      <c r="W495" s="2" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -32315,6 +32831,7 @@
       <c r="T496" s="2" t="inlineStr"/>
       <c r="U496" s="2" t="inlineStr"/>
       <c r="V496" s="2" t="inlineStr"/>
+      <c r="W496" s="2" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -32359,6 +32876,7 @@
       <c r="T497" s="2" t="inlineStr"/>
       <c r="U497" s="2" t="inlineStr"/>
       <c r="V497" s="2" t="inlineStr"/>
+      <c r="W497" s="2" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -32451,6 +32969,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W498" s="2" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -32499,6 +33018,7 @@
       <c r="T499" s="2" t="inlineStr"/>
       <c r="U499" s="2" t="inlineStr"/>
       <c r="V499" s="2" t="inlineStr"/>
+      <c r="W499" s="2" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -32551,6 +33071,7 @@
       <c r="T500" s="2" t="inlineStr"/>
       <c r="U500" s="2" t="inlineStr"/>
       <c r="V500" s="2" t="inlineStr"/>
+      <c r="W500" s="2" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -32595,6 +33116,7 @@
       <c r="T501" s="2" t="inlineStr"/>
       <c r="U501" s="2" t="inlineStr"/>
       <c r="V501" s="2" t="inlineStr"/>
+      <c r="W501" s="2" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -32647,6 +33169,7 @@
       <c r="T502" s="2" t="inlineStr"/>
       <c r="U502" s="2" t="inlineStr"/>
       <c r="V502" s="2" t="inlineStr"/>
+      <c r="W502" s="2" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -32699,6 +33222,7 @@
       </c>
       <c r="U503" s="2" t="inlineStr"/>
       <c r="V503" s="2" t="inlineStr"/>
+      <c r="W503" s="2" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -32751,6 +33275,7 @@
       <c r="T504" s="2" t="inlineStr"/>
       <c r="U504" s="2" t="inlineStr"/>
       <c r="V504" s="2" t="inlineStr"/>
+      <c r="W504" s="2" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -32795,6 +33320,7 @@
       <c r="T505" s="2" t="inlineStr"/>
       <c r="U505" s="2" t="inlineStr"/>
       <c r="V505" s="2" t="inlineStr"/>
+      <c r="W505" s="2" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -32847,6 +33373,7 @@
       </c>
       <c r="U506" s="2" t="inlineStr"/>
       <c r="V506" s="2" t="inlineStr"/>
+      <c r="W506" s="2" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -32899,6 +33426,7 @@
       </c>
       <c r="U507" s="2" t="inlineStr"/>
       <c r="V507" s="2" t="inlineStr"/>
+      <c r="W507" s="2" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -32951,6 +33479,7 @@
       <c r="T508" s="2" t="inlineStr"/>
       <c r="U508" s="2" t="inlineStr"/>
       <c r="V508" s="2" t="inlineStr"/>
+      <c r="W508" s="2" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -33003,6 +33532,7 @@
       <c r="T509" s="2" t="inlineStr"/>
       <c r="U509" s="2" t="inlineStr"/>
       <c r="V509" s="2" t="inlineStr"/>
+      <c r="W509" s="2" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -33047,6 +33577,7 @@
       <c r="T510" s="2" t="inlineStr"/>
       <c r="U510" s="2" t="inlineStr"/>
       <c r="V510" s="2" t="inlineStr"/>
+      <c r="W510" s="2" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -33107,6 +33638,7 @@
       <c r="T511" s="2" t="inlineStr"/>
       <c r="U511" s="2" t="inlineStr"/>
       <c r="V511" s="2" t="inlineStr"/>
+      <c r="W511" s="2" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -33151,6 +33683,7 @@
       <c r="T512" s="2" t="inlineStr"/>
       <c r="U512" s="2" t="inlineStr"/>
       <c r="V512" s="2" t="inlineStr"/>
+      <c r="W512" s="2" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -33203,6 +33736,7 @@
       <c r="T513" s="2" t="inlineStr"/>
       <c r="U513" s="2" t="inlineStr"/>
       <c r="V513" s="2" t="inlineStr"/>
+      <c r="W513" s="2" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -33251,6 +33785,7 @@
       <c r="T514" s="2" t="inlineStr"/>
       <c r="U514" s="2" t="inlineStr"/>
       <c r="V514" s="2" t="inlineStr"/>
+      <c r="W514" s="2" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -33295,6 +33830,7 @@
       <c r="T515" s="2" t="inlineStr"/>
       <c r="U515" s="2" t="inlineStr"/>
       <c r="V515" s="2" t="inlineStr"/>
+      <c r="W515" s="2" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -33343,6 +33879,7 @@
       <c r="T516" s="2" t="inlineStr"/>
       <c r="U516" s="2" t="inlineStr"/>
       <c r="V516" s="2" t="inlineStr"/>
+      <c r="W516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -33387,6 +33924,7 @@
       <c r="T517" s="2" t="inlineStr"/>
       <c r="U517" s="2" t="inlineStr"/>
       <c r="V517" s="2" t="inlineStr"/>
+      <c r="W517" s="2" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -33439,6 +33977,7 @@
       <c r="T518" s="2" t="inlineStr"/>
       <c r="U518" s="2" t="inlineStr"/>
       <c r="V518" s="2" t="inlineStr"/>
+      <c r="W518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -33491,6 +34030,7 @@
       </c>
       <c r="U519" s="2" t="inlineStr"/>
       <c r="V519" s="2" t="inlineStr"/>
+      <c r="W519" s="2" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -33543,6 +34083,7 @@
       <c r="T520" s="2" t="inlineStr"/>
       <c r="U520" s="2" t="inlineStr"/>
       <c r="V520" s="2" t="inlineStr"/>
+      <c r="W520" s="2" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -33591,6 +34132,7 @@
       <c r="T521" s="2" t="inlineStr"/>
       <c r="U521" s="2" t="inlineStr"/>
       <c r="V521" s="2" t="inlineStr"/>
+      <c r="W521" s="2" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -33683,6 +34225,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W522" s="2" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -33775,6 +34318,7 @@
           <t>pppppx------</t>
         </is>
       </c>
+      <c r="W523" s="2" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -33872,6 +34416,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W524" s="2" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -33924,6 +34469,7 @@
       <c r="T525" s="2" t="inlineStr"/>
       <c r="U525" s="2" t="inlineStr"/>
       <c r="V525" s="2" t="inlineStr"/>
+      <c r="W525" s="2" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -34016,6 +34562,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W526" s="2" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -34100,6 +34647,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W527" s="2" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -34184,6 +34732,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W528" s="2" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -34228,6 +34777,7 @@
       <c r="T529" s="2" t="inlineStr"/>
       <c r="U529" s="2" t="inlineStr"/>
       <c r="V529" s="2" t="inlineStr"/>
+      <c r="W529" s="2" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -34280,6 +34830,7 @@
       <c r="T530" s="2" t="inlineStr"/>
       <c r="U530" s="2" t="inlineStr"/>
       <c r="V530" s="2" t="inlineStr"/>
+      <c r="W530" s="2" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -34328,6 +34879,7 @@
       <c r="T531" s="2" t="inlineStr"/>
       <c r="U531" s="2" t="inlineStr"/>
       <c r="V531" s="2" t="inlineStr"/>
+      <c r="W531" s="2" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -34388,6 +34940,7 @@
       <c r="T532" s="2" t="inlineStr"/>
       <c r="U532" s="2" t="inlineStr"/>
       <c r="V532" s="2" t="inlineStr"/>
+      <c r="W532" s="2" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -34436,6 +34989,7 @@
       <c r="T533" s="2" t="inlineStr"/>
       <c r="U533" s="2" t="inlineStr"/>
       <c r="V533" s="2" t="inlineStr"/>
+      <c r="W533" s="2" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -34488,6 +35042,7 @@
       <c r="T534" s="2" t="inlineStr"/>
       <c r="U534" s="2" t="inlineStr"/>
       <c r="V534" s="2" t="inlineStr"/>
+      <c r="W534" s="2" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -34540,6 +35095,7 @@
       <c r="T535" s="2" t="inlineStr"/>
       <c r="U535" s="2" t="inlineStr"/>
       <c r="V535" s="2" t="inlineStr"/>
+      <c r="W535" s="2" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -34616,6 +35172,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -34680,6 +35237,7 @@
       <c r="T537" s="2" t="inlineStr"/>
       <c r="U537" s="2" t="inlineStr"/>
       <c r="V537" s="2" t="inlineStr"/>
+      <c r="W537" s="2" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -34724,6 +35282,7 @@
       <c r="T538" s="2" t="inlineStr"/>
       <c r="U538" s="2" t="inlineStr"/>
       <c r="V538" s="2" t="inlineStr"/>
+      <c r="W538" s="2" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -34772,6 +35331,7 @@
       <c r="T539" s="2" t="inlineStr"/>
       <c r="U539" s="2" t="inlineStr"/>
       <c r="V539" s="2" t="inlineStr"/>
+      <c r="W539" s="2" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -34824,6 +35384,7 @@
       <c r="T540" s="2" t="inlineStr"/>
       <c r="U540" s="2" t="inlineStr"/>
       <c r="V540" s="2" t="inlineStr"/>
+      <c r="W540" s="2" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -34884,6 +35445,7 @@
       <c r="T541" s="2" t="inlineStr"/>
       <c r="U541" s="2" t="inlineStr"/>
       <c r="V541" s="2" t="inlineStr"/>
+      <c r="W541" s="2" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -34968,6 +35530,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -35024,6 +35587,7 @@
       </c>
       <c r="U543" s="2" t="inlineStr"/>
       <c r="V543" s="2" t="inlineStr"/>
+      <c r="W543" s="2" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -35084,6 +35648,7 @@
       <c r="T544" s="2" t="inlineStr"/>
       <c r="U544" s="2" t="inlineStr"/>
       <c r="V544" s="2" t="inlineStr"/>
+      <c r="W544" s="2" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -35140,6 +35705,7 @@
       </c>
       <c r="U545" s="2" t="inlineStr"/>
       <c r="V545" s="2" t="inlineStr"/>
+      <c r="W545" s="2" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -35192,6 +35758,7 @@
       <c r="T546" s="2" t="inlineStr"/>
       <c r="U546" s="2" t="inlineStr"/>
       <c r="V546" s="2" t="inlineStr"/>
+      <c r="W546" s="2" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -35284,6 +35851,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W547" s="2" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -35360,6 +35928,7 @@
           <t>ppppppp-----</t>
         </is>
       </c>
+      <c r="W548" s="2" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -35404,6 +35973,7 @@
       <c r="T549" s="2" t="inlineStr"/>
       <c r="U549" s="2" t="inlineStr"/>
       <c r="V549" s="2" t="inlineStr"/>
+      <c r="W549" s="2" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -35456,6 +36026,7 @@
       <c r="T550" s="2" t="inlineStr"/>
       <c r="U550" s="2" t="inlineStr"/>
       <c r="V550" s="2" t="inlineStr"/>
+      <c r="W550" s="2" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -35508,6 +36079,7 @@
       <c r="T551" s="2" t="inlineStr"/>
       <c r="U551" s="2" t="inlineStr"/>
       <c r="V551" s="2" t="inlineStr"/>
+      <c r="W551" s="2" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -35560,6 +36132,7 @@
       <c r="T552" s="2" t="inlineStr"/>
       <c r="U552" s="2" t="inlineStr"/>
       <c r="V552" s="2" t="inlineStr"/>
+      <c r="W552" s="2" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -35620,6 +36193,7 @@
       <c r="T553" s="2" t="inlineStr"/>
       <c r="U553" s="2" t="inlineStr"/>
       <c r="V553" s="2" t="inlineStr"/>
+      <c r="W553" s="2" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -35672,6 +36246,7 @@
       <c r="T554" s="2" t="inlineStr"/>
       <c r="U554" s="2" t="inlineStr"/>
       <c r="V554" s="2" t="inlineStr"/>
+      <c r="W554" s="2" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -35724,6 +36299,7 @@
       <c r="T555" s="2" t="inlineStr"/>
       <c r="U555" s="2" t="inlineStr"/>
       <c r="V555" s="2" t="inlineStr"/>
+      <c r="W555" s="2" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -35776,6 +36352,7 @@
       </c>
       <c r="U556" s="2" t="inlineStr"/>
       <c r="V556" s="2" t="inlineStr"/>
+      <c r="W556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -35868,6 +36445,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W557" s="2" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -35928,6 +36506,7 @@
       <c r="T558" s="2" t="inlineStr"/>
       <c r="U558" s="2" t="inlineStr"/>
       <c r="V558" s="2" t="inlineStr"/>
+      <c r="W558" s="2" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -36020,6 +36599,7 @@
           <t>pppppp------</t>
         </is>
       </c>
+      <c r="W559" s="2" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -36072,6 +36652,7 @@
       </c>
       <c r="U560" s="2" t="inlineStr"/>
       <c r="V560" s="2" t="inlineStr"/>
+      <c r="W560" s="2" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -36116,6 +36697,7 @@
       <c r="T561" s="2" t="inlineStr"/>
       <c r="U561" s="2" t="inlineStr"/>
       <c r="V561" s="2" t="inlineStr"/>
+      <c r="W561" s="2" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -36160,6 +36742,7 @@
       <c r="T562" s="2" t="inlineStr"/>
       <c r="U562" s="2" t="inlineStr"/>
       <c r="V562" s="2" t="inlineStr"/>
+      <c r="W562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -36204,6 +36787,7 @@
       <c r="T563" s="2" t="inlineStr"/>
       <c r="U563" s="2" t="inlineStr"/>
       <c r="V563" s="2" t="inlineStr"/>
+      <c r="W563" s="2" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -36256,6 +36840,7 @@
       <c r="T564" s="2" t="inlineStr"/>
       <c r="U564" s="2" t="inlineStr"/>
       <c r="V564" s="2" t="inlineStr"/>
+      <c r="W564" s="2" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -36304,6 +36889,7 @@
       <c r="T565" s="2" t="inlineStr"/>
       <c r="U565" s="2" t="inlineStr"/>
       <c r="V565" s="2" t="inlineStr"/>
+      <c r="W565" s="2" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -36348,6 +36934,7 @@
       <c r="T566" s="2" t="inlineStr"/>
       <c r="U566" s="2" t="inlineStr"/>
       <c r="V566" s="2" t="inlineStr"/>
+      <c r="W566" s="2" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -36408,6 +36995,7 @@
       <c r="T567" s="2" t="inlineStr"/>
       <c r="U567" s="2" t="inlineStr"/>
       <c r="V567" s="2" t="inlineStr"/>
+      <c r="W567" s="2" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -36468,6 +37056,7 @@
       </c>
       <c r="U568" s="2" t="inlineStr"/>
       <c r="V568" s="2" t="inlineStr"/>
+      <c r="W568" s="2" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -36520,6 +37109,7 @@
       <c r="T569" s="2" t="inlineStr"/>
       <c r="U569" s="2" t="inlineStr"/>
       <c r="V569" s="2" t="inlineStr"/>
+      <c r="W569" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -10,8 +10,9 @@
     <sheet name="תורמים" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="קובץ_התאמה_חודשיים" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="מזדמנים" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="שמות_לתפילה" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="לבדיקה_קוויטל" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="פרנס_יום" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="שמות_לתפילה" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="לבדיקה_קוויטל" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21213,7 +21214,11 @@
           <t>pppp--p-----</t>
         </is>
       </c>
-      <c r="W318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>פרנס יום — ג' אלול</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -44238,6 +44243,106 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>יום</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>חודש</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>סדר</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>שם_התורם</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>הקדשה</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>נוסח_תפילה</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>טלפון</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ג' אלול</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>אלול</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>לינדה מאגאזינטש</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>לע"נ אמה</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>+1 416-219-8391 / +1 416-222-6362</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51524,7 +51629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -21216,7 +21216,7 @@
       </c>
       <c r="W318" s="2" t="inlineStr">
         <is>
-          <t>פרנס יום — ג' אלול</t>
+          <t>פרנס יום — ג' אב</t>
         </is>
       </c>
     </row>
@@ -44306,7 +44306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ג' אלול</t>
+          <t>ג' אב</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -44314,11 +44314,11 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>אלול</t>
+          <t>אב</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -44327,10 +44327,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>לע"נ אמה</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ג' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>+1 416-219-8391 / +1 416-222-6362</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -21214,11 +21214,7 @@
           <t>pppp--p-----</t>
         </is>
       </c>
-      <c r="W318" s="2" t="inlineStr">
-        <is>
-          <t>פרנס יום — ג' אב</t>
-        </is>
-      </c>
+      <c r="W318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -44248,7 +44244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44257,8 +44253,9 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -44289,15 +44286,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>סכום</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>הקדשה</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>נוסח_תפילה</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>טלפון</t>
         </is>
@@ -44327,15 +44329,20 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ג' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>+1 416-219-8391 / +1 416-222-6362</t>
         </is>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -44308,11 +44308,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ג' אב</t>
+          <t>ב' אב</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ג' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
+          <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ב' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -44308,11 +44308,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ב' אב</t>
+          <t>ג' אב</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ב' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
+          <t>יהי רצון שזכות הלימודים והתפילות הנעשים כאן בכולל חצות בעת רצון הגדול של חצות הלילה עד הבוקר, ג' אב, יהיו ויעמדו לזכות לעילוי נשמת האשה החשובה איבן בת תמו ע"ה</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -7271,7 +7271,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>יוסי</t>
+          <t>יוסף</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7343,7 +7343,11 @@
       <c r="R102" s="2" t="inlineStr"/>
       <c r="S102" s="2" t="inlineStr"/>
       <c r="T102" s="2" t="inlineStr"/>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>יוסי</t>
+        </is>
+      </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>
@@ -10397,7 +10401,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>נתנאל</t>
+          <t>נתניאל</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -10473,7 +10477,11 @@
           <t>מוזג מכפילות</t>
         </is>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>נתנאל</t>
+        </is>
+      </c>
       <c r="V152" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>
@@ -35774,7 +35782,7 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>זאבי</t>
+          <t>זאב</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
@@ -35846,7 +35854,11 @@
       <c r="R547" s="2" t="inlineStr"/>
       <c r="S547" s="2" t="inlineStr"/>
       <c r="T547" s="2" t="inlineStr"/>
-      <c r="U547" s="2" t="inlineStr"/>
+      <c r="U547" s="2" t="inlineStr">
+        <is>
+          <t>זאבי</t>
+        </is>
+      </c>
       <c r="V547" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -1253,7 +1253,11 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>+972 548455419</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
@@ -3873,7 +3877,11 @@
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>+1 347-985-3263</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
@@ -4718,7 +4726,11 @@
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-613-0102</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
@@ -5741,7 +5753,11 @@
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>+1 374-541-3163 / +1 347-541-3163 / +1 917-498-2555 / +1 914-314-8421</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
@@ -12472,7 +12488,11 @@
       </c>
       <c r="D182" s="2" t="inlineStr"/>
       <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-836-0609 / +1 212-362-5643 / +1 212-362-8807</t>
+        </is>
+      </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
           <t>mhalpern12@gmail.com</t>
@@ -15007,7 +15027,11 @@
       </c>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>+1 732-824-1456</t>
+        </is>
+      </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
           <t>Eweingarden@gmail.com</t>
@@ -15572,7 +15596,11 @@
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-974-1750</t>
+        </is>
+      </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
           <t>msilber@silberlawny.com</t>
@@ -21295,7 +21323,11 @@
       </c>
       <c r="D320" s="2" t="inlineStr"/>
       <c r="E320" s="2" t="inlineStr"/>
-      <c r="F320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>+1 732-575-3142</t>
+        </is>
+      </c>
       <c r="G320" s="2" t="inlineStr"/>
       <c r="H320" s="2" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr"/>
@@ -31227,7 +31259,11 @@
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
-      <c r="F472" s="2" t="inlineStr"/>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-377-2571 / +1 917-597-3775</t>
+        </is>
+      </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
           <t>mkohn@mfandco.com</t>
@@ -33402,7 +33438,11 @@
       </c>
       <c r="D507" s="2" t="inlineStr"/>
       <c r="E507" s="2" t="inlineStr"/>
-      <c r="F507" s="2" t="inlineStr"/>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>+972 533158007</t>
+        </is>
+      </c>
       <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr"/>
       <c r="I507" s="2" t="inlineStr"/>
@@ -34595,7 +34635,11 @@
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr"/>
-      <c r="F527" s="2" t="inlineStr"/>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>+1 514-652-1926</t>
+        </is>
+      </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
           <t>mikelive5@hotmail.com</t>
@@ -36775,7 +36819,11 @@
       </c>
       <c r="D563" s="2" t="inlineStr"/>
       <c r="E563" s="2" t="inlineStr"/>
-      <c r="F563" s="2" t="inlineStr"/>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-416-0228</t>
+        </is>
+      </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
           <t>mike@schondevelopment.com</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -681,7 +681,11 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-377-0930 / +1 718-677-6869</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>elchanan@sterlingwm.com</t>
@@ -740,7 +744,11 @@
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>ב.אברמוביץ</t>
+        </is>
+      </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>ppppppp-----</t>
@@ -2099,7 +2107,11 @@
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>+972 533811989 / +1 908-330-9001</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2749,7 +2761,11 @@
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>+1 347-482-5177 / +1 917-686-9833</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>esti4gutman@yahoo.com</t>
@@ -2794,7 +2810,11 @@
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-809-6928 / +972 584052157</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>effiinwili@gmail.com</t>
@@ -5611,7 +5631,11 @@
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-754-6634</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>sbrody11211@yahoo.com</t>
@@ -12045,7 +12069,11 @@
       </c>
       <c r="D175" s="2" t="inlineStr"/>
       <c r="E175" s="2" t="inlineStr"/>
-      <c r="F175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>+972 542615474</t>
+        </is>
+      </c>
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
@@ -13961,7 +13989,11 @@
       </c>
       <c r="D203" s="2" t="inlineStr"/>
       <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>+1 732-664-1000</t>
+        </is>
+      </c>
       <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr"/>
@@ -14290,7 +14322,11 @@
       </c>
       <c r="D208" s="2" t="inlineStr"/>
       <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>+1 347-243-1500</t>
+        </is>
+      </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>simonw11204@gmail.com</t>
@@ -15681,7 +15717,11 @@
       </c>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>+972 548679292 / +972 527319882</t>
+        </is>
+      </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>michaelsinger@live.com.au</t>
@@ -15831,7 +15871,11 @@
       </c>
       <c r="D234" s="2" t="inlineStr"/>
       <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>+972 527168435</t>
+        </is>
+      </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
           <t>david@britanniagroup.NYC</t>
@@ -16088,7 +16132,11 @@
       </c>
       <c r="D239" s="2" t="inlineStr"/>
       <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-929-6162</t>
+        </is>
+      </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
           <t>etabak@bluestonegrp.com</t>
@@ -16984,7 +17032,11 @@
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
-      <c r="F251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>01312019883095</t>
+        </is>
+      </c>
       <c r="G251" s="2" t="inlineStr"/>
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr">
@@ -17829,7 +17881,11 @@
       </c>
       <c r="D264" s="2" t="inlineStr"/>
       <c r="E264" s="2" t="inlineStr"/>
-      <c r="F264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>+972 539356249 / +1 516-791-3311</t>
+        </is>
+      </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
           <t>lisajacobson11@gmail.com</t>
@@ -21680,7 +21736,11 @@
       </c>
       <c r="D325" s="2" t="inlineStr"/>
       <c r="E325" s="2" t="inlineStr"/>
-      <c r="F325" s="2" t="inlineStr"/>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>44 161 773 3670 / 07904-281848</t>
+        </is>
+      </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
           <t>smusic@talktalk.net</t>
@@ -22051,7 +22111,11 @@
       </c>
       <c r="D332" s="2" t="inlineStr"/>
       <c r="E332" s="2" t="inlineStr"/>
-      <c r="F332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-261-3446 / +1 516-610-5047</t>
+        </is>
+      </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
           <t>mmmoscovitz@gmail.com</t>
@@ -23909,7 +23973,11 @@
       </c>
       <c r="D358" s="2" t="inlineStr"/>
       <c r="E358" s="2" t="inlineStr"/>
-      <c r="F358" s="2" t="inlineStr"/>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>+1 732-267-6746</t>
+        </is>
+      </c>
       <c r="G358" s="2" t="inlineStr"/>
       <c r="H358" s="2" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr"/>
@@ -24295,7 +24363,11 @@
       </c>
       <c r="D364" s="2" t="inlineStr"/>
       <c r="E364" s="2" t="inlineStr"/>
-      <c r="F364" s="2" t="inlineStr"/>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>+1 732-523-1113</t>
+        </is>
+      </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
           <t>33miron@gmail.com</t>
@@ -24446,7 +24518,11 @@
       </c>
       <c r="D367" s="2" t="inlineStr"/>
       <c r="E367" s="2" t="inlineStr"/>
-      <c r="F367" s="2" t="inlineStr"/>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-339-2468</t>
+        </is>
+      </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
           <t>Rivky.Nussbaum@lsdco.com</t>
@@ -28767,7 +28843,11 @@
       </c>
       <c r="D432" s="2" t="inlineStr"/>
       <c r="E432" s="2" t="inlineStr"/>
-      <c r="F432" s="2" t="inlineStr"/>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-501-8806</t>
+        </is>
+      </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
           <t>df@thelesergroup.com</t>
@@ -29331,7 +29411,11 @@
       </c>
       <c r="D440" s="2" t="inlineStr"/>
       <c r="E440" s="2" t="inlineStr"/>
-      <c r="F440" s="2" t="inlineStr"/>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-471-1626</t>
+        </is>
+      </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
           <t>Fertig.Y@fibi.co.il</t>
@@ -30104,7 +30188,11 @@
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
-      <c r="F453" s="2" t="inlineStr"/>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>+1 516-295-3181 / +1 516-633-3548</t>
+        </is>
+      </c>
       <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr"/>
       <c r="I453" s="2" t="inlineStr">
@@ -31624,7 +31712,11 @@
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
-      <c r="F477" s="2" t="inlineStr"/>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>+1 650-703-1237</t>
+        </is>
+      </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
           <t>esti.karp@gmail.com</t>
@@ -32217,7 +32309,11 @@
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr"/>
-      <c r="F486" s="2" t="inlineStr"/>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>+1 917-209-5919</t>
+        </is>
+      </c>
       <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="2" t="inlineStr"/>
       <c r="I486" s="2" t="inlineStr">
@@ -33601,7 +33697,11 @@
       </c>
       <c r="D510" s="2" t="inlineStr"/>
       <c r="E510" s="2" t="inlineStr"/>
-      <c r="F510" s="2" t="inlineStr"/>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>+972 556686050</t>
+        </is>
+      </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
           <t>chanirubenstein@gmail.com</t>
@@ -33707,7 +33807,11 @@
       </c>
       <c r="D512" s="2" t="inlineStr"/>
       <c r="E512" s="2" t="inlineStr"/>
-      <c r="F512" s="2" t="inlineStr"/>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>+1 914-806-5826</t>
+        </is>
+      </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
           <t>deenadee94@gmail.com</t>
@@ -34805,7 +34909,11 @@
       </c>
       <c r="D529" s="2" t="inlineStr"/>
       <c r="E529" s="2" t="inlineStr"/>
-      <c r="F529" s="2" t="inlineStr"/>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>+380633855610</t>
+        </is>
+      </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
           <t>charles.rappaport@gmail.com</t>
@@ -34903,7 +35011,11 @@
       </c>
       <c r="D531" s="2" t="inlineStr"/>
       <c r="E531" s="2" t="inlineStr"/>
-      <c r="F531" s="2" t="inlineStr"/>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>+972 586188883</t>
+        </is>
+      </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
           <t>pinishaool@gmail.com</t>
@@ -35013,7 +35125,11 @@
       </c>
       <c r="D533" s="2" t="inlineStr"/>
       <c r="E533" s="2" t="inlineStr"/>
-      <c r="F533" s="2" t="inlineStr"/>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>+1 718-664-8508 / +1 646-261-7569</t>
+        </is>
+      </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
           <t>baruchsebat@gmail.com</t>
@@ -36729,7 +36845,11 @@
       </c>
       <c r="D561" s="2" t="inlineStr"/>
       <c r="E561" s="2" t="inlineStr"/>
-      <c r="F561" s="2" t="inlineStr"/>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>+972 504123124</t>
+        </is>
+      </c>
       <c r="G561" s="2" t="inlineStr">
         <is>
           <t>ronit030292@gmail.com</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -2107,11 +2107,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>+972 533811989 / +1 908-330-9001</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -5631,11 +5627,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>+1 917-754-6634</t>
-        </is>
-      </c>
+      <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>sbrody11211@yahoo.com</t>
@@ -12069,11 +12061,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr"/>
       <c r="E175" s="2" t="inlineStr"/>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>+972 542615474</t>
-        </is>
-      </c>
+      <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
@@ -13989,11 +13977,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr"/>
       <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>+1 732-664-1000</t>
-        </is>
-      </c>
+      <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr"/>
@@ -14322,11 +14306,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr"/>
       <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>+1 347-243-1500</t>
-        </is>
-      </c>
+      <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>simonw11204@gmail.com</t>
@@ -15717,11 +15697,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>+972 548679292 / +972 527319882</t>
-        </is>
-      </c>
+      <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>michaelsinger@live.com.au</t>
@@ -15871,11 +15847,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr"/>
       <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>+972 527168435</t>
-        </is>
-      </c>
+      <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
           <t>david@britanniagroup.NYC</t>
@@ -16132,11 +16104,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr"/>
       <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>+1 917-929-6162</t>
-        </is>
-      </c>
+      <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
           <t>etabak@bluestonegrp.com</t>
@@ -17032,11 +17000,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>01312019883095</t>
-        </is>
-      </c>
+      <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr"/>
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr">
@@ -17881,11 +17845,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr"/>
       <c r="E264" s="2" t="inlineStr"/>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>+972 539356249 / +1 516-791-3311</t>
-        </is>
-      </c>
+      <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
           <t>lisajacobson11@gmail.com</t>
@@ -21736,11 +21696,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr"/>
       <c r="E325" s="2" t="inlineStr"/>
-      <c r="F325" s="2" t="inlineStr">
-        <is>
-          <t>44 161 773 3670 / 07904-281848</t>
-        </is>
-      </c>
+      <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr">
         <is>
           <t>smusic@talktalk.net</t>
@@ -22111,11 +22067,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr"/>
       <c r="E332" s="2" t="inlineStr"/>
-      <c r="F332" s="2" t="inlineStr">
-        <is>
-          <t>+1 718-261-3446 / +1 516-610-5047</t>
-        </is>
-      </c>
+      <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
           <t>mmmoscovitz@gmail.com</t>
@@ -23973,11 +23925,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr"/>
       <c r="E358" s="2" t="inlineStr"/>
-      <c r="F358" s="2" t="inlineStr">
-        <is>
-          <t>+1 732-267-6746</t>
-        </is>
-      </c>
+      <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr"/>
       <c r="H358" s="2" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr"/>
@@ -24363,11 +24311,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr"/>
       <c r="E364" s="2" t="inlineStr"/>
-      <c r="F364" s="2" t="inlineStr">
-        <is>
-          <t>+1 732-523-1113</t>
-        </is>
-      </c>
+      <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
           <t>33miron@gmail.com</t>
@@ -24518,11 +24462,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr"/>
       <c r="E367" s="2" t="inlineStr"/>
-      <c r="F367" s="2" t="inlineStr">
-        <is>
-          <t>+1 718-339-2468</t>
-        </is>
-      </c>
+      <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
           <t>Rivky.Nussbaum@lsdco.com</t>
@@ -28843,11 +28783,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr"/>
       <c r="E432" s="2" t="inlineStr"/>
-      <c r="F432" s="2" t="inlineStr">
-        <is>
-          <t>+1 917-501-8806</t>
-        </is>
-      </c>
+      <c r="F432" s="2" t="inlineStr"/>
       <c r="G432" s="2" t="inlineStr">
         <is>
           <t>df@thelesergroup.com</t>
@@ -29411,11 +29347,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr"/>
       <c r="E440" s="2" t="inlineStr"/>
-      <c r="F440" s="2" t="inlineStr">
-        <is>
-          <t>+1 718-471-1626</t>
-        </is>
-      </c>
+      <c r="F440" s="2" t="inlineStr"/>
       <c r="G440" s="2" t="inlineStr">
         <is>
           <t>Fertig.Y@fibi.co.il</t>
@@ -30188,11 +30120,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
-      <c r="F453" s="2" t="inlineStr">
-        <is>
-          <t>+1 516-295-3181 / +1 516-633-3548</t>
-        </is>
-      </c>
+      <c r="F453" s="2" t="inlineStr"/>
       <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr"/>
       <c r="I453" s="2" t="inlineStr">
@@ -31712,11 +31640,7 @@
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
-      <c r="F477" s="2" t="inlineStr">
-        <is>
-          <t>+1 650-703-1237</t>
-        </is>
-      </c>
+      <c r="F477" s="2" t="inlineStr"/>
       <c r="G477" s="2" t="inlineStr">
         <is>
           <t>esti.karp@gmail.com</t>
@@ -32309,11 +32233,7 @@
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr"/>
-      <c r="F486" s="2" t="inlineStr">
-        <is>
-          <t>+1 917-209-5919</t>
-        </is>
-      </c>
+      <c r="F486" s="2" t="inlineStr"/>
       <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="2" t="inlineStr"/>
       <c r="I486" s="2" t="inlineStr">
@@ -33697,11 +33617,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr"/>
       <c r="E510" s="2" t="inlineStr"/>
-      <c r="F510" s="2" t="inlineStr">
-        <is>
-          <t>+972 556686050</t>
-        </is>
-      </c>
+      <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
           <t>chanirubenstein@gmail.com</t>
@@ -33807,11 +33723,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr"/>
       <c r="E512" s="2" t="inlineStr"/>
-      <c r="F512" s="2" t="inlineStr">
-        <is>
-          <t>+1 914-806-5826</t>
-        </is>
-      </c>
+      <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
           <t>deenadee94@gmail.com</t>
@@ -34909,11 +34821,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr"/>
       <c r="E529" s="2" t="inlineStr"/>
-      <c r="F529" s="2" t="inlineStr">
-        <is>
-          <t>+380633855610</t>
-        </is>
-      </c>
+      <c r="F529" s="2" t="inlineStr"/>
       <c r="G529" s="2" t="inlineStr">
         <is>
           <t>charles.rappaport@gmail.com</t>
@@ -35011,11 +34919,7 @@
       </c>
       <c r="D531" s="2" t="inlineStr"/>
       <c r="E531" s="2" t="inlineStr"/>
-      <c r="F531" s="2" t="inlineStr">
-        <is>
-          <t>+972 586188883</t>
-        </is>
-      </c>
+      <c r="F531" s="2" t="inlineStr"/>
       <c r="G531" s="2" t="inlineStr">
         <is>
           <t>pinishaool@gmail.com</t>
@@ -35125,11 +35029,7 @@
       </c>
       <c r="D533" s="2" t="inlineStr"/>
       <c r="E533" s="2" t="inlineStr"/>
-      <c r="F533" s="2" t="inlineStr">
-        <is>
-          <t>+1 718-664-8508 / +1 646-261-7569</t>
-        </is>
-      </c>
+      <c r="F533" s="2" t="inlineStr"/>
       <c r="G533" s="2" t="inlineStr">
         <is>
           <t>baruchsebat@gmail.com</t>
@@ -36845,11 +36745,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr"/>
       <c r="E561" s="2" t="inlineStr"/>
-      <c r="F561" s="2" t="inlineStr">
-        <is>
-          <t>+972 504123124</t>
-        </is>
-      </c>
+      <c r="F561" s="2" t="inlineStr"/>
       <c r="G561" s="2" t="inlineStr">
         <is>
           <t>ronit030292@gmail.com</t>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -7938,7 +7938,7 @@
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -12314,7 +12314,7 @@
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -18983,13 +18983,13 @@
       <c r="H281" s="2" t="inlineStr"/>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr"/>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="L281" s="2" t="inlineStr"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr"/>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr"/>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr"/>
@@ -28263,7 +28263,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>מזדמן</t>
+          <t>קבוע</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr"/>

--- a/starter/crm-donors-filled.xlsx
+++ b/starter/crm-donors-filled.xlsx
@@ -11385,7 +11385,11 @@
           <t>דצמבר</t>
         </is>
       </c>
-      <c r="O166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
       <c r="P166" s="2" t="inlineStr"/>
       <c r="Q166" s="2" t="inlineStr">
         <is>
@@ -22469,7 +22473,11 @@
           <t>יולי</t>
         </is>
       </c>
-      <c r="O337" s="2" t="inlineStr"/>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>יששכר_זבולון</t>
+        </is>
+      </c>
       <c r="P337" s="2" t="inlineStr"/>
       <c r="Q337" s="2" t="inlineStr">
         <is>
@@ -23209,7 +23217,7 @@
       </c>
       <c r="O347" s="2" t="inlineStr">
         <is>
-          <t>קוויטל_כללי</t>
+          <t>יששכר_זבולון</t>
         </is>
       </c>
       <c r="P347" s="2" t="inlineStr">
